--- a/Plannings 2026 S19.xlsx
+++ b/Plannings 2026 S19.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{84830FEF-CD99-488C-9111-90B341AA8F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{84830FEF-CD99-488C-9111-90B341AA8F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA600701-563D-419E-AFCD-310519774913}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="135">
   <si>
     <t>Planning des salariés du 04/05/2026 au 10/05/2026</t>
   </si>
@@ -205,9 +205,6 @@
   </si>
   <si>
     <t>18:30/20:30</t>
-  </si>
-  <si>
-    <t>21:15/22:15</t>
   </si>
   <si>
     <t>DIVIEN Yohan</t>
@@ -528,7 +525,7 @@
       <name val="Helvetica"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -538,11 +535,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80FF80"/>
       </patternFill>
     </fill>
     <fill>
@@ -611,7 +603,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -631,10 +623,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2372,50 +2361,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="40" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000028000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>30</xdr:row>
@@ -2770,109 +2715,549 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="49" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000031000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="50" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000032000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000031000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000032000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="51" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000033000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="52" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000034000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="53" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000035000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="54" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000036000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="55" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000037000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="56" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000038000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="57" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000039000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="58" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="59" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="60" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="51" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000033000000}"/>
+        <xdr:cNvPr id="61" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2900,208 +3285,32 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="52" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000034000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="53" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000035000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="54" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000036000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="55" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000037000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="56" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000038000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="62" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3122,162 +3331,30 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="57" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000039000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="58" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="59" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="60" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="63" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3309,10 +3386,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="61" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D000000}"/>
+        <xdr:cNvPr id="64" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000040000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3340,111 +3417,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="62" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="63" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="64" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000040000000}"/>
+        <xdr:cNvPr id="65" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000041000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3474,21 +3463,21 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>53</xdr:row>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>53</xdr:row>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="65" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000041000000}"/>
+        <xdr:cNvPr id="66" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3518,21 +3507,21 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:row>57</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:row>57</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="66" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042000000}"/>
+        <xdr:cNvPr id="67" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3560,23 +3549,67 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="68" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="67" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043000000}"/>
+        <xdr:cNvPr id="69" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3604,67 +3637,67 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="68" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="70" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="69" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
+        <xdr:cNvPr id="71" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3692,32 +3725,120 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="70" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="72" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3749,10 +3870,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="71" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047000000}"/>
+        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3780,155 +3901,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="72" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>69</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>69</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
+        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3956,23 +3945,243 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>80</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>80</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
+        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4000,67 +4209,155 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4088,120 +4385,120 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000057000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4222,38 +4519,214 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>84</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>82</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4266,30 +4739,30 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>91</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4310,21 +4783,21 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>91</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4352,111 +4825,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000057000000}"/>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4484,111 +4869,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>93</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>93</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
+        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4616,252 +4913,32 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>93</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>93</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>93</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>93</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4882,30 +4959,30 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>93</xdr:row>
+      <xdr:row>95</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>93</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4926,65 +5003,153 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>95</xdr:row>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>99</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>99</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="102" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>95</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>97</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
       <xdr:row>97</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
+        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5012,67 +5177,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>97</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>97</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>99</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>99</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5082,6 +5203,50 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5113,10 +5278,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="102" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066000000}"/>
+        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5144,23 +5309,111 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>97</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>97</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>103</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>103</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="109" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>106</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>106</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="110" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5188,155 +5441,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>99</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>99</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>97</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>97</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>103</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>103</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>103</xdr:row>
+      <xdr:row>106</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>103</xdr:row>
+      <xdr:row>106</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
+        <xdr:cNvPr id="111" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5364,155 +5485,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>103</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>103</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>105</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>105</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="109" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>108</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>108</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="110" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>108</xdr:row>
+      <xdr:row>109</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>108</xdr:row>
+      <xdr:row>109</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="111" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006F000000}"/>
+        <xdr:cNvPr id="112" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000070000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5540,23 +5529,111 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>109</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>109</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="113" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000071000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>111</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>111</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="114" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000072000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>111</xdr:row>
+      <xdr:row>114</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>111</xdr:row>
+      <xdr:row>114</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="112" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000070000000}"/>
+        <xdr:cNvPr id="115" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000073000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5584,76 +5661,120 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>111</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>111</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="113" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000071000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>113</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>113</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="114" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000072000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="116" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000074000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="117" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000075000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>121</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>121</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="118" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000076000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5674,21 +5795,65 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>116</xdr:row>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="119" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000077000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>119</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>116</xdr:row>
+      <xdr:row>119</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="115" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000073000000}"/>
+        <xdr:cNvPr id="120" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000078000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5716,120 +5881,32 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>119</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>119</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="116" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000074000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>121</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>121</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="117" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000075000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>123</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>123</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="118" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000076000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>124</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>124</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="121" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000079000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5850,65 +5927,21 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>119</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>119</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="119" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000077000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>121</xdr:row>
+      <xdr:row>124</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>121</xdr:row>
+      <xdr:row>124</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="120" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000078000000}"/>
+        <xdr:cNvPr id="122" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5936,84 +5969,40 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>126</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>126</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="121" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000079000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>126</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>126</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="122" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="124" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B18C206F-90E1-4F7C-A767-9E7C820C1325}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="6858000"/>
+          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6391,30 +6380,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H130"/>
+  <dimension ref="A1:H128"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -6443,7 +6432,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="18" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="2"/>
@@ -6456,7 +6445,7 @@
       <c r="H4" s="3"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="19"/>
+      <c r="A5" s="18"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
@@ -6468,7 +6457,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -6483,7 +6472,7 @@
       <c r="H6" s="3"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="19"/>
+      <c r="A7" s="18"/>
       <c r="B7" s="3" t="s">
         <v>16</v>
       </c>
@@ -6497,7 +6486,7 @@
       <c r="H7" s="3"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>17</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -6519,7 +6508,7 @@
       <c r="H8" s="3"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="19"/>
+      <c r="A9" s="18"/>
       <c r="B9" s="3" t="s">
         <v>19</v>
       </c>
@@ -6539,7 +6528,7 @@
       <c r="H9" s="3"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="19"/>
+      <c r="A10" s="18"/>
       <c r="B10" s="4" t="s">
         <v>23</v>
       </c>
@@ -6554,7 +6543,7 @@
       <c r="H10" s="3"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="19"/>
+      <c r="A11" s="18"/>
       <c r="B11" s="3" t="s">
         <v>24</v>
       </c>
@@ -6570,7 +6559,7 @@
       <c r="H11" s="3"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="19"/>
+      <c r="A12" s="18"/>
       <c r="B12" s="3"/>
       <c r="C12" s="4" t="s">
         <v>27</v>
@@ -6584,7 +6573,7 @@
       <c r="H12" s="3"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="19"/>
+      <c r="A13" s="18"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3" t="s">
         <v>28</v>
@@ -6598,7 +6587,7 @@
       <c r="H13" s="3"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="19"/>
+      <c r="A14" s="18"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="4" t="s">
@@ -6610,7 +6599,7 @@
       <c r="H14" s="3"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="19"/>
+      <c r="A15" s="18"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3" t="s">
@@ -6622,7 +6611,7 @@
       <c r="H15" s="3"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="19"/>
+      <c r="A16" s="18"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
@@ -6632,7 +6621,7 @@
       <c r="H16" s="5"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="18" t="s">
         <v>31</v>
       </c>
       <c r="B17" s="3"/>
@@ -6645,7 +6634,7 @@
       <c r="H17" s="3"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="19"/>
+      <c r="A18" s="18"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -6657,7 +6646,7 @@
       <c r="H18" s="3"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="19"/>
+      <c r="A19" s="18"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
@@ -6667,7 +6656,7 @@
       <c r="H19" s="5"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="18" t="s">
         <v>33</v>
       </c>
       <c r="B20" s="3"/>
@@ -6682,7 +6671,7 @@
       <c r="H20" s="3"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="19"/>
+      <c r="A21" s="18"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3" t="s">
         <v>16</v>
@@ -6696,7 +6685,7 @@
       <c r="H21" s="3"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="19"/>
+      <c r="A22" s="18"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
@@ -6706,7 +6695,7 @@
       <c r="H22" s="5"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="18" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="4" t="s">
@@ -6725,7 +6714,7 @@
       <c r="H23" s="3"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="19"/>
+      <c r="A24" s="18"/>
       <c r="B24" s="3" t="s">
         <v>35</v>
       </c>
@@ -6743,7 +6732,7 @@
       <c r="H24" s="3"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="19"/>
+      <c r="A25" s="18"/>
       <c r="B25" s="4" t="s">
         <v>15</v>
       </c>
@@ -6757,7 +6746,7 @@
       <c r="H25" s="3"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="19"/>
+      <c r="A26" s="18"/>
       <c r="B26" s="3" t="s">
         <v>32</v>
       </c>
@@ -6771,7 +6760,7 @@
       <c r="H26" s="3"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="19"/>
+      <c r="A27" s="18"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
@@ -6781,7 +6770,7 @@
       <c r="H27" s="5"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="19" t="s">
+      <c r="A28" s="18" t="s">
         <v>40</v>
       </c>
       <c r="B28" s="3"/>
@@ -6798,7 +6787,7 @@
       <c r="H28" s="3"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="19"/>
+      <c r="A29" s="18"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3" t="s">
         <v>41</v>
@@ -6814,7 +6803,7 @@
       <c r="H29" s="3"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="19"/>
+      <c r="A30" s="18"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
@@ -6824,7 +6813,7 @@
       <c r="H30" s="5"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="19" t="s">
+      <c r="A31" s="18" t="s">
         <v>44</v>
       </c>
       <c r="B31" s="4" t="s">
@@ -6846,7 +6835,7 @@
       <c r="H31" s="3"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="19"/>
+      <c r="A32" s="18"/>
       <c r="B32" s="3" t="s">
         <v>46</v>
       </c>
@@ -6866,7 +6855,7 @@
       <c r="H32" s="3"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="19"/>
+      <c r="A33" s="18"/>
       <c r="B33" s="4" t="s">
         <v>50</v>
       </c>
@@ -6883,7 +6872,7 @@
       <c r="H33" s="3"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="19"/>
+      <c r="A34" s="18"/>
       <c r="B34" s="3" t="s">
         <v>52</v>
       </c>
@@ -6901,7 +6890,7 @@
       <c r="H34" s="3"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="19"/>
+      <c r="A35" s="18"/>
       <c r="B35" s="4" t="s">
         <v>45</v>
       </c>
@@ -6917,7 +6906,7 @@
       <c r="H35" s="3"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="19"/>
+      <c r="A36" s="18"/>
       <c r="B36" s="3" t="s">
         <v>56</v>
       </c>
@@ -6933,10 +6922,10 @@
       <c r="H36" s="3"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="19"/>
+      <c r="A37" s="18"/>
       <c r="B37" s="3"/>
-      <c r="C37" s="6" t="s">
-        <v>59</v>
+      <c r="C37" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>45</v>
@@ -6947,10 +6936,10 @@
       <c r="H37" s="3"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="19"/>
+      <c r="A38" s="18"/>
       <c r="B38" s="3"/>
-      <c r="C38" s="4" t="s">
-        <v>15</v>
+      <c r="C38" s="3" t="s">
+        <v>59</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>60</v>
@@ -6961,1124 +6950,1126 @@
       <c r="H38" s="3"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="19"/>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3" t="s">
+      <c r="A39" s="18" t="s">
         <v>61</v>
       </c>
+      <c r="B39" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
+      <c r="F39" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="H39" s="3"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="19"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
+      <c r="A40" s="18"/>
+      <c r="B40" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H40" s="3"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>63</v>
-      </c>
+      <c r="A41" s="18"/>
+      <c r="B41" s="3"/>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
-      <c r="F41" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="G41" s="3"/>
       <c r="H41" s="3"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="19"/>
-      <c r="B42" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3" t="s">
+      <c r="A42" s="18"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H42" s="3"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="19"/>
       <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
+      <c r="C43" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>66</v>
+      </c>
       <c r="G43" s="3"/>
-      <c r="H43" s="3"/>
+      <c r="H43" s="4" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="19"/>
-      <c r="B44" s="5"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="5"/>
-      <c r="H44" s="5"/>
+      <c r="A44" s="18"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="19" t="s">
-        <v>66</v>
-      </c>
+      <c r="A45" s="18"/>
       <c r="B45" s="3"/>
       <c r="C45" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G45" s="3"/>
-      <c r="H45" s="4" t="s">
-        <v>15</v>
-      </c>
+      <c r="H45" s="3"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="19"/>
+      <c r="A46" s="18"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G46" s="3"/>
-      <c r="H46" s="3" t="s">
-        <v>69</v>
-      </c>
+      <c r="H46" s="3"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="19"/>
+      <c r="A47" s="18"/>
       <c r="B47" s="3"/>
-      <c r="C47" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>67</v>
-      </c>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="19"/>
-      <c r="B48" s="3"/>
-      <c r="C48" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F48" s="3" t="s">
+      <c r="A48" s="18"/>
+      <c r="B48" s="5"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="5"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="5"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="G48" s="3"/>
-      <c r="H48" s="3"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="19"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
-      <c r="E49" s="3"/>
+      <c r="E49" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="19"/>
-      <c r="B50" s="5"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="5"/>
-      <c r="H50" s="5"/>
+      <c r="A50" s="18"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="19" t="s">
+      <c r="A51" s="18"/>
+      <c r="B51" s="5"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G51" s="3"/>
-      <c r="H51" s="3"/>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="19"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
-      <c r="E52" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F52" s="3"/>
+      <c r="E52" s="3"/>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="19"/>
-      <c r="B53" s="5"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="5"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="5"/>
-      <c r="G53" s="5"/>
-      <c r="H53" s="5"/>
+      <c r="A53" s="18"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+      <c r="H53" s="3"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="19" t="s">
+      <c r="A54" s="18"/>
+      <c r="B54" s="5"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="5"/>
+      <c r="G54" s="5"/>
+      <c r="H54" s="5"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="B54" s="3"/>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
-      <c r="E54" s="3"/>
-      <c r="G54" s="3"/>
-      <c r="H54" s="3"/>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="19"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
-      <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="19"/>
-      <c r="B56" s="5"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="5"/>
-      <c r="E56" s="5"/>
-      <c r="F56" s="5"/>
-      <c r="G56" s="5"/>
-      <c r="H56" s="5"/>
+      <c r="A56" s="18"/>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+      <c r="H56" s="3"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="19" t="s">
+      <c r="A57" s="18"/>
+      <c r="B57" s="5"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="5"/>
+      <c r="E57" s="5"/>
+      <c r="F57" s="5"/>
+      <c r="G57" s="5"/>
+      <c r="H57" s="5"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="B57" s="3"/>
-      <c r="C57" s="3"/>
-      <c r="D57" s="3"/>
-      <c r="E57" s="3"/>
-      <c r="G57" s="3"/>
-      <c r="H57" s="3"/>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="19"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
-      <c r="F58" s="3"/>
       <c r="G58" s="3"/>
       <c r="H58" s="3"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="19"/>
-      <c r="B59" s="5"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="5"/>
-      <c r="E59" s="5"/>
-      <c r="F59" s="5"/>
-      <c r="G59" s="5"/>
-      <c r="H59" s="5"/>
+      <c r="A59" s="18"/>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
+      <c r="H59" s="3"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="19" t="s">
+      <c r="A60" s="18"/>
+      <c r="B60" s="5"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="5"/>
+      <c r="E60" s="5"/>
+      <c r="F60" s="5"/>
+      <c r="G60" s="5"/>
+      <c r="H60" s="5"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="B60" s="3"/>
-      <c r="C60" s="3"/>
-      <c r="D60" s="3"/>
-      <c r="E60" s="3"/>
-      <c r="G60" s="3"/>
-      <c r="H60" s="3"/>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="19"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
-      <c r="D61" s="3"/>
+      <c r="D61" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="E61" s="3"/>
-      <c r="F61" s="3"/>
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="19"/>
-      <c r="B62" s="5"/>
-      <c r="C62" s="5"/>
-      <c r="D62" s="5"/>
-      <c r="E62" s="5"/>
-      <c r="F62" s="5"/>
-      <c r="G62" s="5"/>
-      <c r="H62" s="5"/>
+      <c r="A62" s="18"/>
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3"/>
+      <c r="H62" s="3"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="B63" s="3"/>
-      <c r="C63" s="3"/>
-      <c r="D63" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E63" s="3"/>
-      <c r="G63" s="3"/>
-      <c r="H63" s="3"/>
+      <c r="A63" s="18"/>
+      <c r="B63" s="5"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="5"/>
+      <c r="F63" s="5"/>
+      <c r="G63" s="5"/>
+      <c r="H63" s="5"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="19"/>
+      <c r="A64" s="18" t="s">
+        <v>77</v>
+      </c>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
-      <c r="D64" s="3" t="s">
-        <v>77</v>
-      </c>
+      <c r="D64" s="3"/>
       <c r="E64" s="3"/>
-      <c r="F64" s="3"/>
+      <c r="F64" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="G64" s="3"/>
       <c r="H64" s="3"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="19"/>
-      <c r="B65" s="5"/>
-      <c r="C65" s="5"/>
-      <c r="D65" s="5"/>
-      <c r="E65" s="5"/>
-      <c r="F65" s="5"/>
-      <c r="G65" s="5"/>
-      <c r="H65" s="5"/>
+      <c r="A65" s="18"/>
+      <c r="B65" s="3"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
+      <c r="E65" s="3"/>
+      <c r="F65" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G65" s="3"/>
+      <c r="H65" s="3"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="19" t="s">
-        <v>78</v>
-      </c>
+      <c r="A66" s="18"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
-      <c r="F66" s="4" t="s">
-        <v>12</v>
-      </c>
       <c r="G66" s="3"/>
       <c r="H66" s="3"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="19"/>
-      <c r="B67" s="3"/>
-      <c r="C67" s="3"/>
-      <c r="D67" s="3"/>
-      <c r="E67" s="3"/>
-      <c r="F67" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G67" s="3"/>
-      <c r="H67" s="3"/>
+      <c r="A67" s="18"/>
+      <c r="B67" s="5"/>
+      <c r="C67" s="5"/>
+      <c r="D67" s="5"/>
+      <c r="E67" s="5"/>
+      <c r="F67" s="5"/>
+      <c r="G67" s="5"/>
+      <c r="H67" s="5"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="19"/>
-      <c r="B68" s="3"/>
-      <c r="C68" s="3"/>
-      <c r="D68" s="3"/>
+      <c r="A68" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="E68" s="3"/>
       <c r="G68" s="3"/>
       <c r="H68" s="3"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="19"/>
-      <c r="B69" s="5"/>
-      <c r="C69" s="5"/>
-      <c r="D69" s="5"/>
-      <c r="E69" s="5"/>
-      <c r="F69" s="5"/>
-      <c r="G69" s="5"/>
-      <c r="H69" s="5"/>
+      <c r="A69" s="18"/>
+      <c r="B69" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3"/>
+      <c r="H69" s="3"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="B70" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D70" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E70" s="3"/>
-      <c r="G70" s="3"/>
-      <c r="H70" s="3"/>
+      <c r="A70" s="18"/>
+      <c r="B70" s="5"/>
+      <c r="C70" s="5"/>
+      <c r="D70" s="5"/>
+      <c r="E70" s="5"/>
+      <c r="F70" s="5"/>
+      <c r="G70" s="5"/>
+      <c r="H70" s="5"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="19"/>
-      <c r="B71" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D71" s="3" t="s">
+      <c r="A71" s="18" t="s">
         <v>80</v>
       </c>
+      <c r="B71" s="3"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="3"/>
       <c r="E71" s="3"/>
-      <c r="F71" s="3"/>
-      <c r="G71" s="3"/>
-      <c r="H71" s="3"/>
+      <c r="G71" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H71" s="4" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="19"/>
-      <c r="B72" s="5"/>
-      <c r="C72" s="5"/>
-      <c r="D72" s="5"/>
-      <c r="E72" s="5"/>
-      <c r="F72" s="5"/>
-      <c r="G72" s="5"/>
-      <c r="H72" s="5"/>
+      <c r="A72" s="18"/>
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="19" t="s">
-        <v>81</v>
-      </c>
+      <c r="A73" s="18"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
+      <c r="F73" s="3"/>
       <c r="G73" s="4" t="s">
-        <v>82</v>
+        <v>15</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>82</v>
+        <v>15</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="19"/>
+      <c r="A74" s="18"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="19"/>
+      <c r="A75" s="18"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
-      <c r="G75" s="4" t="s">
-        <v>15</v>
-      </c>
+      <c r="G75" s="3"/>
       <c r="H75" s="4" t="s">
-        <v>15</v>
+        <v>81</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="19"/>
+      <c r="A76" s="18"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
-      <c r="G76" s="3" t="s">
-        <v>85</v>
-      </c>
+      <c r="G76" s="3"/>
       <c r="H76" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="18"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
+      <c r="D77" s="5"/>
+      <c r="E77" s="5"/>
+      <c r="F77" s="5"/>
+      <c r="G77" s="5"/>
+      <c r="H77" s="5"/>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="18" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="19"/>
-      <c r="B77" s="3"/>
-      <c r="C77" s="3"/>
-      <c r="D77" s="3"/>
-      <c r="E77" s="3"/>
-      <c r="F77" s="3"/>
-      <c r="G77" s="3"/>
-      <c r="H77" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="19"/>
-      <c r="B78" s="3"/>
-      <c r="C78" s="3"/>
-      <c r="D78" s="3"/>
-      <c r="E78" s="3"/>
-      <c r="F78" s="3"/>
-      <c r="G78" s="3"/>
-      <c r="H78" s="3" t="s">
-        <v>70</v>
+      <c r="B78" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G78" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="H78" s="6" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="19"/>
-      <c r="B79" s="5"/>
-      <c r="C79" s="5"/>
-      <c r="D79" s="5"/>
-      <c r="E79" s="5"/>
-      <c r="F79" s="5"/>
-      <c r="G79" s="5"/>
-      <c r="H79" s="5"/>
+      <c r="A79" s="18"/>
+      <c r="B79" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E79" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="F79" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="G79" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H79" s="7" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="19" t="s">
-        <v>87</v>
-      </c>
+      <c r="A80" s="18"/>
       <c r="B80" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G80" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H80" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="19"/>
-      <c r="B81" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="C81" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="D81" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="E81" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="F81" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="G81" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="H81" s="8" t="s">
-        <v>89</v>
-      </c>
+      <c r="A81" s="18"/>
+      <c r="B81" s="7"/>
+      <c r="C81" s="7"/>
+      <c r="D81" s="7"/>
+      <c r="E81" s="7"/>
+      <c r="G81" s="7"/>
+      <c r="H81" s="7"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="19"/>
-      <c r="B82" s="8" t="s">
+      <c r="A82" s="18"/>
+      <c r="B82" s="5"/>
+      <c r="C82" s="5"/>
+      <c r="D82" s="5"/>
+      <c r="E82" s="5"/>
+      <c r="F82" s="5"/>
+      <c r="G82" s="5"/>
+      <c r="H82" s="5"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="C82" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="D82" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="E82" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="F82" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="G82" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="H82" s="8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="19"/>
-      <c r="B83" s="8"/>
-      <c r="C83" s="8"/>
-      <c r="D83" s="8"/>
-      <c r="E83" s="8"/>
-      <c r="G83" s="8"/>
-      <c r="H83" s="8"/>
+      <c r="B83" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E83" s="3"/>
+      <c r="F83" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H83" s="3"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="19"/>
-      <c r="B84" s="5"/>
-      <c r="C84" s="5"/>
-      <c r="D84" s="5"/>
-      <c r="E84" s="5"/>
-      <c r="F84" s="5"/>
-      <c r="G84" s="5"/>
-      <c r="H84" s="5"/>
+      <c r="A84" s="18"/>
+      <c r="B84" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="H84" s="3"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>63</v>
-      </c>
+      <c r="A85" s="18"/>
+      <c r="B85" s="3"/>
       <c r="C85" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E85" s="3"/>
+      <c r="G85" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="H85" s="3"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" s="18"/>
+      <c r="B86" s="3"/>
+      <c r="C86" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3"/>
+      <c r="G86" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H86" s="3"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="18"/>
+      <c r="B87" s="3"/>
+      <c r="C87" s="3"/>
+      <c r="D87" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D85" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E85" s="3"/>
-      <c r="F85" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="G85" s="4" t="s">
+      <c r="E87" s="3"/>
+      <c r="F87" s="3"/>
+      <c r="G87" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H85" s="3"/>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="19"/>
-      <c r="B86" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E86" s="3"/>
-      <c r="F86" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G86" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="H86" s="3"/>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="19"/>
-      <c r="B87" s="3"/>
-      <c r="C87" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D87" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E87" s="3"/>
-      <c r="G87" s="4" t="s">
-        <v>95</v>
-      </c>
       <c r="H87" s="3"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="19"/>
+      <c r="A88" s="18"/>
       <c r="B88" s="3"/>
-      <c r="C88" s="3" t="s">
-        <v>77</v>
-      </c>
+      <c r="C88" s="3"/>
       <c r="D88" s="3" t="s">
         <v>96</v>
       </c>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="H88" s="3"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="19"/>
+      <c r="A89" s="18"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
       <c r="D89" s="4" t="s">
-        <v>12</v>
+        <v>94</v>
       </c>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
       <c r="G89" s="4" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="H89" s="3"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="19"/>
+      <c r="A90" s="18"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
       <c r="D90" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H90" s="3"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="19"/>
-      <c r="B91" s="3"/>
-      <c r="C91" s="3"/>
-      <c r="D91" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E91" s="3"/>
-      <c r="F91" s="3"/>
-      <c r="G91" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="H91" s="3"/>
+      <c r="A91" s="18"/>
+      <c r="B91" s="5"/>
+      <c r="C91" s="5"/>
+      <c r="D91" s="5"/>
+      <c r="E91" s="5"/>
+      <c r="F91" s="5"/>
+      <c r="G91" s="5"/>
+      <c r="H91" s="5"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="19"/>
-      <c r="B92" s="3"/>
-      <c r="C92" s="3"/>
-      <c r="D92" s="3" t="s">
-        <v>99</v>
-      </c>
+      <c r="A92" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D92" s="3"/>
       <c r="E92" s="3"/>
-      <c r="F92" s="3"/>
-      <c r="G92" s="3" t="s">
-        <v>100</v>
-      </c>
+      <c r="F92" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G92" s="3"/>
       <c r="H92" s="3"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="19"/>
-      <c r="B93" s="5"/>
-      <c r="C93" s="5"/>
-      <c r="D93" s="5"/>
-      <c r="E93" s="5"/>
-      <c r="F93" s="5"/>
-      <c r="G93" s="5"/>
-      <c r="H93" s="5"/>
+      <c r="A93" s="18"/>
+      <c r="B93" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D93" s="3"/>
+      <c r="E93" s="3"/>
+      <c r="F93" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G93" s="3"/>
+      <c r="H93" s="3"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="B94" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="A94" s="18"/>
+      <c r="B94" s="3"/>
+      <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
-      <c r="F94" s="4" t="s">
-        <v>12</v>
-      </c>
       <c r="G94" s="3"/>
       <c r="H94" s="3"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="19"/>
-      <c r="B95" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D95" s="3"/>
-      <c r="E95" s="3"/>
-      <c r="F95" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G95" s="3"/>
-      <c r="H95" s="3"/>
+      <c r="A95" s="18"/>
+      <c r="B95" s="5"/>
+      <c r="C95" s="5"/>
+      <c r="D95" s="5"/>
+      <c r="E95" s="5"/>
+      <c r="F95" s="5"/>
+      <c r="G95" s="5"/>
+      <c r="H95" s="5"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A96" s="19"/>
+      <c r="A96" s="18" t="s">
+        <v>101</v>
+      </c>
       <c r="B96" s="3"/>
-      <c r="C96" s="3"/>
+      <c r="C96" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="D96" s="3"/>
-      <c r="E96" s="3"/>
-      <c r="G96" s="3"/>
-      <c r="H96" s="3"/>
+      <c r="E96" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G96" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="H96" s="4" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="19"/>
-      <c r="B97" s="5"/>
-      <c r="C97" s="5"/>
-      <c r="D97" s="5"/>
-      <c r="E97" s="5"/>
-      <c r="F97" s="5"/>
-      <c r="G97" s="5"/>
-      <c r="H97" s="5"/>
+      <c r="A97" s="18"/>
+      <c r="B97" s="3"/>
+      <c r="C97" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D97" s="3"/>
+      <c r="E97" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A98" s="19" t="s">
-        <v>102</v>
-      </c>
+      <c r="A98" s="18"/>
       <c r="B98" s="3"/>
-      <c r="C98" s="4" t="s">
-        <v>18</v>
-      </c>
+      <c r="C98" s="3"/>
       <c r="D98" s="3"/>
-      <c r="E98" s="4" t="s">
+      <c r="E98" s="3"/>
+      <c r="F98" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F98" s="4" t="s">
-        <v>50</v>
-      </c>
       <c r="G98" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="H98" s="4" t="s">
         <v>15</v>
       </c>
+      <c r="H98" s="3"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" s="19"/>
+      <c r="A99" s="18"/>
       <c r="B99" s="3"/>
-      <c r="C99" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="C99" s="3"/>
       <c r="D99" s="3"/>
-      <c r="E99" s="3" t="s">
-        <v>104</v>
-      </c>
+      <c r="E99" s="3"/>
       <c r="F99" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="H99" s="3" t="s">
-        <v>107</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="H99" s="3"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" s="19"/>
+      <c r="A100" s="18"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
-      <c r="F100" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G100" s="4" t="s">
-        <v>15</v>
-      </c>
+      <c r="G100" s="3"/>
       <c r="H100" s="3"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101" s="19"/>
-      <c r="B101" s="3"/>
-      <c r="C101" s="3"/>
-      <c r="D101" s="3"/>
-      <c r="E101" s="3"/>
-      <c r="F101" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="G101" s="3" t="s">
+      <c r="A101" s="18"/>
+      <c r="B101" s="5"/>
+      <c r="C101" s="5"/>
+      <c r="D101" s="5"/>
+      <c r="E101" s="5"/>
+      <c r="F101" s="5"/>
+      <c r="G101" s="5"/>
+      <c r="H101" s="5"/>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="H101" s="3"/>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A102" s="19"/>
-      <c r="B102" s="3"/>
+      <c r="B102" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
       <c r="G102" s="3"/>
-      <c r="H102" s="3"/>
+      <c r="H102" s="4" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A103" s="19"/>
-      <c r="B103" s="5"/>
-      <c r="C103" s="5"/>
-      <c r="D103" s="5"/>
-      <c r="E103" s="5"/>
-      <c r="F103" s="5"/>
-      <c r="G103" s="5"/>
-      <c r="H103" s="5"/>
+      <c r="A103" s="18"/>
+      <c r="B103" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C103" s="3"/>
+      <c r="D103" s="3"/>
+      <c r="E103" s="3"/>
+      <c r="F103" s="3"/>
+      <c r="G103" s="3"/>
+      <c r="H103" s="3" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A104" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="B104" s="4" t="s">
-        <v>27</v>
-      </c>
+      <c r="A104" s="18"/>
+      <c r="B104" s="3"/>
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
       <c r="E104" s="3"/>
+      <c r="F104" s="3"/>
       <c r="G104" s="3"/>
       <c r="H104" s="4" t="s">
-        <v>82</v>
+        <v>15</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A105" s="19"/>
-      <c r="B105" s="3" t="s">
-        <v>77</v>
-      </c>
+      <c r="A105" s="18"/>
+      <c r="B105" s="3"/>
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
       <c r="E105" s="3"/>
       <c r="F105" s="3"/>
       <c r="G105" s="3"/>
       <c r="H105" s="3" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A106" s="19"/>
-      <c r="B106" s="3"/>
-      <c r="C106" s="3"/>
-      <c r="D106" s="3"/>
-      <c r="E106" s="3"/>
-      <c r="F106" s="3"/>
-      <c r="G106" s="3"/>
-      <c r="H106" s="4" t="s">
-        <v>15</v>
-      </c>
+      <c r="A106" s="18"/>
+      <c r="B106" s="5"/>
+      <c r="C106" s="5"/>
+      <c r="D106" s="5"/>
+      <c r="E106" s="5"/>
+      <c r="F106" s="5"/>
+      <c r="G106" s="5"/>
+      <c r="H106" s="5"/>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A107" s="19"/>
+      <c r="A107" s="18" t="s">
+        <v>111</v>
+      </c>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
-      <c r="D107" s="3"/>
+      <c r="D107" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="E107" s="3"/>
-      <c r="F107" s="3"/>
       <c r="G107" s="3"/>
-      <c r="H107" s="3" t="s">
-        <v>111</v>
-      </c>
+      <c r="H107" s="3"/>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A108" s="19"/>
-      <c r="B108" s="5"/>
-      <c r="C108" s="5"/>
-      <c r="D108" s="5"/>
-      <c r="E108" s="5"/>
-      <c r="F108" s="5"/>
-      <c r="G108" s="5"/>
-      <c r="H108" s="5"/>
+      <c r="A108" s="18"/>
+      <c r="B108" s="3"/>
+      <c r="C108" s="3"/>
+      <c r="D108" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E108" s="3"/>
+      <c r="F108" s="3"/>
+      <c r="G108" s="3"/>
+      <c r="H108" s="3"/>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A109" s="19" t="s">
+      <c r="A109" s="18"/>
+      <c r="B109" s="5"/>
+      <c r="C109" s="5"/>
+      <c r="D109" s="5"/>
+      <c r="E109" s="5"/>
+      <c r="F109" s="5"/>
+      <c r="G109" s="5"/>
+      <c r="H109" s="5"/>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="B109" s="3"/>
-      <c r="C109" s="3"/>
-      <c r="D109" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E109" s="3"/>
-      <c r="G109" s="3"/>
-      <c r="H109" s="3"/>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A110" s="19"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
-      <c r="D110" s="3" t="s">
-        <v>83</v>
-      </c>
+      <c r="D110" s="3"/>
       <c r="E110" s="3"/>
-      <c r="F110" s="3"/>
-      <c r="G110" s="3"/>
+      <c r="G110" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="H110" s="3"/>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A111" s="19"/>
-      <c r="B111" s="5"/>
-      <c r="C111" s="5"/>
-      <c r="D111" s="5"/>
-      <c r="E111" s="5"/>
-      <c r="F111" s="5"/>
-      <c r="G111" s="5"/>
-      <c r="H111" s="5"/>
+      <c r="A111" s="18"/>
+      <c r="B111" s="3"/>
+      <c r="C111" s="3"/>
+      <c r="D111" s="3"/>
+      <c r="E111" s="3"/>
+      <c r="F111" s="3"/>
+      <c r="G111" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H111" s="3"/>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A112" s="19" t="s">
-        <v>113</v>
-      </c>
+      <c r="A112" s="18"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
+      <c r="F112" s="3"/>
       <c r="G112" s="4" t="s">
         <v>12</v>
       </c>
       <c r="H112" s="3"/>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A113" s="19"/>
+      <c r="A113" s="18"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
       <c r="E113" s="3"/>
       <c r="F113" s="3"/>
       <c r="G113" s="3" t="s">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="H113" s="3"/>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A114" s="19"/>
-      <c r="B114" s="3"/>
-      <c r="C114" s="3"/>
-      <c r="D114" s="3"/>
-      <c r="E114" s="3"/>
-      <c r="F114" s="3"/>
-      <c r="G114" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H114" s="3"/>
+      <c r="A114" s="18"/>
+      <c r="B114" s="5"/>
+      <c r="C114" s="5"/>
+      <c r="D114" s="5"/>
+      <c r="E114" s="5"/>
+      <c r="F114" s="5"/>
+      <c r="G114" s="5"/>
+      <c r="H114" s="5"/>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A115" s="19"/>
+      <c r="A115" s="18" t="s">
+        <v>114</v>
+      </c>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
       <c r="E115" s="3"/>
-      <c r="F115" s="3"/>
-      <c r="G115" s="3" t="s">
-        <v>114</v>
-      </c>
+      <c r="G115" s="3"/>
       <c r="H115" s="3"/>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A116" s="19"/>
-      <c r="B116" s="5"/>
-      <c r="C116" s="5"/>
-      <c r="D116" s="5"/>
-      <c r="E116" s="5"/>
-      <c r="F116" s="5"/>
-      <c r="G116" s="5"/>
-      <c r="H116" s="5"/>
+      <c r="A116" s="18"/>
+      <c r="B116" s="3"/>
+      <c r="C116" s="3"/>
+      <c r="D116" s="3"/>
+      <c r="E116" s="3"/>
+      <c r="F116" s="3"/>
+      <c r="G116" s="3"/>
+      <c r="H116" s="3"/>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A117" s="19" t="s">
+      <c r="A117" s="18"/>
+      <c r="B117" s="5"/>
+      <c r="C117" s="5"/>
+      <c r="D117" s="5"/>
+      <c r="E117" s="5"/>
+      <c r="F117" s="5"/>
+      <c r="G117" s="5"/>
+      <c r="H117" s="5"/>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="B117" s="3"/>
-      <c r="C117" s="3"/>
-      <c r="D117" s="3"/>
-      <c r="E117" s="3"/>
-      <c r="G117" s="3"/>
-      <c r="H117" s="3"/>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A118" s="19"/>
-      <c r="B118" s="3"/>
+      <c r="B118" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
       <c r="E118" s="3"/>
-      <c r="F118" s="3"/>
+      <c r="F118" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="G118" s="3"/>
       <c r="H118" s="3"/>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A119" s="19"/>
-      <c r="B119" s="5"/>
-      <c r="C119" s="5"/>
-      <c r="D119" s="5"/>
-      <c r="E119" s="5"/>
-      <c r="F119" s="5"/>
-      <c r="G119" s="5"/>
-      <c r="H119" s="5"/>
+      <c r="A119" s="18"/>
+      <c r="B119" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C119" s="3"/>
+      <c r="D119" s="3"/>
+      <c r="E119" s="3"/>
+      <c r="F119" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G119" s="3"/>
+      <c r="H119" s="3"/>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A120" s="19" t="s">
-        <v>116</v>
-      </c>
+      <c r="A120" s="18"/>
       <c r="B120" s="4" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
-      <c r="F120" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="G120" s="3"/>
       <c r="H120" s="3"/>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A121" s="19"/>
+      <c r="A121" s="18"/>
       <c r="B121" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
       <c r="E121" s="3"/>
-      <c r="F121" s="3" t="s">
-        <v>118</v>
-      </c>
+      <c r="F121" s="3"/>
       <c r="G121" s="3"/>
       <c r="H121" s="3"/>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A122" s="19"/>
+      <c r="A122" s="18"/>
       <c r="B122" s="4" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
+      <c r="F122" s="3"/>
       <c r="G122" s="3"/>
       <c r="H122" s="3"/>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A123" s="19"/>
+      <c r="A123" s="18"/>
       <c r="B123" s="3" t="s">
         <v>119</v>
       </c>
@@ -8090,111 +8081,87 @@
       <c r="H123" s="3"/>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A124" s="19"/>
-      <c r="B124" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C124" s="3"/>
-      <c r="D124" s="3"/>
-      <c r="E124" s="3"/>
-      <c r="F124" s="3"/>
-      <c r="G124" s="3"/>
-      <c r="H124" s="3"/>
+      <c r="A124" s="18"/>
+      <c r="B124" s="5"/>
+      <c r="C124" s="5"/>
+      <c r="D124" s="5"/>
+      <c r="E124" s="5"/>
+      <c r="F124" s="5"/>
+      <c r="G124" s="5"/>
+      <c r="H124" s="5"/>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A125" s="19"/>
-      <c r="B125" s="3" t="s">
+      <c r="A125" s="18" t="s">
         <v>120</v>
       </c>
+      <c r="B125" s="3"/>
       <c r="C125" s="3"/>
-      <c r="D125" s="3"/>
+      <c r="D125" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="E125" s="3"/>
-      <c r="F125" s="3"/>
       <c r="G125" s="3"/>
       <c r="H125" s="3"/>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A126" s="19"/>
-      <c r="B126" s="5"/>
-      <c r="C126" s="5"/>
-      <c r="D126" s="5"/>
-      <c r="E126" s="5"/>
-      <c r="F126" s="5"/>
-      <c r="G126" s="5"/>
-      <c r="H126" s="5"/>
+      <c r="A126" s="18"/>
+      <c r="B126" s="3"/>
+      <c r="C126" s="3"/>
+      <c r="D126" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E126" s="3"/>
+      <c r="F126" s="3"/>
+      <c r="G126" s="3"/>
+      <c r="H126" s="3"/>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A127" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="B127" s="3"/>
-      <c r="C127" s="3"/>
-      <c r="D127" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E127" s="3"/>
-      <c r="G127" s="3"/>
-      <c r="H127" s="3"/>
+      <c r="A127" s="18"/>
+      <c r="B127" s="5"/>
+      <c r="C127" s="5"/>
+      <c r="D127" s="5"/>
+      <c r="E127" s="5"/>
+      <c r="F127" s="5"/>
+      <c r="G127" s="5"/>
+      <c r="H127" s="5"/>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A128" s="19"/>
-      <c r="B128" s="3"/>
-      <c r="C128" s="3"/>
-      <c r="D128" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E128" s="3"/>
-      <c r="F128" s="3"/>
-      <c r="G128" s="3"/>
-      <c r="H128" s="3"/>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A129" s="19"/>
-      <c r="B129" s="5"/>
-      <c r="C129" s="5"/>
-      <c r="D129" s="5"/>
-      <c r="E129" s="5"/>
-      <c r="F129" s="5"/>
-      <c r="G129" s="5"/>
-      <c r="H129" s="5"/>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B130" s="20"/>
-      <c r="C130" s="20"/>
-      <c r="D130" s="20"/>
-      <c r="E130" s="20"/>
-      <c r="F130" s="20"/>
-      <c r="G130" s="20"/>
-      <c r="H130" s="20"/>
+      <c r="B128" s="19"/>
+      <c r="C128" s="19"/>
+      <c r="D128" s="19"/>
+      <c r="E128" s="19"/>
+      <c r="F128" s="19"/>
+      <c r="G128" s="19"/>
+      <c r="H128" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="B130:H130"/>
-    <mergeCell ref="A109:A111"/>
-    <mergeCell ref="A112:A116"/>
-    <mergeCell ref="A117:A119"/>
-    <mergeCell ref="A120:A126"/>
-    <mergeCell ref="A127:A129"/>
-    <mergeCell ref="A80:A84"/>
-    <mergeCell ref="A85:A93"/>
-    <mergeCell ref="A94:A97"/>
-    <mergeCell ref="A98:A103"/>
-    <mergeCell ref="A104:A108"/>
-    <mergeCell ref="A60:A62"/>
-    <mergeCell ref="A63:A65"/>
-    <mergeCell ref="A66:A69"/>
-    <mergeCell ref="A70:A72"/>
-    <mergeCell ref="A73:A79"/>
-    <mergeCell ref="A41:A44"/>
-    <mergeCell ref="A45:A50"/>
-    <mergeCell ref="A51:A53"/>
-    <mergeCell ref="A54:A56"/>
-    <mergeCell ref="A57:A59"/>
+    <mergeCell ref="B128:H128"/>
+    <mergeCell ref="A107:A109"/>
+    <mergeCell ref="A110:A114"/>
+    <mergeCell ref="A115:A117"/>
+    <mergeCell ref="A118:A124"/>
+    <mergeCell ref="A125:A127"/>
+    <mergeCell ref="A78:A82"/>
+    <mergeCell ref="A83:A91"/>
+    <mergeCell ref="A92:A95"/>
+    <mergeCell ref="A96:A101"/>
+    <mergeCell ref="A102:A106"/>
+    <mergeCell ref="A58:A60"/>
+    <mergeCell ref="A61:A63"/>
+    <mergeCell ref="A64:A67"/>
+    <mergeCell ref="A68:A70"/>
+    <mergeCell ref="A71:A77"/>
+    <mergeCell ref="A39:A42"/>
+    <mergeCell ref="A43:A48"/>
+    <mergeCell ref="A49:A51"/>
+    <mergeCell ref="A52:A54"/>
+    <mergeCell ref="A55:A57"/>
     <mergeCell ref="A17:A19"/>
     <mergeCell ref="A20:A22"/>
     <mergeCell ref="A23:A27"/>
     <mergeCell ref="A28:A30"/>
-    <mergeCell ref="A31:A40"/>
+    <mergeCell ref="A31:A38"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="A4:A5"/>
@@ -8212,530 +8179,530 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="22" t="s">
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="12" t="s">
+      <c r="C6" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="D6" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="E6" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="E6" s="12" t="s">
-        <v>127</v>
-      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="13">
-        <v>0</v>
-      </c>
-      <c r="C7" s="13">
-        <v>0</v>
-      </c>
-      <c r="D7" s="13">
-        <v>0</v>
-      </c>
-      <c r="E7" s="13">
+      <c r="B7" s="12">
+        <v>0</v>
+      </c>
+      <c r="C7" s="12">
+        <v>0</v>
+      </c>
+      <c r="D7" s="12">
+        <v>0</v>
+      </c>
+      <c r="E7" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="13">
-        <v>0</v>
-      </c>
-      <c r="C8" s="13">
-        <v>0</v>
-      </c>
-      <c r="D8" s="13">
-        <v>0</v>
-      </c>
-      <c r="E8" s="13">
+      <c r="B8" s="12">
+        <v>0</v>
+      </c>
+      <c r="C8" s="12">
+        <v>0</v>
+      </c>
+      <c r="D8" s="12">
+        <v>0</v>
+      </c>
+      <c r="E8" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="13">
-        <v>0</v>
-      </c>
-      <c r="C9" s="13">
+      <c r="B9" s="12">
+        <v>0</v>
+      </c>
+      <c r="C9" s="12">
         <v>4.1667000000000003E-2</v>
       </c>
-      <c r="D9" s="13">
-        <v>0</v>
-      </c>
-      <c r="E9" s="13">
+      <c r="D9" s="12">
+        <v>0</v>
+      </c>
+      <c r="E9" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="13">
-        <v>0</v>
-      </c>
-      <c r="C10" s="13">
-        <v>0</v>
-      </c>
-      <c r="D10" s="13">
-        <v>0</v>
-      </c>
-      <c r="E10" s="13">
+      <c r="B10" s="12">
+        <v>0</v>
+      </c>
+      <c r="C10" s="12">
+        <v>0</v>
+      </c>
+      <c r="D10" s="12">
+        <v>0</v>
+      </c>
+      <c r="E10" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="13">
-        <v>0</v>
-      </c>
-      <c r="C11" s="13">
-        <v>0</v>
-      </c>
-      <c r="D11" s="13">
-        <v>0</v>
-      </c>
-      <c r="E11" s="13">
+      <c r="B11" s="12">
+        <v>0</v>
+      </c>
+      <c r="C11" s="12">
+        <v>0</v>
+      </c>
+      <c r="D11" s="12">
+        <v>0</v>
+      </c>
+      <c r="E11" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="13">
-        <v>0</v>
-      </c>
-      <c r="C12" s="13">
-        <v>0</v>
-      </c>
-      <c r="D12" s="13">
-        <v>0</v>
-      </c>
-      <c r="E12" s="13">
+      <c r="B12" s="12">
+        <v>0</v>
+      </c>
+      <c r="C12" s="12">
+        <v>0</v>
+      </c>
+      <c r="D12" s="12">
+        <v>0</v>
+      </c>
+      <c r="E12" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="13">
-        <v>0</v>
-      </c>
-      <c r="C13" s="13">
-        <v>0</v>
-      </c>
-      <c r="D13" s="13">
-        <v>0</v>
-      </c>
-      <c r="E13" s="13">
+      <c r="B13" s="12">
+        <v>0</v>
+      </c>
+      <c r="C13" s="12">
+        <v>0</v>
+      </c>
+      <c r="D13" s="12">
+        <v>0</v>
+      </c>
+      <c r="E13" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="13">
-        <v>0</v>
-      </c>
-      <c r="C14" s="13">
-        <v>0</v>
-      </c>
-      <c r="D14" s="13">
-        <v>0</v>
-      </c>
-      <c r="E14" s="13">
+      <c r="B14" s="12">
+        <v>0</v>
+      </c>
+      <c r="C14" s="12">
+        <v>0</v>
+      </c>
+      <c r="D14" s="12">
+        <v>0</v>
+      </c>
+      <c r="E14" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="B15" s="13">
-        <v>0</v>
-      </c>
-      <c r="C15" s="13">
-        <v>0</v>
-      </c>
-      <c r="D15" s="13">
-        <v>0</v>
-      </c>
-      <c r="E15" s="13">
+      <c r="A15" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="12">
+        <v>0</v>
+      </c>
+      <c r="C15" s="12">
+        <v>0</v>
+      </c>
+      <c r="D15" s="12">
+        <v>0</v>
+      </c>
+      <c r="E15" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="B16" s="13">
-        <v>0</v>
-      </c>
-      <c r="C16" s="13">
-        <v>0</v>
-      </c>
-      <c r="D16" s="13">
-        <v>0</v>
-      </c>
-      <c r="E16" s="13">
+      <c r="A16" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" s="12">
+        <v>0</v>
+      </c>
+      <c r="C16" s="12">
+        <v>0</v>
+      </c>
+      <c r="D16" s="12">
+        <v>0</v>
+      </c>
+      <c r="E16" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="B17" s="12">
+        <v>0</v>
+      </c>
+      <c r="C17" s="12">
+        <v>0</v>
+      </c>
+      <c r="D17" s="12">
+        <v>0</v>
+      </c>
+      <c r="E17" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="B17" s="13">
-        <v>0</v>
-      </c>
-      <c r="C17" s="13">
-        <v>0</v>
-      </c>
-      <c r="D17" s="13">
-        <v>0</v>
-      </c>
-      <c r="E17" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="11" t="s">
+      <c r="B18" s="12">
+        <v>0</v>
+      </c>
+      <c r="C18" s="12">
+        <v>0</v>
+      </c>
+      <c r="D18" s="12">
+        <v>0</v>
+      </c>
+      <c r="E18" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B18" s="13">
-        <v>0</v>
-      </c>
-      <c r="C18" s="13">
-        <v>0</v>
-      </c>
-      <c r="D18" s="13">
-        <v>0</v>
-      </c>
-      <c r="E18" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
+      <c r="B19" s="12">
+        <v>0</v>
+      </c>
+      <c r="C19" s="12">
+        <v>0</v>
+      </c>
+      <c r="D19" s="12">
+        <v>0</v>
+      </c>
+      <c r="E19" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="B19" s="13">
-        <v>0</v>
-      </c>
-      <c r="C19" s="13">
-        <v>0</v>
-      </c>
-      <c r="D19" s="13">
-        <v>0</v>
-      </c>
-      <c r="E19" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
+      <c r="B20" s="12">
+        <v>0</v>
+      </c>
+      <c r="C20" s="12">
+        <v>0</v>
+      </c>
+      <c r="D20" s="12">
+        <v>0</v>
+      </c>
+      <c r="E20" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B20" s="13">
-        <v>0</v>
-      </c>
-      <c r="C20" s="13">
-        <v>0</v>
-      </c>
-      <c r="D20" s="13">
-        <v>0</v>
-      </c>
-      <c r="E20" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="B21" s="13">
-        <v>0</v>
-      </c>
-      <c r="C21" s="13">
+      <c r="B21" s="12">
+        <v>0</v>
+      </c>
+      <c r="C21" s="12">
         <v>0.125</v>
       </c>
-      <c r="D21" s="13">
-        <v>0</v>
-      </c>
-      <c r="E21" s="13">
+      <c r="D21" s="12">
+        <v>0</v>
+      </c>
+      <c r="E21" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B22" s="12">
+        <v>0</v>
+      </c>
+      <c r="C22" s="12">
+        <v>0</v>
+      </c>
+      <c r="D22" s="12">
+        <v>0</v>
+      </c>
+      <c r="E22" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="B22" s="13">
-        <v>0</v>
-      </c>
-      <c r="C22" s="13">
-        <v>0</v>
-      </c>
-      <c r="D22" s="13">
-        <v>0</v>
-      </c>
-      <c r="E22" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="B23" s="13">
-        <v>0</v>
-      </c>
-      <c r="C23" s="13">
+      <c r="B23" s="12">
+        <v>0</v>
+      </c>
+      <c r="C23" s="12">
         <v>0.33333400000000002</v>
       </c>
-      <c r="D23" s="13">
-        <v>0</v>
-      </c>
-      <c r="E23" s="13">
+      <c r="D23" s="12">
+        <v>0</v>
+      </c>
+      <c r="E23" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="B24" s="13">
-        <v>0</v>
-      </c>
-      <c r="C24" s="13">
-        <v>0</v>
-      </c>
-      <c r="D24" s="13">
+      <c r="A24" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" s="12">
+        <v>0</v>
+      </c>
+      <c r="C24" s="12">
+        <v>0</v>
+      </c>
+      <c r="D24" s="12">
         <v>0.409028</v>
       </c>
-      <c r="E24" s="13">
+      <c r="E24" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="B25" s="13">
-        <v>0</v>
-      </c>
-      <c r="C25" s="13">
-        <v>0</v>
-      </c>
-      <c r="D25" s="13">
-        <v>0</v>
-      </c>
-      <c r="E25" s="13">
+      <c r="A25" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B25" s="12">
+        <v>0</v>
+      </c>
+      <c r="C25" s="12">
+        <v>0</v>
+      </c>
+      <c r="D25" s="12">
+        <v>0</v>
+      </c>
+      <c r="E25" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="B26" s="13">
-        <v>0</v>
-      </c>
-      <c r="C26" s="13">
+      <c r="A26" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B26" s="12">
+        <v>0</v>
+      </c>
+      <c r="C26" s="12">
         <v>0.125</v>
       </c>
-      <c r="D26" s="13">
+      <c r="D26" s="12">
         <v>8.3334000000000005E-2</v>
       </c>
-      <c r="E26" s="13">
+      <c r="E26" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="B27" s="12">
+        <v>0</v>
+      </c>
+      <c r="C27" s="12">
+        <v>0</v>
+      </c>
+      <c r="D27" s="12">
+        <v>0</v>
+      </c>
+      <c r="E27" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="B27" s="13">
-        <v>0</v>
-      </c>
-      <c r="C27" s="13">
-        <v>0</v>
-      </c>
-      <c r="D27" s="13">
-        <v>0</v>
-      </c>
-      <c r="E27" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="B28" s="13">
-        <v>0</v>
-      </c>
-      <c r="C28" s="13">
-        <v>0</v>
-      </c>
-      <c r="D28" s="13">
-        <v>0</v>
-      </c>
-      <c r="E28" s="13">
+      <c r="B28" s="12">
+        <v>0</v>
+      </c>
+      <c r="C28" s="12">
+        <v>0</v>
+      </c>
+      <c r="D28" s="12">
+        <v>0</v>
+      </c>
+      <c r="E28" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="B29" s="13">
-        <v>0</v>
-      </c>
-      <c r="C29" s="13">
+      <c r="A29" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B29" s="12">
+        <v>0</v>
+      </c>
+      <c r="C29" s="12">
         <v>0.125</v>
       </c>
-      <c r="D29" s="13">
+      <c r="D29" s="12">
         <v>0.160417</v>
       </c>
-      <c r="E29" s="13">
+      <c r="E29" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="11" t="s">
+      <c r="A30" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="B30" s="12">
+        <v>0</v>
+      </c>
+      <c r="C30" s="12">
+        <v>0</v>
+      </c>
+      <c r="D30" s="12">
+        <v>0</v>
+      </c>
+      <c r="E30" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="B30" s="13">
-        <v>0</v>
-      </c>
-      <c r="C30" s="13">
-        <v>0</v>
-      </c>
-      <c r="D30" s="13">
-        <v>0</v>
-      </c>
-      <c r="E30" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="B31" s="13">
-        <v>0</v>
-      </c>
-      <c r="C31" s="13">
-        <v>0</v>
-      </c>
-      <c r="D31" s="13">
-        <v>0</v>
-      </c>
-      <c r="E31" s="13">
+      <c r="B31" s="12">
+        <v>0</v>
+      </c>
+      <c r="C31" s="12">
+        <v>0</v>
+      </c>
+      <c r="D31" s="12">
+        <v>0</v>
+      </c>
+      <c r="E31" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="11" t="s">
+      <c r="A32" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="B32" s="12">
+        <v>0</v>
+      </c>
+      <c r="C32" s="12">
+        <v>0</v>
+      </c>
+      <c r="D32" s="12">
+        <v>0</v>
+      </c>
+      <c r="E32" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="B32" s="13">
-        <v>0</v>
-      </c>
-      <c r="C32" s="13">
-        <v>0</v>
-      </c>
-      <c r="D32" s="13">
-        <v>0</v>
-      </c>
-      <c r="E32" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="B33" s="13">
-        <v>0</v>
-      </c>
-      <c r="C33" s="13">
+      <c r="B33" s="12">
+        <v>0</v>
+      </c>
+      <c r="C33" s="12">
         <v>3.9584000000000001E-2</v>
       </c>
-      <c r="D33" s="13">
-        <v>0</v>
-      </c>
-      <c r="E33" s="13">
+      <c r="D33" s="12">
+        <v>0</v>
+      </c>
+      <c r="E33" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="B34" s="13">
-        <v>0</v>
-      </c>
-      <c r="C34" s="13">
-        <v>0</v>
-      </c>
-      <c r="D34" s="13">
-        <v>0</v>
-      </c>
-      <c r="E34" s="13">
+      <c r="A34" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B34" s="12">
+        <v>0</v>
+      </c>
+      <c r="C34" s="12">
+        <v>0</v>
+      </c>
+      <c r="D34" s="12">
+        <v>0</v>
+      </c>
+      <c r="E34" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B35" s="14">
-        <v>0</v>
-      </c>
-      <c r="C35" s="14">
+      <c r="B35" s="13">
+        <v>0</v>
+      </c>
+      <c r="C35" s="13">
         <v>0.78958399999999995</v>
       </c>
-      <c r="D35" s="14">
+      <c r="D35" s="13">
         <v>0.652084</v>
       </c>
-      <c r="E35" s="14">
+      <c r="E35" s="13">
         <v>0</v>
       </c>
     </row>
@@ -8754,46 +8721,46 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="B4" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="B4" s="17" t="s">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+      <c r="B5" s="16"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="B5" s="17"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
+      <c r="B6" s="16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="B6" s="17" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
+      <c r="B7" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="B7" s="17" t="s">
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
+      <c r="B8" s="16" t="s">
         <v>134</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -8968,13 +8935,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB3AB8D1-EFD8-42ED-B888-E3882B3017DA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1F483C7-9028-4F57-B9B2-0A1FA1490184}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{699380AF-D041-452D-B127-91ACE396E067}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C3B6EAD-CC4B-4575-B2E1-0204E1EA0456}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A74AE907-417C-4438-B3A7-48CF6B094F86}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D1BC428-03DB-41A1-B8B5-2FAC2A2749FD}"/>
 </file>
--- a/Plannings 2026 S19.xlsx
+++ b/Plannings 2026 S19.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{84830FEF-CD99-488C-9111-90B341AA8F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA600701-563D-419E-AFCD-310519774913}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{84830FEF-CD99-488C-9111-90B341AA8F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="136">
   <si>
     <t>Planning des salariés du 04/05/2026 au 10/05/2026</t>
   </si>
@@ -205,6 +205,9 @@
   </si>
   <si>
     <t>18:30/20:30</t>
+  </si>
+  <si>
+    <t>21:15/22:15</t>
   </si>
   <si>
     <t>DIVIEN Yohan</t>
@@ -525,7 +528,7 @@
       <name val="Helvetica"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -535,6 +538,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80FF80"/>
       </patternFill>
     </fill>
     <fill>
@@ -603,7 +611,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -623,7 +631,10 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2361,6 +2372,50 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="40" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000028000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>30</xdr:row>
@@ -2715,13 +2770,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2759,13 +2814,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2803,57 +2858,57 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="51" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000033000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="51" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000033000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2891,13 +2946,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2935,21 +2990,65 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="54" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000036000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
+      <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
       <xdr:row>44</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="54" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000036000000}"/>
+        <xdr:cNvPr id="55" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000037000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2979,21 +3078,21 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="55" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000037000000}"/>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="56" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000038000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3021,23 +3120,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
       <xdr:row>44</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="56" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000038000000}"/>
+        <xdr:cNvPr id="57" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000039000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3067,21 +3166,21 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="57" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000039000000}"/>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="58" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3109,23 +3208,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
       <xdr:row>44</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="58" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A000000}"/>
+        <xdr:cNvPr id="59" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3155,21 +3254,21 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="59" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003B000000}"/>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="60" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3179,182 +3278,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="60" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="61" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="62" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="63" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3386,10 +3309,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="64" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000040000000}"/>
+        <xdr:cNvPr id="61" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3417,23 +3340,111 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="62" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="63" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="65" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000041000000}"/>
+        <xdr:cNvPr id="64" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000040000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3463,21 +3474,21 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>53</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>53</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="66" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042000000}"/>
+        <xdr:cNvPr id="65" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000041000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3507,21 +3518,21 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>57</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>57</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="67" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043000000}"/>
+        <xdr:cNvPr id="66" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3549,67 +3560,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="68" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>59</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>59</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="69" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
+        <xdr:cNvPr id="67" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3637,208 +3604,120 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="68" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="70" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>65</xdr:row>
+      <xdr:row>62</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="69" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>65</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="71" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="72" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="70" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3870,10 +3749,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
+        <xdr:cNvPr id="71" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3901,23 +3780,155 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="72" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>69</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>69</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
+        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3945,243 +3956,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>72</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>80</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>72</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
+        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4209,375 +4000,331 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>82</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000057000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>84</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000052000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>84</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4605,23 +4352,111 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>84</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
+      <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
       <xdr:row>84</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
+        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000057000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4649,507 +4484,595 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>86</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>93</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>93</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>95</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>95</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>95</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>95</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>97</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>97</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>99</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="98" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000062000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>99</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="102" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>95</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>95</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>97</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>97</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>99</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5159,94 +5082,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>95</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>95</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>101</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>101</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5278,10 +5113,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
+        <xdr:cNvPr id="102" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000066000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5309,120 +5144,164 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>99</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>99</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>101</xdr:row>
+      <xdr:row>97</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>101</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>103</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
       <xdr:row>103</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="109" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>106</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>106</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="110" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5443,21 +5322,21 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>106</xdr:row>
+      <xdr:row>103</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>106</xdr:row>
+      <xdr:row>103</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="111" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006F000000}"/>
+        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5485,23 +5364,155 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>103</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>103</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="109" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="110" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>109</xdr:row>
+      <xdr:row>108</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>109</xdr:row>
+      <xdr:row>108</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="112" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000070000000}"/>
+        <xdr:cNvPr id="111" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5529,111 +5540,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>109</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>109</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="113" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000071000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>111</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>111</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="114" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000072000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>114</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>114</xdr:row>
+      <xdr:row>111</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="115" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000073000000}"/>
+        <xdr:cNvPr id="112" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000070000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5661,120 +5584,76 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>117</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>117</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="116" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000074000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>119</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>119</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="117" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000075000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>121</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>121</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="118" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000076000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>111</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>111</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="113" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000071000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>113</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>113</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="114" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000072000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5795,118 +5674,162 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>117</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>117</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="119" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000077000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>119</xdr:row>
+      <xdr:row>116</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>116</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="115" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000073000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>119</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="120" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000078000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>124</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>124</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="121" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000079000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="116" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000074000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>121</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>121</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="117" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000075000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>123</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>123</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="118" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000076000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5927,17 +5850,149 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>124</xdr:row>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="119" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000077000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>121</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>124</xdr:row>
+      <xdr:row>121</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
+        <xdr:cNvPr id="120" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000078000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>126</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>126</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="121" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000079000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>126</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>126</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
         <xdr:cNvPr id="122" name="Picture 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
@@ -5959,50 +6014,6 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="124" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B18C206F-90E1-4F7C-A767-9E7C820C1325}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1828800" y="6858000"/>
-          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6380,30 +6391,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H128"/>
+  <dimension ref="A1:H130"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -6432,7 +6443,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="19" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="2"/>
@@ -6445,7 +6456,7 @@
       <c r="H4" s="3"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="18"/>
+      <c r="A5" s="19"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
@@ -6457,7 +6468,7 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="19" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -6472,7 +6483,7 @@
       <c r="H6" s="3"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="18"/>
+      <c r="A7" s="19"/>
       <c r="B7" s="3" t="s">
         <v>16</v>
       </c>
@@ -6486,7 +6497,7 @@
       <c r="H7" s="3"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="19" t="s">
         <v>17</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -6508,7 +6519,7 @@
       <c r="H8" s="3"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="18"/>
+      <c r="A9" s="19"/>
       <c r="B9" s="3" t="s">
         <v>19</v>
       </c>
@@ -6528,7 +6539,7 @@
       <c r="H9" s="3"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="18"/>
+      <c r="A10" s="19"/>
       <c r="B10" s="4" t="s">
         <v>23</v>
       </c>
@@ -6543,7 +6554,7 @@
       <c r="H10" s="3"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="18"/>
+      <c r="A11" s="19"/>
       <c r="B11" s="3" t="s">
         <v>24</v>
       </c>
@@ -6559,7 +6570,7 @@
       <c r="H11" s="3"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="18"/>
+      <c r="A12" s="19"/>
       <c r="B12" s="3"/>
       <c r="C12" s="4" t="s">
         <v>27</v>
@@ -6573,7 +6584,7 @@
       <c r="H12" s="3"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="18"/>
+      <c r="A13" s="19"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3" t="s">
         <v>28</v>
@@ -6587,7 +6598,7 @@
       <c r="H13" s="3"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="18"/>
+      <c r="A14" s="19"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="4" t="s">
@@ -6599,7 +6610,7 @@
       <c r="H14" s="3"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="18"/>
+      <c r="A15" s="19"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3" t="s">
@@ -6611,7 +6622,7 @@
       <c r="H15" s="3"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="18"/>
+      <c r="A16" s="19"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
@@ -6621,7 +6632,7 @@
       <c r="H16" s="5"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="19" t="s">
         <v>31</v>
       </c>
       <c r="B17" s="3"/>
@@ -6634,7 +6645,7 @@
       <c r="H17" s="3"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="18"/>
+      <c r="A18" s="19"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -6646,7 +6657,7 @@
       <c r="H18" s="3"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="18"/>
+      <c r="A19" s="19"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
@@ -6656,7 +6667,7 @@
       <c r="H19" s="5"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="19" t="s">
         <v>33</v>
       </c>
       <c r="B20" s="3"/>
@@ -6671,7 +6682,7 @@
       <c r="H20" s="3"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="18"/>
+      <c r="A21" s="19"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3" t="s">
         <v>16</v>
@@ -6685,7 +6696,7 @@
       <c r="H21" s="3"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="18"/>
+      <c r="A22" s="19"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
@@ -6695,7 +6706,7 @@
       <c r="H22" s="5"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="18" t="s">
+      <c r="A23" s="19" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="4" t="s">
@@ -6714,7 +6725,7 @@
       <c r="H23" s="3"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="18"/>
+      <c r="A24" s="19"/>
       <c r="B24" s="3" t="s">
         <v>35</v>
       </c>
@@ -6732,7 +6743,7 @@
       <c r="H24" s="3"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="18"/>
+      <c r="A25" s="19"/>
       <c r="B25" s="4" t="s">
         <v>15</v>
       </c>
@@ -6746,7 +6757,7 @@
       <c r="H25" s="3"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="18"/>
+      <c r="A26" s="19"/>
       <c r="B26" s="3" t="s">
         <v>32</v>
       </c>
@@ -6760,7 +6771,7 @@
       <c r="H26" s="3"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="18"/>
+      <c r="A27" s="19"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
@@ -6770,7 +6781,7 @@
       <c r="H27" s="5"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="18" t="s">
+      <c r="A28" s="19" t="s">
         <v>40</v>
       </c>
       <c r="B28" s="3"/>
@@ -6787,7 +6798,7 @@
       <c r="H28" s="3"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="18"/>
+      <c r="A29" s="19"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3" t="s">
         <v>41</v>
@@ -6803,7 +6814,7 @@
       <c r="H29" s="3"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="18"/>
+      <c r="A30" s="19"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
@@ -6813,7 +6824,7 @@
       <c r="H30" s="5"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="18" t="s">
+      <c r="A31" s="19" t="s">
         <v>44</v>
       </c>
       <c r="B31" s="4" t="s">
@@ -6835,7 +6846,7 @@
       <c r="H31" s="3"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="18"/>
+      <c r="A32" s="19"/>
       <c r="B32" s="3" t="s">
         <v>46</v>
       </c>
@@ -6855,7 +6866,7 @@
       <c r="H32" s="3"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="18"/>
+      <c r="A33" s="19"/>
       <c r="B33" s="4" t="s">
         <v>50</v>
       </c>
@@ -6872,7 +6883,7 @@
       <c r="H33" s="3"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="18"/>
+      <c r="A34" s="19"/>
       <c r="B34" s="3" t="s">
         <v>52</v>
       </c>
@@ -6890,7 +6901,7 @@
       <c r="H34" s="3"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="18"/>
+      <c r="A35" s="19"/>
       <c r="B35" s="4" t="s">
         <v>45</v>
       </c>
@@ -6906,7 +6917,7 @@
       <c r="H35" s="3"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="18"/>
+      <c r="A36" s="19"/>
       <c r="B36" s="3" t="s">
         <v>56</v>
       </c>
@@ -6922,10 +6933,10 @@
       <c r="H36" s="3"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="18"/>
+      <c r="A37" s="19"/>
       <c r="B37" s="3"/>
-      <c r="C37" s="4" t="s">
-        <v>45</v>
+      <c r="C37" s="6" t="s">
+        <v>59</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>45</v>
@@ -6936,10 +6947,10 @@
       <c r="H37" s="3"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="18"/>
+      <c r="A38" s="19"/>
       <c r="B38" s="3"/>
-      <c r="C38" s="3" t="s">
-        <v>59</v>
+      <c r="C38" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>60</v>
@@ -6950,1126 +6961,1124 @@
       <c r="H38" s="3"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="18" t="s">
+      <c r="A39" s="19"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B39" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
-      <c r="F39" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
       <c r="H39" s="3"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="18"/>
-      <c r="B40" s="3" t="s">
+      <c r="A40" s="19"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="B41" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H40" s="3"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="18"/>
-      <c r="B41" s="3"/>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
-      <c r="G41" s="3"/>
+      <c r="F41" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="H41" s="3"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="18"/>
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5"/>
-      <c r="H42" s="5"/>
+      <c r="A42" s="19"/>
+      <c r="B42" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H42" s="3"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="18" t="s">
-        <v>65</v>
-      </c>
+      <c r="A43" s="19"/>
       <c r="B43" s="3"/>
-      <c r="C43" s="4" t="s">
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="19"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="D43" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="G43" s="3"/>
-      <c r="H43" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="18"/>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G44" s="3"/>
-      <c r="H44" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="18"/>
       <c r="B45" s="3"/>
       <c r="C45" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G45" s="3"/>
-      <c r="H45" s="3"/>
+      <c r="H45" s="4" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="18"/>
+      <c r="A46" s="19"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G46" s="3"/>
+      <c r="H46" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="18"/>
+      <c r="A47" s="19"/>
       <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
+      <c r="C47" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>67</v>
+      </c>
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="18"/>
-      <c r="B48" s="5"/>
-      <c r="C48" s="5"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="5"/>
-      <c r="H48" s="5"/>
+      <c r="A48" s="19"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="18" t="s">
-        <v>71</v>
-      </c>
+      <c r="A49" s="19"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
-      <c r="E49" s="4" t="s">
-        <v>15</v>
-      </c>
+      <c r="E49" s="3"/>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="18"/>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3"/>
-      <c r="H50" s="3"/>
+      <c r="A50" s="19"/>
+      <c r="B50" s="5"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="18"/>
-      <c r="B51" s="5"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
-      <c r="H51" s="5"/>
+      <c r="A51" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G51" s="3"/>
+      <c r="H51" s="3"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="18" t="s">
-        <v>72</v>
-      </c>
+      <c r="A52" s="19"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
-      <c r="E52" s="3"/>
+      <c r="E52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F52" s="3"/>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="18"/>
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
-      <c r="E53" s="3"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3"/>
-      <c r="H53" s="3"/>
+      <c r="A53" s="19"/>
+      <c r="B53" s="5"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="5"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="5"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="5"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="18"/>
-      <c r="B54" s="5"/>
-      <c r="C54" s="5"/>
-      <c r="D54" s="5"/>
-      <c r="E54" s="5"/>
-      <c r="F54" s="5"/>
-      <c r="G54" s="5"/>
-      <c r="H54" s="5"/>
+      <c r="A54" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="G54" s="3"/>
+      <c r="H54" s="3"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="18" t="s">
-        <v>73</v>
-      </c>
+      <c r="A55" s="19"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="18"/>
-      <c r="B56" s="3"/>
-      <c r="C56" s="3"/>
-      <c r="D56" s="3"/>
-      <c r="E56" s="3"/>
-      <c r="F56" s="3"/>
-      <c r="G56" s="3"/>
-      <c r="H56" s="3"/>
+      <c r="A56" s="19"/>
+      <c r="B56" s="5"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="5"/>
+      <c r="F56" s="5"/>
+      <c r="G56" s="5"/>
+      <c r="H56" s="5"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="18"/>
-      <c r="B57" s="5"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="5"/>
-      <c r="E57" s="5"/>
-      <c r="F57" s="5"/>
-      <c r="G57" s="5"/>
-      <c r="H57" s="5"/>
+      <c r="A57" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="G57" s="3"/>
+      <c r="H57" s="3"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="18" t="s">
-        <v>74</v>
-      </c>
+      <c r="A58" s="19"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
       <c r="G58" s="3"/>
       <c r="H58" s="3"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="18"/>
-      <c r="B59" s="3"/>
-      <c r="C59" s="3"/>
-      <c r="D59" s="3"/>
-      <c r="E59" s="3"/>
-      <c r="F59" s="3"/>
-      <c r="G59" s="3"/>
-      <c r="H59" s="3"/>
+      <c r="A59" s="19"/>
+      <c r="B59" s="5"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="5"/>
+      <c r="E59" s="5"/>
+      <c r="F59" s="5"/>
+      <c r="G59" s="5"/>
+      <c r="H59" s="5"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="18"/>
-      <c r="B60" s="5"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="5"/>
-      <c r="E60" s="5"/>
-      <c r="F60" s="5"/>
-      <c r="G60" s="5"/>
-      <c r="H60" s="5"/>
+      <c r="A60" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="G60" s="3"/>
+      <c r="H60" s="3"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="18" t="s">
-        <v>75</v>
-      </c>
+      <c r="A61" s="19"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
-      <c r="D61" s="4" t="s">
-        <v>27</v>
-      </c>
+      <c r="D61" s="3"/>
       <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="18"/>
-      <c r="B62" s="3"/>
-      <c r="C62" s="3"/>
-      <c r="D62" s="3" t="s">
+      <c r="A62" s="19"/>
+      <c r="B62" s="5"/>
+      <c r="C62" s="5"/>
+      <c r="D62" s="5"/>
+      <c r="E62" s="5"/>
+      <c r="F62" s="5"/>
+      <c r="G62" s="5"/>
+      <c r="H62" s="5"/>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="E62" s="3"/>
-      <c r="F62" s="3"/>
-      <c r="G62" s="3"/>
-      <c r="H62" s="3"/>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="18"/>
-      <c r="B63" s="5"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
-      <c r="G63" s="5"/>
-      <c r="H63" s="5"/>
+      <c r="B63" s="3"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E63" s="3"/>
+      <c r="G63" s="3"/>
+      <c r="H63" s="3"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="18" t="s">
-        <v>77</v>
-      </c>
+      <c r="A64" s="19"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
-      <c r="D64" s="3"/>
+      <c r="D64" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="E64" s="3"/>
-      <c r="F64" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="F64" s="3"/>
       <c r="G64" s="3"/>
       <c r="H64" s="3"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="18"/>
-      <c r="B65" s="3"/>
-      <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3"/>
-      <c r="F65" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="G65" s="3"/>
-      <c r="H65" s="3"/>
+      <c r="A65" s="19"/>
+      <c r="B65" s="5"/>
+      <c r="C65" s="5"/>
+      <c r="D65" s="5"/>
+      <c r="E65" s="5"/>
+      <c r="F65" s="5"/>
+      <c r="G65" s="5"/>
+      <c r="H65" s="5"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="18"/>
+      <c r="A66" s="19" t="s">
+        <v>78</v>
+      </c>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
+      <c r="F66" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="G66" s="3"/>
       <c r="H66" s="3"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="18"/>
-      <c r="B67" s="5"/>
-      <c r="C67" s="5"/>
-      <c r="D67" s="5"/>
-      <c r="E67" s="5"/>
-      <c r="F67" s="5"/>
-      <c r="G67" s="5"/>
-      <c r="H67" s="5"/>
+      <c r="A67" s="19"/>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G67" s="3"/>
+      <c r="H67" s="3"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>27</v>
-      </c>
+      <c r="A68" s="19"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
       <c r="E68" s="3"/>
       <c r="G68" s="3"/>
       <c r="H68" s="3"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="18"/>
-      <c r="B69" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D69" s="3" t="s">
+      <c r="A69" s="19"/>
+      <c r="B69" s="5"/>
+      <c r="C69" s="5"/>
+      <c r="D69" s="5"/>
+      <c r="E69" s="5"/>
+      <c r="F69" s="5"/>
+      <c r="G69" s="5"/>
+      <c r="H69" s="5"/>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="E69" s="3"/>
-      <c r="F69" s="3"/>
-      <c r="G69" s="3"/>
-      <c r="H69" s="3"/>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="18"/>
-      <c r="B70" s="5"/>
-      <c r="C70" s="5"/>
-      <c r="D70" s="5"/>
-      <c r="E70" s="5"/>
-      <c r="F70" s="5"/>
-      <c r="G70" s="5"/>
-      <c r="H70" s="5"/>
+      <c r="B70" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E70" s="3"/>
+      <c r="G70" s="3"/>
+      <c r="H70" s="3"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="18" t="s">
+      <c r="A71" s="19"/>
+      <c r="B71" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D71" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B71" s="3"/>
-      <c r="C71" s="3"/>
-      <c r="D71" s="3"/>
       <c r="E71" s="3"/>
-      <c r="G71" s="4" t="s">
+      <c r="F71" s="3"/>
+      <c r="G71" s="3"/>
+      <c r="H71" s="3"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="19"/>
+      <c r="B72" s="5"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="5"/>
+      <c r="E72" s="5"/>
+      <c r="F72" s="5"/>
+      <c r="G72" s="5"/>
+      <c r="H72" s="5"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="H71" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="18"/>
-      <c r="B72" s="3"/>
-      <c r="C72" s="3"/>
-      <c r="D72" s="3"/>
-      <c r="E72" s="3"/>
-      <c r="F72" s="3"/>
-      <c r="G72" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="18"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
-      <c r="F73" s="3"/>
       <c r="G73" s="4" t="s">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>15</v>
+        <v>82</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="18"/>
+      <c r="A74" s="19"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="H74" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="H74" s="3" t="s">
-        <v>85</v>
-      </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="18"/>
+      <c r="A75" s="19"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
-      <c r="G75" s="3"/>
+      <c r="G75" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="H75" s="4" t="s">
-        <v>81</v>
+        <v>15</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="18"/>
+      <c r="A76" s="19"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
-      <c r="G76" s="3"/>
+      <c r="G76" s="3" t="s">
+        <v>85</v>
+      </c>
       <c r="H76" s="3" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="18"/>
-      <c r="B77" s="5"/>
-      <c r="C77" s="5"/>
-      <c r="D77" s="5"/>
-      <c r="E77" s="5"/>
-      <c r="F77" s="5"/>
-      <c r="G77" s="5"/>
-      <c r="H77" s="5"/>
+      <c r="A77" s="19"/>
+      <c r="B77" s="3"/>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3"/>
+      <c r="G77" s="3"/>
+      <c r="H77" s="4" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="B78" s="6" t="s">
+      <c r="A78" s="19"/>
+      <c r="B78" s="3"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3"/>
+      <c r="H78" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" s="19"/>
+      <c r="B79" s="5"/>
+      <c r="C79" s="5"/>
+      <c r="D79" s="5"/>
+      <c r="E79" s="5"/>
+      <c r="F79" s="5"/>
+      <c r="G79" s="5"/>
+      <c r="H79" s="5"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="C78" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="D78" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="E78" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="F78" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="G78" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="18"/>
-      <c r="B79" s="7" t="s">
+      <c r="B80" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C79" s="7" t="s">
+      <c r="C80" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="D79" s="7" t="s">
+      <c r="D80" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="E79" s="7" t="s">
+      <c r="E80" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="F79" s="7" t="s">
+      <c r="F80" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="G79" s="7" t="s">
+      <c r="G80" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="H79" s="7" t="s">
+      <c r="H80" s="7" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="18"/>
-      <c r="B80" s="7" t="s">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="19"/>
+      <c r="B81" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="C80" s="7" t="s">
+      <c r="C81" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="D80" s="7" t="s">
+      <c r="D81" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="E80" s="7" t="s">
+      <c r="E81" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="F80" s="7" t="s">
+      <c r="F81" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="G80" s="7" t="s">
+      <c r="G81" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="H80" s="7" t="s">
+      <c r="H81" s="8" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="18"/>
-      <c r="B81" s="7"/>
-      <c r="C81" s="7"/>
-      <c r="D81" s="7"/>
-      <c r="E81" s="7"/>
-      <c r="G81" s="7"/>
-      <c r="H81" s="7"/>
-    </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="18"/>
-      <c r="B82" s="5"/>
-      <c r="C82" s="5"/>
-      <c r="D82" s="5"/>
-      <c r="E82" s="5"/>
-      <c r="F82" s="5"/>
-      <c r="G82" s="5"/>
-      <c r="H82" s="5"/>
+      <c r="A82" s="19"/>
+      <c r="B82" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D82" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="F82" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="G82" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="H82" s="8" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="B83" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C83" s="4" t="s">
+      <c r="A83" s="19"/>
+      <c r="B83" s="8"/>
+      <c r="C83" s="8"/>
+      <c r="D83" s="8"/>
+      <c r="E83" s="8"/>
+      <c r="G83" s="8"/>
+      <c r="H83" s="8"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="19"/>
+      <c r="B84" s="5"/>
+      <c r="C84" s="5"/>
+      <c r="D84" s="5"/>
+      <c r="E84" s="5"/>
+      <c r="F84" s="5"/>
+      <c r="G84" s="5"/>
+      <c r="H84" s="5"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C85" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D83" s="4" t="s">
+      <c r="D85" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E83" s="3"/>
-      <c r="F83" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="G83" s="4" t="s">
+      <c r="E85" s="3"/>
+      <c r="F85" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G85" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H83" s="3"/>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="18"/>
-      <c r="B84" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C84" s="3" t="s">
+      <c r="H85" s="3"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" s="19"/>
+      <c r="B86" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D84" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E84" s="3"/>
-      <c r="F84" s="3" t="s">
+      <c r="C86" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G84" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="H84" s="3"/>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="18"/>
-      <c r="B85" s="3"/>
-      <c r="C85" s="4" t="s">
+      <c r="G86" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="H86" s="3"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="19"/>
+      <c r="B87" s="3"/>
+      <c r="C87" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D85" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E85" s="3"/>
-      <c r="G85" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="H85" s="3"/>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="18"/>
-      <c r="B86" s="3"/>
-      <c r="C86" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D86" s="3" t="s">
+      <c r="D87" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E86" s="3"/>
-      <c r="F86" s="3"/>
-      <c r="G86" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="H86" s="3"/>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="18"/>
-      <c r="B87" s="3"/>
-      <c r="C87" s="3"/>
-      <c r="D87" s="4" t="s">
-        <v>12</v>
-      </c>
       <c r="E87" s="3"/>
-      <c r="F87" s="3"/>
       <c r="G87" s="4" t="s">
-        <v>12</v>
+        <v>95</v>
       </c>
       <c r="H87" s="3"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="18"/>
+      <c r="A88" s="19"/>
       <c r="B88" s="3"/>
-      <c r="C88" s="3"/>
+      <c r="C88" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="D88" s="3" t="s">
         <v>96</v>
       </c>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="H88" s="3"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="18"/>
+      <c r="A89" s="19"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
       <c r="D89" s="4" t="s">
-        <v>94</v>
+        <v>12</v>
       </c>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
       <c r="G89" s="4" t="s">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="H89" s="3"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="18"/>
+      <c r="A90" s="19"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
       <c r="D90" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="H90" s="3"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" s="19"/>
+      <c r="B91" s="3"/>
+      <c r="C91" s="3"/>
+      <c r="D91" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E91" s="3"/>
+      <c r="F91" s="3"/>
+      <c r="G91" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="H91" s="3"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="19"/>
+      <c r="B92" s="3"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H90" s="3"/>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="18"/>
-      <c r="B91" s="5"/>
-      <c r="C91" s="5"/>
-      <c r="D91" s="5"/>
-      <c r="E91" s="5"/>
-      <c r="F91" s="5"/>
-      <c r="G91" s="5"/>
-      <c r="H91" s="5"/>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="18" t="s">
+      <c r="E92" s="3"/>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B92" s="4" t="s">
+      <c r="H92" s="3"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" s="19"/>
+      <c r="B93" s="5"/>
+      <c r="C93" s="5"/>
+      <c r="D93" s="5"/>
+      <c r="E93" s="5"/>
+      <c r="F93" s="5"/>
+      <c r="G93" s="5"/>
+      <c r="H93" s="5"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="B94" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C92" s="4" t="s">
+      <c r="C94" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D92" s="3"/>
-      <c r="E92" s="3"/>
-      <c r="F92" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G92" s="3"/>
-      <c r="H92" s="3"/>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="18"/>
-      <c r="B93" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D93" s="3"/>
-      <c r="E93" s="3"/>
-      <c r="F93" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="G93" s="3"/>
-      <c r="H93" s="3"/>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="18"/>
-      <c r="B94" s="3"/>
-      <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
+      <c r="F94" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="G94" s="3"/>
       <c r="H94" s="3"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="18"/>
-      <c r="B95" s="5"/>
-      <c r="C95" s="5"/>
-      <c r="D95" s="5"/>
-      <c r="E95" s="5"/>
-      <c r="F95" s="5"/>
-      <c r="G95" s="5"/>
-      <c r="H95" s="5"/>
+      <c r="A95" s="19"/>
+      <c r="B95" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D95" s="3"/>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G95" s="3"/>
+      <c r="H95" s="3"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A96" s="18" t="s">
-        <v>101</v>
-      </c>
+      <c r="A96" s="19"/>
       <c r="B96" s="3"/>
-      <c r="C96" s="4" t="s">
+      <c r="C96" s="3"/>
+      <c r="D96" s="3"/>
+      <c r="E96" s="3"/>
+      <c r="G96" s="3"/>
+      <c r="H96" s="3"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" s="19"/>
+      <c r="B97" s="5"/>
+      <c r="C97" s="5"/>
+      <c r="D97" s="5"/>
+      <c r="E97" s="5"/>
+      <c r="F97" s="5"/>
+      <c r="G97" s="5"/>
+      <c r="H97" s="5"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="B98" s="3"/>
+      <c r="C98" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D96" s="3"/>
-      <c r="E96" s="4" t="s">
+      <c r="D98" s="3"/>
+      <c r="E98" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F96" s="4" t="s">
+      <c r="F98" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="G96" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="H96" s="4" t="s">
+      <c r="G98" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H98" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="18"/>
-      <c r="B97" s="3"/>
-      <c r="C97" s="3" t="s">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" s="19"/>
+      <c r="B99" s="3"/>
+      <c r="C99" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D97" s="3"/>
-      <c r="E97" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F97" s="3" t="s">
+      <c r="D99" s="3"/>
+      <c r="E99" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="G97" s="3" t="s">
+      <c r="F99" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="H97" s="3" t="s">
+      <c r="G99" s="3" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A98" s="18"/>
-      <c r="B98" s="3"/>
-      <c r="C98" s="3"/>
-      <c r="D98" s="3"/>
-      <c r="E98" s="3"/>
-      <c r="F98" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G98" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H98" s="3"/>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" s="18"/>
-      <c r="B99" s="3"/>
-      <c r="C99" s="3"/>
-      <c r="D99" s="3"/>
-      <c r="E99" s="3"/>
-      <c r="F99" s="3" t="s">
+      <c r="H99" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="G99" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="H99" s="3"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" s="18"/>
+      <c r="A100" s="19"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
-      <c r="G100" s="3"/>
+      <c r="F100" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G100" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="H100" s="3"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101" s="18"/>
-      <c r="B101" s="5"/>
-      <c r="C101" s="5"/>
-      <c r="D101" s="5"/>
-      <c r="E101" s="5"/>
-      <c r="F101" s="5"/>
-      <c r="G101" s="5"/>
-      <c r="H101" s="5"/>
+      <c r="A101" s="19"/>
+      <c r="B101" s="3"/>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3"/>
+      <c r="E101" s="3"/>
+      <c r="F101" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H101" s="3"/>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A102" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="B102" s="4" t="s">
-        <v>27</v>
-      </c>
+      <c r="A102" s="19"/>
+      <c r="B102" s="3"/>
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
       <c r="G102" s="3"/>
-      <c r="H102" s="4" t="s">
-        <v>81</v>
-      </c>
+      <c r="H102" s="3"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A103" s="18"/>
-      <c r="B103" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C103" s="3"/>
-      <c r="D103" s="3"/>
-      <c r="E103" s="3"/>
-      <c r="F103" s="3"/>
-      <c r="G103" s="3"/>
-      <c r="H103" s="3" t="s">
-        <v>82</v>
-      </c>
+      <c r="A103" s="19"/>
+      <c r="B103" s="5"/>
+      <c r="C103" s="5"/>
+      <c r="D103" s="5"/>
+      <c r="E103" s="5"/>
+      <c r="F103" s="5"/>
+      <c r="G103" s="5"/>
+      <c r="H103" s="5"/>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A104" s="18"/>
-      <c r="B104" s="3"/>
+      <c r="A104" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
       <c r="E104" s="3"/>
-      <c r="F104" s="3"/>
       <c r="G104" s="3"/>
       <c r="H104" s="4" t="s">
-        <v>15</v>
+        <v>82</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A105" s="18"/>
-      <c r="B105" s="3"/>
+      <c r="A105" s="19"/>
+      <c r="B105" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
       <c r="E105" s="3"/>
       <c r="F105" s="3"/>
       <c r="G105" s="3"/>
       <c r="H105" s="3" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A106" s="18"/>
-      <c r="B106" s="5"/>
-      <c r="C106" s="5"/>
-      <c r="D106" s="5"/>
-      <c r="E106" s="5"/>
-      <c r="F106" s="5"/>
-      <c r="G106" s="5"/>
-      <c r="H106" s="5"/>
+      <c r="A106" s="19"/>
+      <c r="B106" s="3"/>
+      <c r="C106" s="3"/>
+      <c r="D106" s="3"/>
+      <c r="E106" s="3"/>
+      <c r="F106" s="3"/>
+      <c r="G106" s="3"/>
+      <c r="H106" s="4" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A107" s="18" t="s">
-        <v>111</v>
-      </c>
+      <c r="A107" s="19"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
-      <c r="D107" s="4" t="s">
+      <c r="D107" s="3"/>
+      <c r="E107" s="3"/>
+      <c r="F107" s="3"/>
+      <c r="G107" s="3"/>
+      <c r="H107" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" s="19"/>
+      <c r="B108" s="5"/>
+      <c r="C108" s="5"/>
+      <c r="D108" s="5"/>
+      <c r="E108" s="5"/>
+      <c r="F108" s="5"/>
+      <c r="G108" s="5"/>
+      <c r="H108" s="5"/>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="B109" s="3"/>
+      <c r="C109" s="3"/>
+      <c r="D109" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E107" s="3"/>
-      <c r="G107" s="3"/>
-      <c r="H107" s="3"/>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A108" s="18"/>
-      <c r="B108" s="3"/>
-      <c r="C108" s="3"/>
-      <c r="D108" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E108" s="3"/>
-      <c r="F108" s="3"/>
-      <c r="G108" s="3"/>
-      <c r="H108" s="3"/>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A109" s="18"/>
-      <c r="B109" s="5"/>
-      <c r="C109" s="5"/>
-      <c r="D109" s="5"/>
-      <c r="E109" s="5"/>
-      <c r="F109" s="5"/>
-      <c r="G109" s="5"/>
-      <c r="H109" s="5"/>
+      <c r="E109" s="3"/>
+      <c r="G109" s="3"/>
+      <c r="H109" s="3"/>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A110" s="18" t="s">
-        <v>112</v>
-      </c>
+      <c r="A110" s="19"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
-      <c r="D110" s="3"/>
+      <c r="D110" s="3" t="s">
+        <v>83</v>
+      </c>
       <c r="E110" s="3"/>
-      <c r="G110" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="F110" s="3"/>
+      <c r="G110" s="3"/>
       <c r="H110" s="3"/>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A111" s="18"/>
-      <c r="B111" s="3"/>
-      <c r="C111" s="3"/>
-      <c r="D111" s="3"/>
-      <c r="E111" s="3"/>
-      <c r="F111" s="3"/>
-      <c r="G111" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H111" s="3"/>
+      <c r="A111" s="19"/>
+      <c r="B111" s="5"/>
+      <c r="C111" s="5"/>
+      <c r="D111" s="5"/>
+      <c r="E111" s="5"/>
+      <c r="F111" s="5"/>
+      <c r="G111" s="5"/>
+      <c r="H111" s="5"/>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A112" s="18"/>
+      <c r="A112" s="19" t="s">
+        <v>113</v>
+      </c>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
-      <c r="F112" s="3"/>
       <c r="G112" s="4" t="s">
         <v>12</v>
       </c>
       <c r="H112" s="3"/>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A113" s="18"/>
+      <c r="A113" s="19"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
       <c r="E113" s="3"/>
       <c r="F113" s="3"/>
       <c r="G113" s="3" t="s">
-        <v>113</v>
+        <v>13</v>
       </c>
       <c r="H113" s="3"/>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A114" s="18"/>
-      <c r="B114" s="5"/>
-      <c r="C114" s="5"/>
-      <c r="D114" s="5"/>
-      <c r="E114" s="5"/>
-      <c r="F114" s="5"/>
-      <c r="G114" s="5"/>
-      <c r="H114" s="5"/>
+      <c r="A114" s="19"/>
+      <c r="B114" s="3"/>
+      <c r="C114" s="3"/>
+      <c r="D114" s="3"/>
+      <c r="E114" s="3"/>
+      <c r="F114" s="3"/>
+      <c r="G114" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H114" s="3"/>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A115" s="18" t="s">
-        <v>114</v>
-      </c>
+      <c r="A115" s="19"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
       <c r="E115" s="3"/>
-      <c r="G115" s="3"/>
+      <c r="F115" s="3"/>
+      <c r="G115" s="3" t="s">
+        <v>114</v>
+      </c>
       <c r="H115" s="3"/>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A116" s="18"/>
-      <c r="B116" s="3"/>
-      <c r="C116" s="3"/>
-      <c r="D116" s="3"/>
-      <c r="E116" s="3"/>
-      <c r="F116" s="3"/>
-      <c r="G116" s="3"/>
-      <c r="H116" s="3"/>
+      <c r="A116" s="19"/>
+      <c r="B116" s="5"/>
+      <c r="C116" s="5"/>
+      <c r="D116" s="5"/>
+      <c r="E116" s="5"/>
+      <c r="F116" s="5"/>
+      <c r="G116" s="5"/>
+      <c r="H116" s="5"/>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A117" s="18"/>
-      <c r="B117" s="5"/>
-      <c r="C117" s="5"/>
-      <c r="D117" s="5"/>
-      <c r="E117" s="5"/>
-      <c r="F117" s="5"/>
-      <c r="G117" s="5"/>
-      <c r="H117" s="5"/>
+      <c r="A117" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="B117" s="3"/>
+      <c r="C117" s="3"/>
+      <c r="D117" s="3"/>
+      <c r="E117" s="3"/>
+      <c r="G117" s="3"/>
+      <c r="H117" s="3"/>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A118" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="B118" s="4" t="s">
-        <v>15</v>
-      </c>
+      <c r="A118" s="19"/>
+      <c r="B118" s="3"/>
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
       <c r="E118" s="3"/>
-      <c r="F118" s="4" t="s">
-        <v>15</v>
-      </c>
+      <c r="F118" s="3"/>
       <c r="G118" s="3"/>
       <c r="H118" s="3"/>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A119" s="18"/>
-      <c r="B119" s="3" t="s">
+      <c r="A119" s="19"/>
+      <c r="B119" s="5"/>
+      <c r="C119" s="5"/>
+      <c r="D119" s="5"/>
+      <c r="E119" s="5"/>
+      <c r="F119" s="5"/>
+      <c r="G119" s="5"/>
+      <c r="H119" s="5"/>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="C119" s="3"/>
-      <c r="D119" s="3"/>
-      <c r="E119" s="3"/>
-      <c r="F119" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="G119" s="3"/>
-      <c r="H119" s="3"/>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A120" s="18"/>
       <c r="B120" s="4" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
+      <c r="F120" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="G120" s="3"/>
       <c r="H120" s="3"/>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A121" s="18"/>
+      <c r="A121" s="19"/>
       <c r="B121" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
       <c r="E121" s="3"/>
-      <c r="F121" s="3"/>
+      <c r="F121" s="3" t="s">
+        <v>118</v>
+      </c>
       <c r="G121" s="3"/>
       <c r="H121" s="3"/>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A122" s="18"/>
+      <c r="A122" s="19"/>
       <c r="B122" s="4" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
-      <c r="F122" s="3"/>
       <c r="G122" s="3"/>
       <c r="H122" s="3"/>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A123" s="18"/>
+      <c r="A123" s="19"/>
       <c r="B123" s="3" t="s">
         <v>119</v>
       </c>
@@ -8081,87 +8090,111 @@
       <c r="H123" s="3"/>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A124" s="18"/>
-      <c r="B124" s="5"/>
-      <c r="C124" s="5"/>
-      <c r="D124" s="5"/>
-      <c r="E124" s="5"/>
-      <c r="F124" s="5"/>
-      <c r="G124" s="5"/>
-      <c r="H124" s="5"/>
+      <c r="A124" s="19"/>
+      <c r="B124" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C124" s="3"/>
+      <c r="D124" s="3"/>
+      <c r="E124" s="3"/>
+      <c r="F124" s="3"/>
+      <c r="G124" s="3"/>
+      <c r="H124" s="3"/>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A125" s="18" t="s">
+      <c r="A125" s="19"/>
+      <c r="B125" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B125" s="3"/>
       <c r="C125" s="3"/>
-      <c r="D125" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="D125" s="3"/>
       <c r="E125" s="3"/>
+      <c r="F125" s="3"/>
       <c r="G125" s="3"/>
       <c r="H125" s="3"/>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A126" s="18"/>
-      <c r="B126" s="3"/>
-      <c r="C126" s="3"/>
-      <c r="D126" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E126" s="3"/>
-      <c r="F126" s="3"/>
-      <c r="G126" s="3"/>
-      <c r="H126" s="3"/>
+      <c r="A126" s="19"/>
+      <c r="B126" s="5"/>
+      <c r="C126" s="5"/>
+      <c r="D126" s="5"/>
+      <c r="E126" s="5"/>
+      <c r="F126" s="5"/>
+      <c r="G126" s="5"/>
+      <c r="H126" s="5"/>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A127" s="18"/>
-      <c r="B127" s="5"/>
-      <c r="C127" s="5"/>
-      <c r="D127" s="5"/>
-      <c r="E127" s="5"/>
-      <c r="F127" s="5"/>
-      <c r="G127" s="5"/>
-      <c r="H127" s="5"/>
+      <c r="A127" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="B127" s="3"/>
+      <c r="C127" s="3"/>
+      <c r="D127" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E127" s="3"/>
+      <c r="G127" s="3"/>
+      <c r="H127" s="3"/>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B128" s="19"/>
-      <c r="C128" s="19"/>
-      <c r="D128" s="19"/>
-      <c r="E128" s="19"/>
-      <c r="F128" s="19"/>
-      <c r="G128" s="19"/>
-      <c r="H128" s="19"/>
+      <c r="A128" s="19"/>
+      <c r="B128" s="3"/>
+      <c r="C128" s="3"/>
+      <c r="D128" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E128" s="3"/>
+      <c r="F128" s="3"/>
+      <c r="G128" s="3"/>
+      <c r="H128" s="3"/>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" s="19"/>
+      <c r="B129" s="5"/>
+      <c r="C129" s="5"/>
+      <c r="D129" s="5"/>
+      <c r="E129" s="5"/>
+      <c r="F129" s="5"/>
+      <c r="G129" s="5"/>
+      <c r="H129" s="5"/>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B130" s="20"/>
+      <c r="C130" s="20"/>
+      <c r="D130" s="20"/>
+      <c r="E130" s="20"/>
+      <c r="F130" s="20"/>
+      <c r="G130" s="20"/>
+      <c r="H130" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="B128:H128"/>
-    <mergeCell ref="A107:A109"/>
-    <mergeCell ref="A110:A114"/>
-    <mergeCell ref="A115:A117"/>
-    <mergeCell ref="A118:A124"/>
-    <mergeCell ref="A125:A127"/>
-    <mergeCell ref="A78:A82"/>
-    <mergeCell ref="A83:A91"/>
-    <mergeCell ref="A92:A95"/>
-    <mergeCell ref="A96:A101"/>
-    <mergeCell ref="A102:A106"/>
-    <mergeCell ref="A58:A60"/>
-    <mergeCell ref="A61:A63"/>
-    <mergeCell ref="A64:A67"/>
-    <mergeCell ref="A68:A70"/>
-    <mergeCell ref="A71:A77"/>
-    <mergeCell ref="A39:A42"/>
-    <mergeCell ref="A43:A48"/>
-    <mergeCell ref="A49:A51"/>
-    <mergeCell ref="A52:A54"/>
-    <mergeCell ref="A55:A57"/>
+    <mergeCell ref="B130:H130"/>
+    <mergeCell ref="A109:A111"/>
+    <mergeCell ref="A112:A116"/>
+    <mergeCell ref="A117:A119"/>
+    <mergeCell ref="A120:A126"/>
+    <mergeCell ref="A127:A129"/>
+    <mergeCell ref="A80:A84"/>
+    <mergeCell ref="A85:A93"/>
+    <mergeCell ref="A94:A97"/>
+    <mergeCell ref="A98:A103"/>
+    <mergeCell ref="A104:A108"/>
+    <mergeCell ref="A60:A62"/>
+    <mergeCell ref="A63:A65"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="A70:A72"/>
+    <mergeCell ref="A73:A79"/>
+    <mergeCell ref="A41:A44"/>
+    <mergeCell ref="A45:A50"/>
+    <mergeCell ref="A51:A53"/>
+    <mergeCell ref="A54:A56"/>
+    <mergeCell ref="A57:A59"/>
     <mergeCell ref="A17:A19"/>
     <mergeCell ref="A20:A22"/>
     <mergeCell ref="A23:A27"/>
     <mergeCell ref="A28:A30"/>
-    <mergeCell ref="A31:A38"/>
+    <mergeCell ref="A31:A40"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="A4:A5"/>
@@ -8179,530 +8212,530 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="13">
+        <v>0</v>
+      </c>
+      <c r="C7" s="13">
+        <v>0</v>
+      </c>
+      <c r="D7" s="13">
+        <v>0</v>
+      </c>
+      <c r="E7" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="13">
+        <v>0</v>
+      </c>
+      <c r="C8" s="13">
+        <v>0</v>
+      </c>
+      <c r="D8" s="13">
+        <v>0</v>
+      </c>
+      <c r="E8" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="13">
+        <v>0</v>
+      </c>
+      <c r="C9" s="13">
+        <v>4.1667000000000003E-2</v>
+      </c>
+      <c r="D9" s="13">
+        <v>0</v>
+      </c>
+      <c r="E9" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="13">
+        <v>0</v>
+      </c>
+      <c r="C10" s="13">
+        <v>0</v>
+      </c>
+      <c r="D10" s="13">
+        <v>0</v>
+      </c>
+      <c r="E10" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="13">
+        <v>0</v>
+      </c>
+      <c r="C11" s="13">
+        <v>0</v>
+      </c>
+      <c r="D11" s="13">
+        <v>0</v>
+      </c>
+      <c r="E11" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="13">
+        <v>0</v>
+      </c>
+      <c r="C12" s="13">
+        <v>0</v>
+      </c>
+      <c r="D12" s="13">
+        <v>0</v>
+      </c>
+      <c r="E12" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="13">
+        <v>0</v>
+      </c>
+      <c r="C13" s="13">
+        <v>0</v>
+      </c>
+      <c r="D13" s="13">
+        <v>0</v>
+      </c>
+      <c r="E13" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="13">
+        <v>0</v>
+      </c>
+      <c r="C14" s="13">
+        <v>0</v>
+      </c>
+      <c r="D14" s="13">
+        <v>0</v>
+      </c>
+      <c r="E14" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B15" s="13">
+        <v>0</v>
+      </c>
+      <c r="C15" s="13">
+        <v>0</v>
+      </c>
+      <c r="D15" s="13">
+        <v>0</v>
+      </c>
+      <c r="E15" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16" s="13">
+        <v>0</v>
+      </c>
+      <c r="C16" s="13">
+        <v>0</v>
+      </c>
+      <c r="D16" s="13">
+        <v>0</v>
+      </c>
+      <c r="E16" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" s="13">
+        <v>0</v>
+      </c>
+      <c r="C17" s="13">
+        <v>0</v>
+      </c>
+      <c r="D17" s="13">
+        <v>0</v>
+      </c>
+      <c r="E17" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="13">
+        <v>0</v>
+      </c>
+      <c r="C18" s="13">
+        <v>0</v>
+      </c>
+      <c r="D18" s="13">
+        <v>0</v>
+      </c>
+      <c r="E18" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" s="13">
+        <v>0</v>
+      </c>
+      <c r="C19" s="13">
+        <v>0</v>
+      </c>
+      <c r="D19" s="13">
+        <v>0</v>
+      </c>
+      <c r="E19" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" s="13">
+        <v>0</v>
+      </c>
+      <c r="C20" s="13">
+        <v>0</v>
+      </c>
+      <c r="D20" s="13">
+        <v>0</v>
+      </c>
+      <c r="E20" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="B21" s="13">
+        <v>0</v>
+      </c>
+      <c r="C21" s="13">
+        <v>0.125</v>
+      </c>
+      <c r="D21" s="13">
+        <v>0</v>
+      </c>
+      <c r="E21" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" s="13">
+        <v>0</v>
+      </c>
+      <c r="C22" s="13">
+        <v>0</v>
+      </c>
+      <c r="D22" s="13">
+        <v>0</v>
+      </c>
+      <c r="E22" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="B23" s="13">
+        <v>0</v>
+      </c>
+      <c r="C23" s="13">
+        <v>0.33333400000000002</v>
+      </c>
+      <c r="D23" s="13">
+        <v>0</v>
+      </c>
+      <c r="E23" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B24" s="13">
+        <v>0</v>
+      </c>
+      <c r="C24" s="13">
+        <v>0</v>
+      </c>
+      <c r="D24" s="13">
+        <v>0.409028</v>
+      </c>
+      <c r="E24" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B25" s="13">
+        <v>0</v>
+      </c>
+      <c r="C25" s="13">
+        <v>0</v>
+      </c>
+      <c r="D25" s="13">
+        <v>0</v>
+      </c>
+      <c r="E25" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B26" s="13">
+        <v>0</v>
+      </c>
+      <c r="C26" s="13">
+        <v>0.125</v>
+      </c>
+      <c r="D26" s="13">
+        <v>8.3334000000000005E-2</v>
+      </c>
+      <c r="E26" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="B27" s="13">
+        <v>0</v>
+      </c>
+      <c r="C27" s="13">
+        <v>0</v>
+      </c>
+      <c r="D27" s="13">
+        <v>0</v>
+      </c>
+      <c r="E27" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B28" s="13">
+        <v>0</v>
+      </c>
+      <c r="C28" s="13">
+        <v>0</v>
+      </c>
+      <c r="D28" s="13">
+        <v>0</v>
+      </c>
+      <c r="E28" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="B29" s="13">
+        <v>0</v>
+      </c>
+      <c r="C29" s="13">
+        <v>0.125</v>
+      </c>
+      <c r="D29" s="13">
+        <v>0.160417</v>
+      </c>
+      <c r="E29" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B30" s="13">
+        <v>0</v>
+      </c>
+      <c r="C30" s="13">
+        <v>0</v>
+      </c>
+      <c r="D30" s="13">
+        <v>0</v>
+      </c>
+      <c r="E30" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="B31" s="13">
+        <v>0</v>
+      </c>
+      <c r="C31" s="13">
+        <v>0</v>
+      </c>
+      <c r="D31" s="13">
+        <v>0</v>
+      </c>
+      <c r="E31" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="B32" s="13">
+        <v>0</v>
+      </c>
+      <c r="C32" s="13">
+        <v>0</v>
+      </c>
+      <c r="D32" s="13">
+        <v>0</v>
+      </c>
+      <c r="E32" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="B33" s="13">
+        <v>0</v>
+      </c>
+      <c r="C33" s="13">
+        <v>3.9584000000000001E-2</v>
+      </c>
+      <c r="D33" s="13">
+        <v>0</v>
+      </c>
+      <c r="E33" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="12">
-        <v>0</v>
-      </c>
-      <c r="C7" s="12">
-        <v>0</v>
-      </c>
-      <c r="D7" s="12">
-        <v>0</v>
-      </c>
-      <c r="E7" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="12">
-        <v>0</v>
-      </c>
-      <c r="C8" s="12">
-        <v>0</v>
-      </c>
-      <c r="D8" s="12">
-        <v>0</v>
-      </c>
-      <c r="E8" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="12">
-        <v>0</v>
-      </c>
-      <c r="C9" s="12">
-        <v>4.1667000000000003E-2</v>
-      </c>
-      <c r="D9" s="12">
-        <v>0</v>
-      </c>
-      <c r="E9" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="12">
-        <v>0</v>
-      </c>
-      <c r="C10" s="12">
-        <v>0</v>
-      </c>
-      <c r="D10" s="12">
-        <v>0</v>
-      </c>
-      <c r="E10" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="12">
-        <v>0</v>
-      </c>
-      <c r="C11" s="12">
-        <v>0</v>
-      </c>
-      <c r="D11" s="12">
-        <v>0</v>
-      </c>
-      <c r="E11" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="12">
-        <v>0</v>
-      </c>
-      <c r="C12" s="12">
-        <v>0</v>
-      </c>
-      <c r="D12" s="12">
-        <v>0</v>
-      </c>
-      <c r="E12" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="12">
-        <v>0</v>
-      </c>
-      <c r="C13" s="12">
-        <v>0</v>
-      </c>
-      <c r="D13" s="12">
-        <v>0</v>
-      </c>
-      <c r="E13" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B14" s="12">
-        <v>0</v>
-      </c>
-      <c r="C14" s="12">
-        <v>0</v>
-      </c>
-      <c r="D14" s="12">
-        <v>0</v>
-      </c>
-      <c r="E14" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="B15" s="12">
-        <v>0</v>
-      </c>
-      <c r="C15" s="12">
-        <v>0</v>
-      </c>
-      <c r="D15" s="12">
-        <v>0</v>
-      </c>
-      <c r="E15" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B16" s="12">
-        <v>0</v>
-      </c>
-      <c r="C16" s="12">
-        <v>0</v>
-      </c>
-      <c r="D16" s="12">
-        <v>0</v>
-      </c>
-      <c r="E16" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="B17" s="12">
-        <v>0</v>
-      </c>
-      <c r="C17" s="12">
-        <v>0</v>
-      </c>
-      <c r="D17" s="12">
-        <v>0</v>
-      </c>
-      <c r="E17" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="B18" s="12">
-        <v>0</v>
-      </c>
-      <c r="C18" s="12">
-        <v>0</v>
-      </c>
-      <c r="D18" s="12">
-        <v>0</v>
-      </c>
-      <c r="E18" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="B19" s="12">
-        <v>0</v>
-      </c>
-      <c r="C19" s="12">
-        <v>0</v>
-      </c>
-      <c r="D19" s="12">
-        <v>0</v>
-      </c>
-      <c r="E19" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="B20" s="12">
-        <v>0</v>
-      </c>
-      <c r="C20" s="12">
-        <v>0</v>
-      </c>
-      <c r="D20" s="12">
-        <v>0</v>
-      </c>
-      <c r="E20" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="B21" s="12">
-        <v>0</v>
-      </c>
-      <c r="C21" s="12">
-        <v>0.125</v>
-      </c>
-      <c r="D21" s="12">
-        <v>0</v>
-      </c>
-      <c r="E21" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="B22" s="12">
-        <v>0</v>
-      </c>
-      <c r="C22" s="12">
-        <v>0</v>
-      </c>
-      <c r="D22" s="12">
-        <v>0</v>
-      </c>
-      <c r="E22" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="B23" s="12">
-        <v>0</v>
-      </c>
-      <c r="C23" s="12">
-        <v>0.33333400000000002</v>
-      </c>
-      <c r="D23" s="12">
-        <v>0</v>
-      </c>
-      <c r="E23" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="B24" s="12">
-        <v>0</v>
-      </c>
-      <c r="C24" s="12">
-        <v>0</v>
-      </c>
-      <c r="D24" s="12">
-        <v>0.409028</v>
-      </c>
-      <c r="E24" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="B25" s="12">
-        <v>0</v>
-      </c>
-      <c r="C25" s="12">
-        <v>0</v>
-      </c>
-      <c r="D25" s="12">
-        <v>0</v>
-      </c>
-      <c r="E25" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="B26" s="12">
-        <v>0</v>
-      </c>
-      <c r="C26" s="12">
-        <v>0.125</v>
-      </c>
-      <c r="D26" s="12">
-        <v>8.3334000000000005E-2</v>
-      </c>
-      <c r="E26" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="B27" s="12">
-        <v>0</v>
-      </c>
-      <c r="C27" s="12">
-        <v>0</v>
-      </c>
-      <c r="D27" s="12">
-        <v>0</v>
-      </c>
-      <c r="E27" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="B28" s="12">
-        <v>0</v>
-      </c>
-      <c r="C28" s="12">
-        <v>0</v>
-      </c>
-      <c r="D28" s="12">
-        <v>0</v>
-      </c>
-      <c r="E28" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="B29" s="12">
-        <v>0</v>
-      </c>
-      <c r="C29" s="12">
-        <v>0.125</v>
-      </c>
-      <c r="D29" s="12">
-        <v>0.160417</v>
-      </c>
-      <c r="E29" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="B30" s="12">
-        <v>0</v>
-      </c>
-      <c r="C30" s="12">
-        <v>0</v>
-      </c>
-      <c r="D30" s="12">
-        <v>0</v>
-      </c>
-      <c r="E30" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="B31" s="12">
-        <v>0</v>
-      </c>
-      <c r="C31" s="12">
-        <v>0</v>
-      </c>
-      <c r="D31" s="12">
-        <v>0</v>
-      </c>
-      <c r="E31" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="B32" s="12">
-        <v>0</v>
-      </c>
-      <c r="C32" s="12">
-        <v>0</v>
-      </c>
-      <c r="D32" s="12">
-        <v>0</v>
-      </c>
-      <c r="E32" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="B33" s="12">
-        <v>0</v>
-      </c>
-      <c r="C33" s="12">
-        <v>3.9584000000000001E-2</v>
-      </c>
-      <c r="D33" s="12">
-        <v>0</v>
-      </c>
-      <c r="E33" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="B34" s="12">
-        <v>0</v>
-      </c>
-      <c r="C34" s="12">
-        <v>0</v>
-      </c>
-      <c r="D34" s="12">
-        <v>0</v>
-      </c>
-      <c r="E34" s="12">
+      <c r="B34" s="13">
+        <v>0</v>
+      </c>
+      <c r="C34" s="13">
+        <v>0</v>
+      </c>
+      <c r="D34" s="13">
+        <v>0</v>
+      </c>
+      <c r="E34" s="13">
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B35" s="13">
-        <v>0</v>
-      </c>
-      <c r="C35" s="13">
+      <c r="B35" s="14">
+        <v>0</v>
+      </c>
+      <c r="C35" s="14">
         <v>0.78958399999999995</v>
       </c>
-      <c r="D35" s="13">
+      <c r="D35" s="14">
         <v>0.652084</v>
       </c>
-      <c r="E35" s="13">
+      <c r="E35" s="14">
         <v>0</v>
       </c>
     </row>
@@ -8721,46 +8754,46 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="B4" s="16" t="s">
+      <c r="A4" s="16" t="s">
         <v>128</v>
       </c>
+      <c r="B4" s="17" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="B5" s="16"/>
+      <c r="A5" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="B5" s="17"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>101</v>
+      <c r="A6" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="B7" s="16" t="s">
+      <c r="A7" s="16" t="s">
         <v>132</v>
       </c>
+      <c r="B7" s="17" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="B8" s="16" t="s">
+      <c r="A8" s="16" t="s">
         <v>134</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -8935,13 +8968,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1F483C7-9028-4F57-B9B2-0A1FA1490184}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB3AB8D1-EFD8-42ED-B888-E3882B3017DA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C3B6EAD-CC4B-4575-B2E1-0204E1EA0456}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{699380AF-D041-452D-B127-91ACE396E067}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D1BC428-03DB-41A1-B8B5-2FAC2A2749FD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A74AE907-417C-4438-B3A7-48CF6B094F86}"/>
 </file>
--- a/Plannings 2026 S19.xlsx
+++ b/Plannings 2026 S19.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{84830FEF-CD99-488C-9111-90B341AA8F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA600701-563D-419E-AFCD-310519774913}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{84830FEF-CD99-488C-9111-90B341AA8F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E9CC753-6547-4148-989A-AAA1232D25F0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2759,50 +2759,6 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000032000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
       <xdr:row>40</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
@@ -6002,6 +5958,50 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1828800" y="6858000"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>124</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>124</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="125" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FEE2E840-DF84-4CBC-B6F4-0BF38063220A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3048000" y="12001500"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6380,7 +6380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H128"/>
+  <dimension ref="A1:H127"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6959,9 +6959,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
-      <c r="F39" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="F39" s="4"/>
       <c r="G39" s="4" t="s">
         <v>12</v>
       </c>
@@ -6975,9 +6973,7 @@
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
-      <c r="F40" s="3" t="s">
-        <v>64</v>
-      </c>
+      <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>13</v>
       </c>
@@ -8100,6 +8096,9 @@
         <v>12</v>
       </c>
       <c r="E125" s="3"/>
+      <c r="F125" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="G125" s="3"/>
       <c r="H125" s="3"/>
     </row>
@@ -8111,37 +8110,29 @@
         <v>82</v>
       </c>
       <c r="E126" s="3"/>
-      <c r="F126" s="3"/>
+      <c r="F126" s="3" t="s">
+        <v>64</v>
+      </c>
       <c r="G126" s="3"/>
       <c r="H126" s="3"/>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A127" s="18"/>
-      <c r="B127" s="5"/>
-      <c r="C127" s="5"/>
-      <c r="D127" s="5"/>
-      <c r="E127" s="5"/>
-      <c r="F127" s="5"/>
-      <c r="G127" s="5"/>
-      <c r="H127" s="5"/>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B128" s="19"/>
-      <c r="C128" s="19"/>
-      <c r="D128" s="19"/>
-      <c r="E128" s="19"/>
-      <c r="F128" s="19"/>
-      <c r="G128" s="19"/>
-      <c r="H128" s="19"/>
+      <c r="B127" s="19"/>
+      <c r="C127" s="19"/>
+      <c r="D127" s="19"/>
+      <c r="E127" s="19"/>
+      <c r="F127" s="19"/>
+      <c r="G127" s="19"/>
+      <c r="H127" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="B128:H128"/>
+    <mergeCell ref="B127:H127"/>
     <mergeCell ref="A107:A109"/>
     <mergeCell ref="A110:A114"/>
     <mergeCell ref="A115:A117"/>
     <mergeCell ref="A118:A124"/>
-    <mergeCell ref="A125:A127"/>
+    <mergeCell ref="A125:A126"/>
     <mergeCell ref="A78:A82"/>
     <mergeCell ref="A83:A91"/>
     <mergeCell ref="A92:A95"/>
@@ -8935,13 +8926,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1F483C7-9028-4F57-B9B2-0A1FA1490184}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E892E56B-4DB9-4737-87C8-68381ACFF402}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C3B6EAD-CC4B-4575-B2E1-0204E1EA0456}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB6A53DC-7929-40D2-9B98-EC353EFBC1E5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D1BC428-03DB-41A1-B8B5-2FAC2A2749FD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8A8CB62-EC1E-4BD8-BBB5-8A7D85090CA9}"/>
 </file>
--- a/Plannings 2026 S19.xlsx
+++ b/Plannings 2026 S19.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30015"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
@@ -17,16 +17,29 @@
     <sheet name="Résultats par salarié" sheetId="2" r:id="rId2"/>
     <sheet name="Informations" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="135">
   <si>
-    <t>Planning des salariés du 04/05/2026 au 10/05/2026</t>
-  </si>
-  <si>
     <t>Mai-2026</t>
   </si>
   <si>
@@ -216,46 +229,46 @@
     <t>08:30/17:45</t>
   </si>
   <si>
+    <t>DONAER Nicolas</t>
+  </si>
+  <si>
+    <t>REU</t>
+  </si>
+  <si>
+    <t>09:30/12:30</t>
+  </si>
+  <si>
+    <t>14:30/23:40</t>
+  </si>
+  <si>
+    <t>13:30/17:30</t>
+  </si>
+  <si>
+    <t>13:30/20:30</t>
+  </si>
+  <si>
+    <t>DOVINA Théo</t>
+  </si>
+  <si>
+    <t>FREIXEDAS-BERENGUER Maxime</t>
+  </si>
+  <si>
+    <t>HEBERT Jean Baptiste</t>
+  </si>
+  <si>
+    <t>JARGUEL Thomas</t>
+  </si>
+  <si>
+    <t>KABUNDA NDEKE Marvyn</t>
+  </si>
+  <si>
+    <t>19:30/22:30</t>
+  </si>
+  <si>
+    <t>LABEFODE Thomas</t>
+  </si>
+  <si>
     <t>17:15/19:15</t>
-  </si>
-  <si>
-    <t>DONAER Nicolas</t>
-  </si>
-  <si>
-    <t>REU</t>
-  </si>
-  <si>
-    <t>09:30/12:30</t>
-  </si>
-  <si>
-    <t>14:30/23:40</t>
-  </si>
-  <si>
-    <t>13:30/17:30</t>
-  </si>
-  <si>
-    <t>13:30/20:30</t>
-  </si>
-  <si>
-    <t>DOVINA Théo</t>
-  </si>
-  <si>
-    <t>FREIXEDAS-BERENGUER Maxime</t>
-  </si>
-  <si>
-    <t>HEBERT Jean Baptiste</t>
-  </si>
-  <si>
-    <t>JARGUEL Thomas</t>
-  </si>
-  <si>
-    <t>KABUNDA NDEKE Marvyn</t>
-  </si>
-  <si>
-    <t>19:30/22:30</t>
-  </si>
-  <si>
-    <t>LABEFODE Thomas</t>
   </si>
   <si>
     <t>LOUIBA Yacine</t>
@@ -387,6 +400,9 @@
   </si>
   <si>
     <t>VASSANT Tiffany</t>
+  </si>
+  <si>
+    <t>Planning des salariés du 04/05/2026 au 10/05/2026</t>
   </si>
   <si>
     <t>Jour de référence : 10/05/2026</t>
@@ -438,7 +454,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[h]:mm"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -475,51 +491,12 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Helvetica"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Helvetica"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Helvetica"/>
     </font>
     <font>
       <b/>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Helvetica"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Helvetica"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Helvetica"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Helvetica"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Helvetica"/>
-    </font>
-    <font>
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Helvetica"/>
@@ -603,7 +580,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -629,31 +606,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -662,11 +615,29 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6381,103 +6352,103 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H127"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B1" s="17" t="s">
+    <row r="1" spans="1:8">
+      <c r="B1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="B2" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="17" t="s">
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="12" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>11</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="G4" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="18"/>
+    <row r="5" spans="1:8">
+      <c r="A5" s="12"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="3"/>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="3"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
+      <c r="B6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="C6" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="18"/>
+    <row r="7" spans="1:8">
+      <c r="A7" s="12"/>
       <c r="B7" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -6485,133 +6456,133 @@
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
+    <row r="8" spans="1:8">
+      <c r="A8" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>18</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="18"/>
+    <row r="9" spans="1:8">
+      <c r="A9" s="12"/>
       <c r="B9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="18"/>
+    <row r="10" spans="1:8">
+      <c r="A10" s="12"/>
       <c r="B10" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="18"/>
+    <row r="11" spans="1:8">
+      <c r="A11" s="12"/>
       <c r="B11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="18"/>
+    <row r="12" spans="1:8">
+      <c r="A12" s="12"/>
       <c r="B12" s="3"/>
       <c r="C12" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="18"/>
+    <row r="13" spans="1:8">
+      <c r="A13" s="12"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>29</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="18"/>
+    <row r="14" spans="1:8">
+      <c r="A14" s="12"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="18"/>
+    <row r="15" spans="1:8">
+      <c r="A15" s="12"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="18"/>
+    <row r="16" spans="1:8">
+      <c r="A16" s="12"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
@@ -6620,33 +6591,33 @@
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
-        <v>31</v>
+    <row r="17" spans="1:8">
+      <c r="A17" s="12" t="s">
+        <v>30</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="18"/>
+    <row r="18" spans="1:8">
+      <c r="A18" s="12"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="18"/>
+    <row r="19" spans="1:8">
+      <c r="A19" s="12"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
@@ -6655,37 +6626,37 @@
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="18" t="s">
-        <v>33</v>
+    <row r="20" spans="1:8">
+      <c r="A20" s="12" t="s">
+        <v>32</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="18"/>
+    <row r="21" spans="1:8">
+      <c r="A21" s="12"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="18"/>
+    <row r="22" spans="1:8">
+      <c r="A22" s="12"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
@@ -6694,73 +6665,73 @@
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="18" t="s">
-        <v>34</v>
+    <row r="23" spans="1:8">
+      <c r="A23" s="12" t="s">
+        <v>33</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="18"/>
+    <row r="24" spans="1:8">
+      <c r="A24" s="12"/>
       <c r="B24" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="18"/>
+    <row r="25" spans="1:8">
+      <c r="A25" s="12"/>
       <c r="B25" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="18"/>
+    <row r="26" spans="1:8">
+      <c r="A26" s="12"/>
       <c r="B26" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C26" s="3"/>
       <c r="D26" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="18"/>
+    <row r="27" spans="1:8">
+      <c r="A27" s="12"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
@@ -6769,41 +6740,41 @@
       <c r="G27" s="5"/>
       <c r="H27" s="5"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="18" t="s">
-        <v>40</v>
+    <row r="28" spans="1:8">
+      <c r="A28" s="12" t="s">
+        <v>39</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E28" s="3"/>
       <c r="G28" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H28" s="3"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="18"/>
+    <row r="29" spans="1:8">
+      <c r="A29" s="12"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H29" s="3"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="18"/>
+    <row r="30" spans="1:8">
+      <c r="A30" s="12"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
@@ -6812,175 +6783,175 @@
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="18" t="s">
+    <row r="31" spans="1:8">
+      <c r="A31" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B31" s="4" t="s">
-        <v>45</v>
-      </c>
       <c r="C31" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="18"/>
+    <row r="32" spans="1:8">
+      <c r="A32" s="12"/>
       <c r="B32" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="D32" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="E32" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="18"/>
+    <row r="33" spans="1:8">
+      <c r="A33" s="12"/>
       <c r="B33" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C33" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="D33" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="18"/>
+    <row r="34" spans="1:8">
+      <c r="A34" s="12"/>
       <c r="B34" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="D34" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="E34" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="18"/>
+    <row r="35" spans="1:8">
+      <c r="A35" s="12"/>
       <c r="B35" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="18"/>
+    <row r="36" spans="1:8">
+      <c r="A36" s="12"/>
       <c r="B36" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="D36" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="18"/>
+    <row r="37" spans="1:8">
+      <c r="A37" s="12"/>
       <c r="B37" s="3"/>
       <c r="C37" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="18"/>
+    <row r="38" spans="1:8">
+      <c r="A38" s="12"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="18" t="s">
+    <row r="39" spans="1:8">
+      <c r="A39" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B39" s="4" t="s">
         <v>61</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>62</v>
       </c>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="4"/>
       <c r="G39" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H39" s="3"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="18"/>
+    <row r="40" spans="1:8">
+      <c r="A40" s="12"/>
       <c r="B40" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H40" s="3"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="18"/>
+    <row r="41" spans="1:8">
+      <c r="A41" s="12"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
@@ -6988,8 +6959,8 @@
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="18"/>
+    <row r="42" spans="1:8">
+      <c r="A42" s="12"/>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
       <c r="D42" s="5"/>
@@ -6998,86 +6969,86 @@
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="18" t="s">
-        <v>65</v>
+    <row r="43" spans="1:8">
+      <c r="A43" s="12" t="s">
+        <v>63</v>
       </c>
       <c r="B43" s="3"/>
       <c r="C43" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="18"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="12"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G44" s="3"/>
       <c r="H44" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="18"/>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="12"/>
       <c r="B45" s="3"/>
       <c r="C45" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="18"/>
+    <row r="46" spans="1:8">
+      <c r="A46" s="12"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="18"/>
+    <row r="47" spans="1:8">
+      <c r="A47" s="12"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
@@ -7085,8 +7056,8 @@
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="18"/>
+    <row r="48" spans="1:8">
+      <c r="A48" s="12"/>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
       <c r="D48" s="5"/>
@@ -7095,33 +7066,33 @@
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="18" t="s">
-        <v>71</v>
+    <row r="49" spans="1:8">
+      <c r="A49" s="12" t="s">
+        <v>69</v>
       </c>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="18"/>
+    <row r="50" spans="1:8">
+      <c r="A50" s="12"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
       <c r="E50" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="18"/>
+    <row r="51" spans="1:8">
+      <c r="A51" s="12"/>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
       <c r="D51" s="5"/>
@@ -7130,9 +7101,9 @@
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="18" t="s">
-        <v>72</v>
+    <row r="52" spans="1:8">
+      <c r="A52" s="12" t="s">
+        <v>70</v>
       </c>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -7141,8 +7112,8 @@
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="18"/>
+    <row r="53" spans="1:8">
+      <c r="A53" s="12"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
@@ -7151,8 +7122,8 @@
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="18"/>
+    <row r="54" spans="1:8">
+      <c r="A54" s="12"/>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
       <c r="D54" s="5"/>
@@ -7161,9 +7132,9 @@
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="18" t="s">
-        <v>73</v>
+    <row r="55" spans="1:8">
+      <c r="A55" s="12" t="s">
+        <v>71</v>
       </c>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -7172,8 +7143,8 @@
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="18"/>
+    <row r="56" spans="1:8">
+      <c r="A56" s="12"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
@@ -7182,8 +7153,8 @@
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="18"/>
+    <row r="57" spans="1:8">
+      <c r="A57" s="12"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
       <c r="D57" s="5"/>
@@ -7192,9 +7163,9 @@
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="18" t="s">
-        <v>74</v>
+    <row r="58" spans="1:8">
+      <c r="A58" s="12" t="s">
+        <v>72</v>
       </c>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -7203,8 +7174,8 @@
       <c r="G58" s="3"/>
       <c r="H58" s="3"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="18"/>
+    <row r="59" spans="1:8">
+      <c r="A59" s="12"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
@@ -7213,8 +7184,8 @@
       <c r="G59" s="3"/>
       <c r="H59" s="3"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="18"/>
+    <row r="60" spans="1:8">
+      <c r="A60" s="12"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
       <c r="D60" s="5"/>
@@ -7223,33 +7194,33 @@
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="18" t="s">
-        <v>75</v>
+    <row r="61" spans="1:8">
+      <c r="A61" s="12" t="s">
+        <v>73</v>
       </c>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
       <c r="D61" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E61" s="3"/>
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="18"/>
+    <row r="62" spans="1:8">
+      <c r="A62" s="12"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
       <c r="D62" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
       <c r="G62" s="3"/>
       <c r="H62" s="3"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="18"/>
+    <row r="63" spans="1:8">
+      <c r="A63" s="12"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
       <c r="D63" s="5"/>
@@ -7258,34 +7229,34 @@
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="18" t="s">
-        <v>77</v>
+    <row r="64" spans="1:8">
+      <c r="A64" s="12" t="s">
+        <v>75</v>
       </c>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
       <c r="F64" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G64" s="3"/>
       <c r="H64" s="3"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="18"/>
+    <row r="65" spans="1:8">
+      <c r="A65" s="12"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
       <c r="F65" s="3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="G65" s="3"/>
       <c r="H65" s="3"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="18"/>
+    <row r="66" spans="1:8">
+      <c r="A66" s="12"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
@@ -7293,8 +7264,8 @@
       <c r="G66" s="3"/>
       <c r="H66" s="3"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="18"/>
+    <row r="67" spans="1:8">
+      <c r="A67" s="12"/>
       <c r="B67" s="5"/>
       <c r="C67" s="5"/>
       <c r="D67" s="5"/>
@@ -7303,41 +7274,41 @@
       <c r="G67" s="5"/>
       <c r="H67" s="5"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="18" t="s">
-        <v>78</v>
+    <row r="68" spans="1:8">
+      <c r="A68" s="12" t="s">
+        <v>77</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E68" s="3"/>
       <c r="G68" s="3"/>
       <c r="H68" s="3"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="18"/>
+    <row r="69" spans="1:8">
+      <c r="A69" s="12"/>
       <c r="B69" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
       <c r="G69" s="3"/>
       <c r="H69" s="3"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="18"/>
+    <row r="70" spans="1:8">
+      <c r="A70" s="12"/>
       <c r="B70" s="5"/>
       <c r="C70" s="5"/>
       <c r="D70" s="5"/>
@@ -7346,65 +7317,65 @@
       <c r="G70" s="5"/>
       <c r="H70" s="5"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="18" t="s">
-        <v>80</v>
+    <row r="71" spans="1:8">
+      <c r="A71" s="12" t="s">
+        <v>79</v>
       </c>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
       <c r="G71" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="18"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="12"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H72" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="18"/>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="12"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
       <c r="G73" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="18"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" s="12"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="H74" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="H74" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="18"/>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" s="12"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
@@ -7412,11 +7383,11 @@
       <c r="F75" s="3"/>
       <c r="G75" s="3"/>
       <c r="H75" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="18"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" s="12"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
@@ -7424,11 +7395,11 @@
       <c r="F76" s="3"/>
       <c r="G76" s="3"/>
       <c r="H76" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="18"/>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" s="12"/>
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
       <c r="D77" s="5"/>
@@ -7437,82 +7408,82 @@
       <c r="G77" s="5"/>
       <c r="H77" s="5"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="18" t="s">
+    <row r="78" spans="1:8">
+      <c r="A78" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B78" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="B78" s="6" t="s">
+      <c r="C78" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="G78" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="H78" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" s="12"/>
+      <c r="B79" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="C78" s="6" t="s">
+      <c r="C79" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="D78" s="6" t="s">
+      <c r="D79" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="E78" s="6" t="s">
+      <c r="E79" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="F78" s="6" t="s">
+      <c r="F79" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G78" s="6" t="s">
+      <c r="G79" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="H78" s="6" t="s">
+      <c r="H79" s="7" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="18"/>
-      <c r="B79" s="7" t="s">
+    <row r="80" spans="1:8">
+      <c r="A80" s="12"/>
+      <c r="B80" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C79" s="7" t="s">
+      <c r="C80" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="D79" s="7" t="s">
+      <c r="D80" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="E79" s="7" t="s">
+      <c r="E80" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="F79" s="7" t="s">
+      <c r="F80" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="G79" s="7" t="s">
+      <c r="G80" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="H79" s="7" t="s">
+      <c r="H80" s="7" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="18"/>
-      <c r="B80" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C80" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D80" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="E80" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="F80" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="G80" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="H80" s="7" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="18"/>
+    <row r="81" spans="1:8">
+      <c r="A81" s="12"/>
       <c r="B81" s="7"/>
       <c r="C81" s="7"/>
       <c r="D81" s="7"/>
@@ -7520,8 +7491,8 @@
       <c r="G81" s="7"/>
       <c r="H81" s="7"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="18"/>
+    <row r="82" spans="1:8">
+      <c r="A82" s="12"/>
       <c r="B82" s="5"/>
       <c r="C82" s="5"/>
       <c r="D82" s="5"/>
@@ -7530,137 +7501,137 @@
       <c r="G82" s="5"/>
       <c r="H82" s="5"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="18" t="s">
-        <v>90</v>
+    <row r="83" spans="1:8">
+      <c r="A83" s="12" t="s">
+        <v>89</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E83" s="3"/>
       <c r="F83" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H83" s="3"/>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84" s="12"/>
+      <c r="B84" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D84" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="G83" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H83" s="3"/>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="18"/>
-      <c r="B84" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>92</v>
       </c>
       <c r="E84" s="3"/>
       <c r="F84" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H84" s="3"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="18"/>
+    <row r="85" spans="1:8">
+      <c r="A85" s="12"/>
       <c r="B85" s="3"/>
       <c r="C85" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E85" s="3"/>
       <c r="G85" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H85" s="3"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="18"/>
+    <row r="86" spans="1:8">
+      <c r="A86" s="12"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H86" s="3"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="18"/>
+    <row r="87" spans="1:8">
+      <c r="A87" s="12"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
       <c r="D87" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
       <c r="G87" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H87" s="3"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="18"/>
+    <row r="88" spans="1:8">
+      <c r="A88" s="12"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
       <c r="D88" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H88" s="3"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="18"/>
+    <row r="89" spans="1:8">
+      <c r="A89" s="12"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
       <c r="D89" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
       <c r="G89" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H89" s="3"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="18"/>
+    <row r="90" spans="1:8">
+      <c r="A90" s="12"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
       <c r="D90" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H90" s="3"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="18"/>
+    <row r="91" spans="1:8">
+      <c r="A91" s="12"/>
       <c r="B91" s="5"/>
       <c r="C91" s="5"/>
       <c r="D91" s="5"/>
@@ -7669,42 +7640,42 @@
       <c r="G91" s="5"/>
       <c r="H91" s="5"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="18" t="s">
-        <v>100</v>
+    <row r="92" spans="1:8">
+      <c r="A92" s="12" t="s">
+        <v>99</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
       <c r="F92" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G92" s="3"/>
       <c r="H92" s="3"/>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="18"/>
+    <row r="93" spans="1:8">
+      <c r="A93" s="12"/>
       <c r="B93" s="3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="G93" s="3"/>
       <c r="H93" s="3"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="18"/>
+    <row r="94" spans="1:8">
+      <c r="A94" s="12"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
@@ -7712,8 +7683,8 @@
       <c r="G94" s="3"/>
       <c r="H94" s="3"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="18"/>
+    <row r="95" spans="1:8">
+      <c r="A95" s="12"/>
       <c r="B95" s="5"/>
       <c r="C95" s="5"/>
       <c r="D95" s="5"/>
@@ -7722,78 +7693,78 @@
       <c r="G95" s="5"/>
       <c r="H95" s="5"/>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A96" s="18" t="s">
-        <v>101</v>
+    <row r="96" spans="1:8">
+      <c r="A96" s="12" t="s">
+        <v>100</v>
       </c>
       <c r="B96" s="3"/>
       <c r="C96" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D96" s="3"/>
       <c r="E96" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="18"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" s="12"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D97" s="3"/>
       <c r="E97" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F97" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="F97" s="3" t="s">
+      <c r="G97" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="G97" s="3" t="s">
+      <c r="H97" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="H97" s="3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A98" s="18"/>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98" s="12"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
       <c r="F98" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H98" s="3"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" s="18"/>
+    <row r="99" spans="1:8">
+      <c r="A99" s="12"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
       <c r="F99" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G99" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="G99" s="3" t="s">
-        <v>108</v>
-      </c>
       <c r="H99" s="3"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" s="18"/>
+    <row r="100" spans="1:8">
+      <c r="A100" s="12"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
@@ -7801,8 +7772,8 @@
       <c r="G100" s="3"/>
       <c r="H100" s="3"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101" s="18"/>
+    <row r="101" spans="1:8">
+      <c r="A101" s="12"/>
       <c r="B101" s="5"/>
       <c r="C101" s="5"/>
       <c r="D101" s="5"/>
@@ -7811,25 +7782,25 @@
       <c r="G101" s="5"/>
       <c r="H101" s="5"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A102" s="18" t="s">
-        <v>109</v>
+    <row r="102" spans="1:8">
+      <c r="A102" s="12" t="s">
+        <v>108</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
       <c r="G102" s="3"/>
       <c r="H102" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A103" s="18"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
+      <c r="A103" s="12"/>
       <c r="B103" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
@@ -7837,11 +7808,11 @@
       <c r="F103" s="3"/>
       <c r="G103" s="3"/>
       <c r="H103" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A104" s="18"/>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
+      <c r="A104" s="12"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
@@ -7849,11 +7820,11 @@
       <c r="F104" s="3"/>
       <c r="G104" s="3"/>
       <c r="H104" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A105" s="18"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
+      <c r="A105" s="12"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
@@ -7861,11 +7832,11 @@
       <c r="F105" s="3"/>
       <c r="G105" s="3"/>
       <c r="H105" s="3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A106" s="18"/>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
+      <c r="A106" s="12"/>
       <c r="B106" s="5"/>
       <c r="C106" s="5"/>
       <c r="D106" s="5"/>
@@ -7874,33 +7845,33 @@
       <c r="G106" s="5"/>
       <c r="H106" s="5"/>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A107" s="18" t="s">
-        <v>111</v>
+    <row r="107" spans="1:8">
+      <c r="A107" s="12" t="s">
+        <v>110</v>
       </c>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
       <c r="D107" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E107" s="3"/>
       <c r="G107" s="3"/>
       <c r="H107" s="3"/>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A108" s="18"/>
+    <row r="108" spans="1:8">
+      <c r="A108" s="12"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
       <c r="D108" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E108" s="3"/>
       <c r="F108" s="3"/>
       <c r="G108" s="3"/>
       <c r="H108" s="3"/>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A109" s="18"/>
+    <row r="109" spans="1:8">
+      <c r="A109" s="12"/>
       <c r="B109" s="5"/>
       <c r="C109" s="5"/>
       <c r="D109" s="5"/>
@@ -7909,57 +7880,57 @@
       <c r="G109" s="5"/>
       <c r="H109" s="5"/>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A110" s="18" t="s">
-        <v>112</v>
+    <row r="110" spans="1:8">
+      <c r="A110" s="12" t="s">
+        <v>111</v>
       </c>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
       <c r="E110" s="3"/>
       <c r="G110" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H110" s="3"/>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A111" s="18"/>
+    <row r="111" spans="1:8">
+      <c r="A111" s="12"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
       <c r="D111" s="3"/>
       <c r="E111" s="3"/>
       <c r="F111" s="3"/>
       <c r="G111" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H111" s="3"/>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A112" s="18"/>
+    <row r="112" spans="1:8">
+      <c r="A112" s="12"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
       <c r="F112" s="3"/>
       <c r="G112" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H112" s="3"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A113" s="18"/>
+    <row r="113" spans="1:8">
+      <c r="A113" s="12"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
       <c r="E113" s="3"/>
       <c r="F113" s="3"/>
       <c r="G113" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H113" s="3"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A114" s="18"/>
+    <row r="114" spans="1:8">
+      <c r="A114" s="12"/>
       <c r="B114" s="5"/>
       <c r="C114" s="5"/>
       <c r="D114" s="5"/>
@@ -7968,9 +7939,9 @@
       <c r="G114" s="5"/>
       <c r="H114" s="5"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A115" s="18" t="s">
-        <v>114</v>
+    <row r="115" spans="1:8">
+      <c r="A115" s="12" t="s">
+        <v>113</v>
       </c>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
@@ -7979,8 +7950,8 @@
       <c r="G115" s="3"/>
       <c r="H115" s="3"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A116" s="18"/>
+    <row r="116" spans="1:8">
+      <c r="A116" s="12"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
@@ -7989,8 +7960,8 @@
       <c r="G116" s="3"/>
       <c r="H116" s="3"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A117" s="18"/>
+    <row r="117" spans="1:8">
+      <c r="A117" s="12"/>
       <c r="B117" s="5"/>
       <c r="C117" s="5"/>
       <c r="D117" s="5"/>
@@ -7999,40 +7970,40 @@
       <c r="G117" s="5"/>
       <c r="H117" s="5"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A118" s="18" t="s">
-        <v>115</v>
+    <row r="118" spans="1:8">
+      <c r="A118" s="12" t="s">
+        <v>114</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
       <c r="E118" s="3"/>
       <c r="F118" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G118" s="3"/>
       <c r="H118" s="3"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A119" s="18"/>
+    <row r="119" spans="1:8">
+      <c r="A119" s="12"/>
       <c r="B119" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C119" s="3"/>
       <c r="D119" s="3"/>
       <c r="E119" s="3"/>
       <c r="F119" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G119" s="3"/>
       <c r="H119" s="3"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A120" s="18"/>
+    <row r="120" spans="1:8">
+      <c r="A120" s="12"/>
       <c r="B120" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
@@ -8040,10 +8011,10 @@
       <c r="G120" s="3"/>
       <c r="H120" s="3"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A121" s="18"/>
+    <row r="121" spans="1:8">
+      <c r="A121" s="12"/>
       <c r="B121" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
@@ -8052,10 +8023,10 @@
       <c r="G121" s="3"/>
       <c r="H121" s="3"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A122" s="18"/>
+    <row r="122" spans="1:8">
+      <c r="A122" s="12"/>
       <c r="B122" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
@@ -8064,10 +8035,10 @@
       <c r="G122" s="3"/>
       <c r="H122" s="3"/>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A123" s="18"/>
+    <row r="123" spans="1:8">
+      <c r="A123" s="12"/>
       <c r="B123" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
@@ -8076,8 +8047,8 @@
       <c r="G123" s="3"/>
       <c r="H123" s="3"/>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A124" s="18"/>
+    <row r="124" spans="1:8">
+      <c r="A124" s="12"/>
       <c r="B124" s="5"/>
       <c r="C124" s="5"/>
       <c r="D124" s="5"/>
@@ -8086,78 +8057,78 @@
       <c r="G124" s="5"/>
       <c r="H124" s="5"/>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A125" s="18" t="s">
-        <v>120</v>
+    <row r="125" spans="1:8">
+      <c r="A125" s="12" t="s">
+        <v>119</v>
       </c>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
       <c r="D125" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E125" s="3"/>
       <c r="F125" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G125" s="3"/>
       <c r="H125" s="3"/>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A126" s="18"/>
+    <row r="126" spans="1:8">
+      <c r="A126" s="12"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
       <c r="D126" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E126" s="3"/>
       <c r="F126" s="3" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="G126" s="3"/>
       <c r="H126" s="3"/>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B127" s="19"/>
-      <c r="C127" s="19"/>
-      <c r="D127" s="19"/>
-      <c r="E127" s="19"/>
-      <c r="F127" s="19"/>
-      <c r="G127" s="19"/>
-      <c r="H127" s="19"/>
+    <row r="127" spans="1:8">
+      <c r="B127" s="11"/>
+      <c r="C127" s="11"/>
+      <c r="D127" s="11"/>
+      <c r="E127" s="11"/>
+      <c r="F127" s="11"/>
+      <c r="G127" s="11"/>
+      <c r="H127" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A16"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="A23:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A31:A38"/>
+    <mergeCell ref="A39:A42"/>
+    <mergeCell ref="A43:A48"/>
+    <mergeCell ref="A49:A51"/>
+    <mergeCell ref="A52:A54"/>
+    <mergeCell ref="A55:A57"/>
+    <mergeCell ref="A58:A60"/>
+    <mergeCell ref="A61:A63"/>
+    <mergeCell ref="A64:A67"/>
+    <mergeCell ref="A68:A70"/>
+    <mergeCell ref="A71:A77"/>
+    <mergeCell ref="A78:A82"/>
+    <mergeCell ref="A83:A91"/>
+    <mergeCell ref="A92:A95"/>
+    <mergeCell ref="A96:A101"/>
+    <mergeCell ref="A102:A106"/>
     <mergeCell ref="B127:H127"/>
     <mergeCell ref="A107:A109"/>
     <mergeCell ref="A110:A114"/>
     <mergeCell ref="A115:A117"/>
     <mergeCell ref="A118:A124"/>
     <mergeCell ref="A125:A126"/>
-    <mergeCell ref="A78:A82"/>
-    <mergeCell ref="A83:A91"/>
-    <mergeCell ref="A92:A95"/>
-    <mergeCell ref="A96:A101"/>
-    <mergeCell ref="A102:A106"/>
-    <mergeCell ref="A58:A60"/>
-    <mergeCell ref="A61:A63"/>
-    <mergeCell ref="A64:A67"/>
-    <mergeCell ref="A68:A70"/>
-    <mergeCell ref="A71:A77"/>
-    <mergeCell ref="A39:A42"/>
-    <mergeCell ref="A43:A48"/>
-    <mergeCell ref="A49:A51"/>
-    <mergeCell ref="A52:A54"/>
-    <mergeCell ref="A55:A57"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="A20:A22"/>
-    <mergeCell ref="A23:A27"/>
-    <mergeCell ref="A28:A30"/>
-    <mergeCell ref="A31:A38"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -8167,533 +8138,533 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15.75">
       <c r="A1" s="8" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="20" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="B4" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="21" t="s">
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="B5" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="11" t="s">
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="9" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5">
       <c r="A7" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="12">
-        <v>0</v>
-      </c>
-      <c r="C7" s="12">
-        <v>0</v>
-      </c>
-      <c r="D7" s="12">
-        <v>0</v>
-      </c>
-      <c r="E7" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="B7" s="16">
+        <v>0</v>
+      </c>
+      <c r="C7" s="16">
+        <v>0</v>
+      </c>
+      <c r="D7" s="16">
+        <v>0</v>
+      </c>
+      <c r="E7" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="12">
-        <v>0</v>
-      </c>
-      <c r="C8" s="12">
-        <v>0</v>
-      </c>
-      <c r="D8" s="12">
-        <v>0</v>
-      </c>
-      <c r="E8" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="B8" s="16">
+        <v>0</v>
+      </c>
+      <c r="C8" s="16">
+        <v>0</v>
+      </c>
+      <c r="D8" s="16">
+        <v>0</v>
+      </c>
+      <c r="E8" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="12">
-        <v>0</v>
-      </c>
-      <c r="C9" s="12">
+        <v>16</v>
+      </c>
+      <c r="B9" s="16">
+        <v>0</v>
+      </c>
+      <c r="C9" s="16">
         <v>4.1667000000000003E-2</v>
       </c>
-      <c r="D9" s="12">
-        <v>0</v>
-      </c>
-      <c r="E9" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D9" s="16">
+        <v>0</v>
+      </c>
+      <c r="E9" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="12">
-        <v>0</v>
-      </c>
-      <c r="C10" s="12">
-        <v>0</v>
-      </c>
-      <c r="D10" s="12">
-        <v>0</v>
-      </c>
-      <c r="E10" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="B10" s="16">
+        <v>0</v>
+      </c>
+      <c r="C10" s="16">
+        <v>0</v>
+      </c>
+      <c r="D10" s="16">
+        <v>0</v>
+      </c>
+      <c r="E10" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="16">
+        <v>0</v>
+      </c>
+      <c r="C11" s="16">
+        <v>0</v>
+      </c>
+      <c r="D11" s="16">
+        <v>0</v>
+      </c>
+      <c r="E11" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="12">
-        <v>0</v>
-      </c>
-      <c r="C11" s="12">
-        <v>0</v>
-      </c>
-      <c r="D11" s="12">
-        <v>0</v>
-      </c>
-      <c r="E11" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="12">
-        <v>0</v>
-      </c>
-      <c r="C12" s="12">
-        <v>0</v>
-      </c>
-      <c r="D12" s="12">
-        <v>0</v>
-      </c>
-      <c r="E12" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B12" s="16">
+        <v>0</v>
+      </c>
+      <c r="C12" s="16">
+        <v>0</v>
+      </c>
+      <c r="D12" s="16">
+        <v>0</v>
+      </c>
+      <c r="E12" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="12">
-        <v>0</v>
-      </c>
-      <c r="C13" s="12">
-        <v>0</v>
-      </c>
-      <c r="D13" s="12">
-        <v>0</v>
-      </c>
-      <c r="E13" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="B13" s="16">
+        <v>0</v>
+      </c>
+      <c r="C13" s="16">
+        <v>0</v>
+      </c>
+      <c r="D13" s="16">
+        <v>0</v>
+      </c>
+      <c r="E13" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B14" s="12">
-        <v>0</v>
-      </c>
-      <c r="C14" s="12">
-        <v>0</v>
-      </c>
-      <c r="D14" s="12">
-        <v>0</v>
-      </c>
-      <c r="E14" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+      <c r="B14" s="16">
+        <v>0</v>
+      </c>
+      <c r="C14" s="16">
+        <v>0</v>
+      </c>
+      <c r="D14" s="16">
+        <v>0</v>
+      </c>
+      <c r="E14" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="B15" s="12">
-        <v>0</v>
-      </c>
-      <c r="C15" s="12">
-        <v>0</v>
-      </c>
-      <c r="D15" s="12">
-        <v>0</v>
-      </c>
-      <c r="E15" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+      <c r="B15" s="16">
+        <v>0</v>
+      </c>
+      <c r="C15" s="16">
+        <v>0</v>
+      </c>
+      <c r="D15" s="16">
+        <v>0</v>
+      </c>
+      <c r="E15" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B16" s="12">
-        <v>0</v>
-      </c>
-      <c r="C16" s="12">
-        <v>0</v>
-      </c>
-      <c r="D16" s="12">
-        <v>0</v>
-      </c>
-      <c r="E16" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+      <c r="B16" s="16">
+        <v>0</v>
+      </c>
+      <c r="C16" s="16">
+        <v>0</v>
+      </c>
+      <c r="D16" s="16">
+        <v>0</v>
+      </c>
+      <c r="E16" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="16">
+        <v>0</v>
+      </c>
+      <c r="C17" s="16">
+        <v>0</v>
+      </c>
+      <c r="D17" s="16">
+        <v>0</v>
+      </c>
+      <c r="E17" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" s="16">
+        <v>0</v>
+      </c>
+      <c r="C18" s="16">
+        <v>0</v>
+      </c>
+      <c r="D18" s="16">
+        <v>0</v>
+      </c>
+      <c r="E18" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="B17" s="12">
-        <v>0</v>
-      </c>
-      <c r="C17" s="12">
-        <v>0</v>
-      </c>
-      <c r="D17" s="12">
-        <v>0</v>
-      </c>
-      <c r="E17" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
+      <c r="B19" s="16">
+        <v>0</v>
+      </c>
+      <c r="C19" s="16">
+        <v>0</v>
+      </c>
+      <c r="D19" s="16">
+        <v>0</v>
+      </c>
+      <c r="E19" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="B18" s="12">
-        <v>0</v>
-      </c>
-      <c r="C18" s="12">
-        <v>0</v>
-      </c>
-      <c r="D18" s="12">
-        <v>0</v>
-      </c>
-      <c r="E18" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
+      <c r="B20" s="16">
+        <v>0</v>
+      </c>
+      <c r="C20" s="16">
+        <v>0</v>
+      </c>
+      <c r="D20" s="16">
+        <v>0</v>
+      </c>
+      <c r="E20" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B19" s="12">
-        <v>0</v>
-      </c>
-      <c r="C19" s="12">
-        <v>0</v>
-      </c>
-      <c r="D19" s="12">
-        <v>0</v>
-      </c>
-      <c r="E19" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="B20" s="12">
-        <v>0</v>
-      </c>
-      <c r="C20" s="12">
-        <v>0</v>
-      </c>
-      <c r="D20" s="12">
-        <v>0</v>
-      </c>
-      <c r="E20" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
+      <c r="B21" s="16">
+        <v>0</v>
+      </c>
+      <c r="C21" s="16">
+        <v>0.125</v>
+      </c>
+      <c r="D21" s="16">
+        <v>0</v>
+      </c>
+      <c r="E21" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B21" s="12">
-        <v>0</v>
-      </c>
-      <c r="C21" s="12">
+      <c r="B22" s="16">
+        <v>0</v>
+      </c>
+      <c r="C22" s="16">
+        <v>0</v>
+      </c>
+      <c r="D22" s="16">
+        <v>0</v>
+      </c>
+      <c r="E22" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" s="16">
+        <v>0</v>
+      </c>
+      <c r="C23" s="16">
+        <v>0.33333400000000002</v>
+      </c>
+      <c r="D23" s="16">
+        <v>0</v>
+      </c>
+      <c r="E23" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="B24" s="16">
+        <v>0</v>
+      </c>
+      <c r="C24" s="16">
+        <v>0</v>
+      </c>
+      <c r="D24" s="16">
+        <v>0.409028</v>
+      </c>
+      <c r="E24" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B25" s="16">
+        <v>0</v>
+      </c>
+      <c r="C25" s="16">
+        <v>0</v>
+      </c>
+      <c r="D25" s="16">
+        <v>0</v>
+      </c>
+      <c r="E25" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B26" s="16">
+        <v>0</v>
+      </c>
+      <c r="C26" s="16">
         <v>0.125</v>
       </c>
-      <c r="D21" s="12">
-        <v>0</v>
-      </c>
-      <c r="E21" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="B22" s="12">
-        <v>0</v>
-      </c>
-      <c r="C22" s="12">
-        <v>0</v>
-      </c>
-      <c r="D22" s="12">
-        <v>0</v>
-      </c>
-      <c r="E22" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="B23" s="12">
-        <v>0</v>
-      </c>
-      <c r="C23" s="12">
-        <v>0.33333400000000002</v>
-      </c>
-      <c r="D23" s="12">
-        <v>0</v>
-      </c>
-      <c r="E23" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="B24" s="12">
-        <v>0</v>
-      </c>
-      <c r="C24" s="12">
-        <v>0</v>
-      </c>
-      <c r="D24" s="12">
-        <v>0.409028</v>
-      </c>
-      <c r="E24" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="B25" s="12">
-        <v>0</v>
-      </c>
-      <c r="C25" s="12">
-        <v>0</v>
-      </c>
-      <c r="D25" s="12">
-        <v>0</v>
-      </c>
-      <c r="E25" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="B26" s="12">
-        <v>0</v>
-      </c>
-      <c r="C26" s="12">
+      <c r="D26" s="16">
+        <v>8.3334000000000005E-2</v>
+      </c>
+      <c r="E26" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B27" s="16">
+        <v>0</v>
+      </c>
+      <c r="C27" s="16">
+        <v>0</v>
+      </c>
+      <c r="D27" s="16">
+        <v>0</v>
+      </c>
+      <c r="E27" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="B28" s="16">
+        <v>0</v>
+      </c>
+      <c r="C28" s="16">
+        <v>0</v>
+      </c>
+      <c r="D28" s="16">
+        <v>0</v>
+      </c>
+      <c r="E28" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="B29" s="16">
+        <v>0</v>
+      </c>
+      <c r="C29" s="16">
         <v>0.125</v>
       </c>
-      <c r="D26" s="12">
-        <v>8.3334000000000005E-2</v>
-      </c>
-      <c r="E26" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="B27" s="12">
-        <v>0</v>
-      </c>
-      <c r="C27" s="12">
-        <v>0</v>
-      </c>
-      <c r="D27" s="12">
-        <v>0</v>
-      </c>
-      <c r="E27" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="B28" s="12">
-        <v>0</v>
-      </c>
-      <c r="C28" s="12">
-        <v>0</v>
-      </c>
-      <c r="D28" s="12">
-        <v>0</v>
-      </c>
-      <c r="E28" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="B29" s="12">
-        <v>0</v>
-      </c>
-      <c r="C29" s="12">
-        <v>0.125</v>
-      </c>
-      <c r="D29" s="12">
+      <c r="D29" s="16">
         <v>0.160417</v>
       </c>
-      <c r="E29" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E29" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B30" s="16">
+        <v>0</v>
+      </c>
+      <c r="C30" s="16">
+        <v>0</v>
+      </c>
+      <c r="D30" s="16">
+        <v>0</v>
+      </c>
+      <c r="E30" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="B30" s="12">
-        <v>0</v>
-      </c>
-      <c r="C30" s="12">
-        <v>0</v>
-      </c>
-      <c r="D30" s="12">
-        <v>0</v>
-      </c>
-      <c r="E30" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="B31" s="12">
-        <v>0</v>
-      </c>
-      <c r="C31" s="12">
-        <v>0</v>
-      </c>
-      <c r="D31" s="12">
-        <v>0</v>
-      </c>
-      <c r="E31" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B31" s="16">
+        <v>0</v>
+      </c>
+      <c r="C31" s="16">
+        <v>0</v>
+      </c>
+      <c r="D31" s="16">
+        <v>0</v>
+      </c>
+      <c r="E31" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="B32" s="16">
+        <v>0</v>
+      </c>
+      <c r="C32" s="16">
+        <v>0</v>
+      </c>
+      <c r="D32" s="16">
+        <v>0</v>
+      </c>
+      <c r="E32" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="B32" s="12">
-        <v>0</v>
-      </c>
-      <c r="C32" s="12">
-        <v>0</v>
-      </c>
-      <c r="D32" s="12">
-        <v>0</v>
-      </c>
-      <c r="E32" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="B33" s="12">
-        <v>0</v>
-      </c>
-      <c r="C33" s="12">
+      <c r="B33" s="16">
+        <v>0</v>
+      </c>
+      <c r="C33" s="16">
         <v>3.9584000000000001E-2</v>
       </c>
-      <c r="D33" s="12">
-        <v>0</v>
-      </c>
-      <c r="E33" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D33" s="16">
+        <v>0</v>
+      </c>
+      <c r="E33" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="B34" s="12">
-        <v>0</v>
-      </c>
-      <c r="C34" s="12">
-        <v>0</v>
-      </c>
-      <c r="D34" s="12">
-        <v>0</v>
-      </c>
-      <c r="E34" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B35" s="13">
-        <v>0</v>
-      </c>
-      <c r="C35" s="13">
+        <v>119</v>
+      </c>
+      <c r="B34" s="16">
+        <v>0</v>
+      </c>
+      <c r="C34" s="16">
+        <v>0</v>
+      </c>
+      <c r="D34" s="16">
+        <v>0</v>
+      </c>
+      <c r="E34" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="B35" s="17">
+        <v>0</v>
+      </c>
+      <c r="C35" s="17">
         <v>0.78958399999999995</v>
       </c>
-      <c r="D35" s="13">
+      <c r="D35" s="17">
         <v>0.652084</v>
       </c>
-      <c r="E35" s="13">
+      <c r="E35" s="17">
         <v>0</v>
       </c>
     </row>
@@ -8709,48 +8680,48 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+    <row r="1" spans="1:2" ht="15.75">
+      <c r="A1" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="19" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+    <row r="5" spans="1:2">
+      <c r="A5" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="B5" s="16"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+      <c r="B5" s="19"/>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="B6" s="16" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
+      <c r="B6" s="19" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="19" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
+    <row r="8" spans="1:2">
+      <c r="A8" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="19" t="s">
         <v>134</v>
       </c>
     </row>
@@ -8761,6 +8732,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3c298670-db79-47a5-968d-a4570c34317f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="17e8e7ea-beb0-4155-adc4-5bfa61f32508" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F57AE488C1C9C348AE667C65EC1B6349" ma:contentTypeVersion="83" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="584bf6b77295f7da4f9cf4ac656056b1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3c298670-db79-47a5-968d-a4570c34317f" xmlns:ns3="17e8e7ea-beb0-4155-adc4-5bfa61f32508" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0744868ac059cd1623b27209cff1bde4" ns2:_="" ns3:_="">
     <xsd:import namespace="3c298670-db79-47a5-968d-a4570c34317f"/>
@@ -8905,28 +8896,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3c298670-db79-47a5-968d-a4570c34317f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="17e8e7ea-beb0-4155-adc4-5bfa61f32508" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E892E56B-4DB9-4737-87C8-68381ACFF402}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8A8CB62-EC1E-4BD8-BBB5-8A7D85090CA9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8934,5 +8905,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8A8CB62-EC1E-4BD8-BBB5-8A7D85090CA9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E892E56B-4DB9-4737-87C8-68381ACFF402}"/>
 </file>
--- a/Plannings 2026 S19.xlsx
+++ b/Plannings 2026 S19.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="8_{84830FEF-CD99-488C-9111-90B341AA8F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5ECE974D-BCD0-47D7-87DF-507B575CD68E}"/>
+  <xr:revisionPtr revIDLastSave="50" documentId="8_{84830FEF-CD99-488C-9111-90B341AA8F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{253740F5-E8EA-4A9B-AEAA-EA4B2B693C21}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="133">
   <si>
     <t>Planning des salariés du 04/05/2026 au 10/05/2026</t>
   </si>
@@ -430,7 +430,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[h]:mm"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -516,8 +516,14 @@
       <color rgb="FF000000"/>
       <name val="Helvetica"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -529,8 +535,26 @@
         <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC99FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF99FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="21">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -708,15 +732,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -798,7 +813,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -877,7 +892,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -887,31 +901,64 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -920,6 +967,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFCCFFFF"/>
+      <color rgb="FFCCECFF"/>
+      <color rgb="FFFF99FF"/>
+      <color rgb="FFCC99FF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -3003,23 +3058,507 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="52" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000034000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="53" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000035000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="54" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000036000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="55" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000037000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="56" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000038000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="57" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000039000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="58" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>35</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="59" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="60" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="62" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="63" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="51" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000033000000}"/>
+        <xdr:cNvPr id="64" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000040000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3037,534 +3576,6 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="52" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000034000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="53" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000035000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="54" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000036000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="55" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000037000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="56" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000038000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="57" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000039000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="58" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="59" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="60" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="61" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="62" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="63" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3588,10 +3599,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="64" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000040000000}"/>
+        <xdr:cNvPr id="66" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3609,6 +3620,94 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="67" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="68" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3632,10 +3731,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="66" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042000000}"/>
+        <xdr:cNvPr id="69" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3665,21 +3764,197 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="70" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="72" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="67" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043000000}"/>
+        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3697,270 +3972,6 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="68" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="69" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="70" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="72" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3984,10 +3995,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
+        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4015,23 +4026,551 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000057000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
+        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4061,21 +4600,153 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4103,23 +4774,331 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>53</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4149,65 +5128,21 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>51</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4235,155 +5170,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4411,199 +5214,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000057000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
+        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4631,23 +5258,111 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="109" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="110" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4675,595 +5390,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>74</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>74</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
+        <xdr:cNvPr id="111" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5281,138 +5424,6 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="109" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="110" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5436,10 +5447,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="111" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006F000000}"/>
+        <xdr:cNvPr id="112" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000070000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5467,23 +5478,111 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="113" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000071000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="114" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000072000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>80</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>80</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="112" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000070000000}"/>
+        <xdr:cNvPr id="115" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000073000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5511,76 +5610,120 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="113" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000071000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>80</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>80</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="114" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000072000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="116" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000074000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="117" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000075000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="118" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000076000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5601,21 +5744,65 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="119" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000077000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>83</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>83</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="115" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000073000000}"/>
+        <xdr:cNvPr id="120" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000078000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5643,120 +5830,32 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="116" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000074000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="117" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000075000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
+      <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>87</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
+      <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
       <xdr:row>87</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="118" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000076000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <xdr:cNvPr id="121" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000079000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5777,65 +5876,21 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="119" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000077000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>85</xdr:row>
+      <xdr:row>87</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>85</xdr:row>
+      <xdr:row>87</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="120" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000078000000}"/>
+        <xdr:cNvPr id="122" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5863,39 +5918,39 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>89</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>89</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="121" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000079000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="124" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B18C206F-90E1-4F7C-A767-9E7C820C1325}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="6858000"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5909,101 +5964,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>89</xdr:row>
+      <xdr:row>87</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>89</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="122" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00007A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="124" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B18C206F-90E1-4F7C-A767-9E7C820C1325}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1828800" y="6858000"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>89</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>89</xdr:row>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>87</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6406,7 +6373,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H92"/>
+  <dimension ref="A1:H90"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="34.5703125" customWidth="1"/>
@@ -6435,28 +6402,28 @@
       <c r="H2" s="12"/>
     </row>
     <row r="3" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="29" t="s">
+      <c r="E3" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="29" t="s">
+      <c r="F3" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="29" t="s">
+      <c r="G3" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="29" t="s">
+      <c r="H3" s="28" t="s">
         <v>10</v>
       </c>
     </row>
@@ -6464,24 +6431,24 @@
       <c r="A4" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="30"/>
+      <c r="B4" s="29"/>
       <c r="C4" s="17"/>
       <c r="D4" s="17"/>
       <c r="E4" s="17"/>
       <c r="F4" s="25"/>
-      <c r="G4" s="17" t="s">
+      <c r="G4" s="47" t="s">
         <v>12</v>
       </c>
       <c r="H4" s="18"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="19"/>
-      <c r="B5" s="31"/>
+      <c r="B5" s="30"/>
       <c r="C5" s="20"/>
       <c r="D5" s="20"/>
       <c r="E5" s="20"/>
       <c r="F5" s="20"/>
-      <c r="G5" s="20" t="s">
+      <c r="G5" s="49" t="s">
         <v>13</v>
       </c>
       <c r="H5" s="21"/>
@@ -6532,9 +6499,7 @@
       <c r="E8" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="17" t="s">
-        <v>18</v>
-      </c>
+      <c r="F8" s="17"/>
       <c r="G8" s="17"/>
       <c r="H8" s="18"/>
     </row>
@@ -6552,21 +6517,19 @@
       <c r="E9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="23"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="22"/>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="40" t="s">
         <v>23</v>
       </c>
       <c r="E10" s="1"/>
@@ -6576,13 +6539,13 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="22"/>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="41" t="s">
         <v>26</v>
       </c>
       <c r="E11" s="1"/>
@@ -6592,8 +6555,8 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="22"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="2" t="s">
+      <c r="B12" s="41"/>
+      <c r="C12" s="40" t="s">
         <v>27</v>
       </c>
       <c r="D12" s="2" t="s">
@@ -6606,8 +6569,8 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="22"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1" t="s">
+      <c r="B13" s="41"/>
+      <c r="C13" s="41" t="s">
         <v>28</v>
       </c>
       <c r="D13" s="1" t="s">
@@ -6620,9 +6583,9 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="22"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="2" t="s">
+      <c r="B14" s="41"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="40" t="s">
         <v>23</v>
       </c>
       <c r="E14" s="1"/>
@@ -6632,9 +6595,9 @@
     </row>
     <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="19"/>
-      <c r="B15" s="20"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20" t="s">
+      <c r="B15" s="42"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="42" t="s">
         <v>30</v>
       </c>
       <c r="E15" s="20"/>
@@ -6923,7 +6886,7 @@
       <c r="H32" s="23"/>
     </row>
     <row r="33" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="32"/>
+      <c r="A33" s="31"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1" t="s">
         <v>59</v>
@@ -6940,280 +6903,288 @@
       <c r="A34" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="B34" s="17" t="s">
+      <c r="B34" s="44" t="s">
         <v>62</v>
       </c>
       <c r="C34" s="17"/>
       <c r="D34" s="17"/>
       <c r="E34" s="17"/>
       <c r="F34" s="17"/>
-      <c r="G34" s="17" t="s">
+      <c r="G34" s="47" t="s">
         <v>12</v>
       </c>
       <c r="H34" s="18"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="22"/>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="45" t="s">
         <v>63</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
-      <c r="G35" s="1" t="s">
+      <c r="G35" s="48" t="s">
         <v>13</v>
       </c>
       <c r="H35" s="23"/>
     </row>
-    <row r="36" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="19"/>
-      <c r="B36" s="20"/>
-      <c r="C36" s="20"/>
-      <c r="D36" s="20"/>
-      <c r="E36" s="20"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="20"/>
-      <c r="H36" s="21"/>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="B36" s="17"/>
+      <c r="C36" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="D36" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="E36" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="F36" s="44" t="s">
+        <v>66</v>
+      </c>
+      <c r="G36" s="17"/>
+      <c r="H36" s="18" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="B37" s="17"/>
-      <c r="C37" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="D37" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="E37" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="F37" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="G37" s="17"/>
-      <c r="H37" s="18" t="s">
-        <v>15</v>
+      <c r="A37" s="22"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="D37" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="E37" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="F37" s="45" t="s">
+        <v>67</v>
+      </c>
+      <c r="G37" s="1"/>
+      <c r="H37" s="23" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="22"/>
       <c r="B38" s="1"/>
-      <c r="C38" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>67</v>
+      <c r="C38" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="D38" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="E38" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="F38" s="46" t="s">
+        <v>66</v>
       </c>
       <c r="G38" s="1"/>
-      <c r="H38" s="23" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H38" s="23"/>
+    </row>
+    <row r="39" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="22"/>
       <c r="B39" s="1"/>
-      <c r="C39" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>66</v>
+      <c r="C39" s="45" t="s">
+        <v>69</v>
+      </c>
+      <c r="D39" s="45" t="s">
+        <v>69</v>
+      </c>
+      <c r="E39" s="45" t="s">
+        <v>69</v>
+      </c>
+      <c r="F39" s="45" t="s">
+        <v>70</v>
       </c>
       <c r="G39" s="1"/>
       <c r="H39" s="23"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="22"/>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="G40" s="1"/>
-      <c r="H40" s="23"/>
+      <c r="A40" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B40" s="17"/>
+      <c r="C40" s="17"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F40" s="25"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="18"/>
     </row>
     <row r="41" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="19"/>
       <c r="B41" s="20"/>
       <c r="C41" s="20"/>
       <c r="D41" s="20"/>
-      <c r="E41" s="20"/>
-      <c r="F41" s="28"/>
+      <c r="E41" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F41" s="20"/>
       <c r="G41" s="20"/>
       <c r="H41" s="21"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="B42" s="17"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="17"/>
-      <c r="E42" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="F42" s="25"/>
-      <c r="G42" s="17"/>
-      <c r="H42" s="18"/>
+    <row r="42" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="B42" s="34"/>
+      <c r="C42" s="35"/>
+      <c r="D42" s="35"/>
+      <c r="E42" s="35"/>
+      <c r="F42" s="35"/>
+      <c r="G42" s="35"/>
+      <c r="H42" s="36"/>
     </row>
     <row r="43" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="19"/>
-      <c r="B43" s="20"/>
-      <c r="C43" s="20"/>
-      <c r="D43" s="20"/>
-      <c r="E43" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="F43" s="20"/>
-      <c r="G43" s="20"/>
-      <c r="H43" s="21"/>
-    </row>
-    <row r="44" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="B44" s="35"/>
-      <c r="C44" s="36"/>
-      <c r="D44" s="36"/>
-      <c r="E44" s="36"/>
-      <c r="F44" s="36"/>
-      <c r="G44" s="36"/>
-      <c r="H44" s="37"/>
+      <c r="A43" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="B43" s="34"/>
+      <c r="C43" s="35"/>
+      <c r="D43" s="35"/>
+      <c r="E43" s="35"/>
+      <c r="F43" s="35"/>
+      <c r="G43" s="35"/>
+      <c r="H43" s="36"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="E44" s="1"/>
+      <c r="F44" s="24"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="23"/>
     </row>
     <row r="45" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="B45" s="35"/>
-      <c r="C45" s="36"/>
-      <c r="D45" s="36"/>
-      <c r="E45" s="36"/>
-      <c r="F45" s="36"/>
-      <c r="G45" s="36"/>
-      <c r="H45" s="37"/>
+      <c r="A45" s="19"/>
+      <c r="B45" s="20"/>
+      <c r="C45" s="20"/>
+      <c r="D45" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="E45" s="20"/>
+      <c r="F45" s="20"/>
+      <c r="G45" s="20"/>
+      <c r="H45" s="21"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E46" s="1"/>
-      <c r="F46" s="24"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="23"/>
+      <c r="A46" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="B46" s="17"/>
+      <c r="C46" s="17"/>
+      <c r="D46" s="17"/>
+      <c r="E46" s="17"/>
+      <c r="F46" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="G46" s="17"/>
+      <c r="H46" s="18"/>
     </row>
     <row r="47" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="19"/>
-      <c r="B47" s="20"/>
-      <c r="C47" s="20"/>
-      <c r="D47" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="E47" s="20"/>
-      <c r="F47" s="20"/>
-      <c r="G47" s="20"/>
-      <c r="H47" s="21"/>
+      <c r="A47" s="22"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="48" t="s">
+        <v>64</v>
+      </c>
+      <c r="G47" s="1"/>
+      <c r="H47" s="23"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="B48" s="17"/>
-      <c r="C48" s="17"/>
-      <c r="D48" s="17"/>
+        <v>78</v>
+      </c>
+      <c r="B48" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="C48" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="D48" s="43" t="s">
+        <v>27</v>
+      </c>
       <c r="E48" s="17"/>
-      <c r="F48" s="17" t="s">
-        <v>12</v>
-      </c>
+      <c r="F48" s="25"/>
       <c r="G48" s="17"/>
       <c r="H48" s="18"/>
     </row>
     <row r="49" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="22"/>
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G49" s="1"/>
-      <c r="H49" s="23"/>
+      <c r="A49" s="19"/>
+      <c r="B49" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="C49" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="D49" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="E49" s="20"/>
+      <c r="F49" s="20"/>
+      <c r="G49" s="20"/>
+      <c r="H49" s="21"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="B50" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="C50" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="D50" s="17" t="s">
-        <v>27</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="B50" s="17"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="17"/>
       <c r="E50" s="17"/>
       <c r="F50" s="25"/>
-      <c r="G50" s="17"/>
-      <c r="H50" s="18"/>
-    </row>
-    <row r="51" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="19"/>
-      <c r="B51" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="C51" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="D51" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="E51" s="20"/>
-      <c r="F51" s="20"/>
-      <c r="G51" s="20"/>
-      <c r="H51" s="21"/>
+      <c r="G50" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="H50" s="18" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="22"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H51" s="23" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="B52" s="17"/>
-      <c r="C52" s="17"/>
-      <c r="D52" s="17"/>
-      <c r="E52" s="17"/>
-      <c r="F52" s="25"/>
-      <c r="G52" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="H52" s="18" t="s">
-        <v>81</v>
+      <c r="A52" s="22"/>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H52" s="26" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
@@ -7224,10 +7195,10 @@
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H53" s="23" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
@@ -7237,559 +7208,531 @@
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
-      <c r="G54" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="G54" s="1"/>
       <c r="H54" s="26" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="22"/>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="31"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
-      <c r="G55" s="1" t="s">
-        <v>84</v>
-      </c>
+      <c r="G55" s="1"/>
       <c r="H55" s="23" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="22"/>
-      <c r="B56" s="1"/>
-      <c r="C56" s="1"/>
-      <c r="D56" s="1"/>
-      <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="26" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="32"/>
-      <c r="B57" s="1"/>
-      <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
-      <c r="E57" s="1"/>
-      <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="23" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="34" t="s">
+    <row r="56" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="B58" s="40" t="s">
+      <c r="B56" s="39" t="s">
         <v>87</v>
       </c>
-      <c r="C58" s="38"/>
-      <c r="D58" s="38"/>
-      <c r="E58" s="38"/>
-      <c r="F58" s="38"/>
-      <c r="G58" s="38"/>
-      <c r="H58" s="39"/>
+      <c r="C56" s="37"/>
+      <c r="D56" s="37"/>
+      <c r="E56" s="37"/>
+      <c r="F56" s="37"/>
+      <c r="G56" s="37"/>
+      <c r="H56" s="38"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B57" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="C57" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="D57" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="E57" s="17"/>
+      <c r="F57" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="G57" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="H57" s="18"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="22"/>
+      <c r="B58" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C58" s="48" t="s">
+        <v>64</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G58" s="48" t="s">
+        <v>91</v>
+      </c>
+      <c r="H58" s="23"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="B59" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="C59" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="D59" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="E59" s="17"/>
-      <c r="F59" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="G59" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="H59" s="18"/>
+      <c r="A59" s="22"/>
+      <c r="B59" s="1"/>
+      <c r="C59" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="D59" s="50" t="s">
+        <v>92</v>
+      </c>
+      <c r="E59" s="1"/>
+      <c r="F59" s="24"/>
+      <c r="G59" s="50" t="s">
+        <v>92</v>
+      </c>
+      <c r="H59" s="23"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="22"/>
-      <c r="B60" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>90</v>
+      <c r="B60" s="1"/>
+      <c r="C60" s="41" t="s">
+        <v>76</v>
+      </c>
+      <c r="D60" s="48" t="s">
+        <v>93</v>
       </c>
       <c r="E60" s="1"/>
-      <c r="F60" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>91</v>
+      <c r="F60" s="1"/>
+      <c r="G60" s="48" t="s">
+        <v>67</v>
       </c>
       <c r="H60" s="23"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="22"/>
       <c r="B61" s="1"/>
-      <c r="C61" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>92</v>
+      <c r="C61" s="41"/>
+      <c r="D61" s="50" t="s">
+        <v>12</v>
       </c>
       <c r="E61" s="1"/>
-      <c r="F61" s="24"/>
-      <c r="G61" s="2" t="s">
-        <v>92</v>
+      <c r="F61" s="1"/>
+      <c r="G61" s="50" t="s">
+        <v>12</v>
       </c>
       <c r="H61" s="23"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="22"/>
       <c r="B62" s="1"/>
-      <c r="C62" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>93</v>
+      <c r="C62" s="41"/>
+      <c r="D62" s="48" t="s">
+        <v>94</v>
       </c>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
-      <c r="G62" s="1" t="s">
-        <v>67</v>
+      <c r="G62" s="48" t="s">
+        <v>95</v>
       </c>
       <c r="H62" s="23"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="22"/>
       <c r="B63" s="1"/>
-      <c r="C63" s="1"/>
-      <c r="D63" s="2" t="s">
-        <v>12</v>
+      <c r="C63" s="41"/>
+      <c r="D63" s="50" t="s">
+        <v>92</v>
       </c>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
       <c r="G63" s="2" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="H63" s="23"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="22"/>
+    <row r="64" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="31"/>
       <c r="B64" s="1"/>
-      <c r="C64" s="1"/>
-      <c r="D64" s="1" t="s">
-        <v>94</v>
+      <c r="C64" s="41"/>
+      <c r="D64" s="48" t="s">
+        <v>96</v>
       </c>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H64" s="23"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="22"/>
-      <c r="B65" s="1"/>
-      <c r="C65" s="1"/>
-      <c r="D65" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E65" s="1"/>
-      <c r="F65" s="1"/>
-      <c r="G65" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H65" s="23"/>
+      <c r="A65" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="B65" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="C65" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="D65" s="17"/>
+      <c r="E65" s="17"/>
+      <c r="F65" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="G65" s="17"/>
+      <c r="H65" s="18"/>
     </row>
     <row r="66" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="32"/>
-      <c r="B66" s="1"/>
-      <c r="C66" s="1"/>
-      <c r="D66" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="E66" s="1"/>
-      <c r="F66" s="1"/>
-      <c r="G66" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="H66" s="23"/>
+      <c r="A66" s="19"/>
+      <c r="B66" s="49" t="s">
+        <v>64</v>
+      </c>
+      <c r="C66" s="49" t="s">
+        <v>64</v>
+      </c>
+      <c r="D66" s="20"/>
+      <c r="E66" s="20"/>
+      <c r="F66" s="49" t="s">
+        <v>64</v>
+      </c>
+      <c r="G66" s="20"/>
+      <c r="H66" s="21"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="B67" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="C67" s="17" t="s">
-        <v>12</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="B67" s="17"/>
+      <c r="C67" s="17"/>
       <c r="D67" s="17"/>
-      <c r="E67" s="17"/>
+      <c r="E67" s="17" t="s">
+        <v>15</v>
+      </c>
       <c r="F67" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G67" s="17"/>
-      <c r="H67" s="18"/>
-    </row>
-    <row r="68" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="19"/>
-      <c r="B68" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="C68" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="D68" s="20"/>
-      <c r="E68" s="20"/>
-      <c r="F68" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="G68" s="20"/>
-      <c r="H68" s="21"/>
+        <v>50</v>
+      </c>
+      <c r="G67" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="H67" s="18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="22"/>
+      <c r="B68" s="1"/>
+      <c r="C68" s="1"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H68" s="23" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="B69" s="17"/>
-      <c r="C69" s="17"/>
-      <c r="D69" s="17"/>
-      <c r="E69" s="17" t="s">
+      <c r="A69" s="22"/>
+      <c r="B69" s="1"/>
+      <c r="C69" s="1"/>
+      <c r="D69" s="1"/>
+      <c r="E69" s="1"/>
+      <c r="F69" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F69" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="G69" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="H69" s="18" t="s">
+      <c r="G69" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="22"/>
-      <c r="B70" s="1"/>
-      <c r="C70" s="1"/>
-      <c r="D70" s="1"/>
-      <c r="E70" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="H70" s="23" t="s">
-        <v>104</v>
-      </c>
+      <c r="H69" s="23"/>
+    </row>
+    <row r="70" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="19"/>
+      <c r="B70" s="20"/>
+      <c r="C70" s="20"/>
+      <c r="D70" s="20"/>
+      <c r="E70" s="20"/>
+      <c r="F70" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="G70" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="H70" s="21"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="22"/>
-      <c r="B71" s="1"/>
+      <c r="A71" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="B71" s="41" t="s">
+        <v>27</v>
+      </c>
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
-      <c r="F71" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G71" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H71" s="23"/>
-    </row>
-    <row r="72" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="19"/>
-      <c r="B72" s="20"/>
-      <c r="C72" s="20"/>
-      <c r="D72" s="20"/>
-      <c r="E72" s="20"/>
-      <c r="F72" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="G72" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="H72" s="21"/>
+      <c r="F71" s="24"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="23" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="22"/>
+      <c r="B72" s="41" t="s">
+        <v>76</v>
+      </c>
+      <c r="C72" s="1"/>
+      <c r="D72" s="1"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="23" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="33" t="s">
-        <v>107</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="A73" s="22"/>
+      <c r="B73" s="41"/>
       <c r="C73" s="1"/>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
-      <c r="F73" s="24"/>
+      <c r="F73" s="1"/>
       <c r="G73" s="1"/>
-      <c r="H73" s="23" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="22"/>
-      <c r="B74" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C74" s="1"/>
-      <c r="D74" s="1"/>
-      <c r="E74" s="1"/>
-      <c r="F74" s="1"/>
-      <c r="G74" s="1"/>
-      <c r="H74" s="23" t="s">
-        <v>82</v>
+      <c r="H73" s="26" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="19"/>
+      <c r="B74" s="42"/>
+      <c r="C74" s="20"/>
+      <c r="D74" s="20"/>
+      <c r="E74" s="20"/>
+      <c r="F74" s="20"/>
+      <c r="G74" s="20"/>
+      <c r="H74" s="21" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="22"/>
-      <c r="B75" s="1"/>
-      <c r="C75" s="1"/>
-      <c r="D75" s="1"/>
-      <c r="E75" s="1"/>
-      <c r="F75" s="1"/>
-      <c r="G75" s="1"/>
-      <c r="H75" s="26" t="s">
-        <v>15</v>
-      </c>
+      <c r="A75" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="B75" s="17"/>
+      <c r="C75" s="17"/>
+      <c r="D75" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="E75" s="17"/>
+      <c r="F75" s="25"/>
+      <c r="G75" s="17"/>
+      <c r="H75" s="18"/>
     </row>
     <row r="76" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="19"/>
       <c r="B76" s="20"/>
       <c r="C76" s="20"/>
-      <c r="D76" s="20"/>
+      <c r="D76" s="49" t="s">
+        <v>82</v>
+      </c>
       <c r="E76" s="20"/>
       <c r="F76" s="20"/>
       <c r="G76" s="20"/>
-      <c r="H76" s="21" t="s">
-        <v>108</v>
-      </c>
+      <c r="H76" s="21"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B77" s="17"/>
       <c r="C77" s="17"/>
-      <c r="D77" s="17" t="s">
-        <v>12</v>
-      </c>
+      <c r="D77" s="17"/>
       <c r="E77" s="17"/>
       <c r="F77" s="25"/>
-      <c r="G77" s="17"/>
+      <c r="G77" s="47" t="s">
+        <v>12</v>
+      </c>
       <c r="H77" s="18"/>
     </row>
-    <row r="78" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="19"/>
-      <c r="B78" s="20"/>
-      <c r="C78" s="20"/>
-      <c r="D78" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="E78" s="20"/>
-      <c r="F78" s="20"/>
-      <c r="G78" s="20"/>
-      <c r="H78" s="21"/>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="22"/>
+      <c r="B78" s="1"/>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="H78" s="23"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="B79" s="17"/>
-      <c r="C79" s="17"/>
-      <c r="D79" s="17"/>
-      <c r="E79" s="17"/>
-      <c r="F79" s="25"/>
-      <c r="G79" s="17" t="s">
+      <c r="A79" s="22"/>
+      <c r="B79" s="1"/>
+      <c r="C79" s="1"/>
+      <c r="D79" s="1"/>
+      <c r="E79" s="1"/>
+      <c r="F79" s="1"/>
+      <c r="G79" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="H79" s="18"/>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="22"/>
-      <c r="B80" s="1"/>
-      <c r="C80" s="1"/>
-      <c r="D80" s="1"/>
-      <c r="E80" s="1"/>
-      <c r="F80" s="1"/>
-      <c r="G80" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H80" s="23"/>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="22"/>
-      <c r="B81" s="1"/>
-      <c r="C81" s="1"/>
-      <c r="D81" s="1"/>
-      <c r="E81" s="1"/>
-      <c r="F81" s="1"/>
-      <c r="G81" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H81" s="23"/>
-    </row>
-    <row r="82" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="19"/>
-      <c r="B82" s="20"/>
-      <c r="C82" s="20"/>
-      <c r="D82" s="20"/>
-      <c r="E82" s="20"/>
-      <c r="F82" s="20"/>
-      <c r="G82" s="20" t="s">
+      <c r="H79" s="23"/>
+    </row>
+    <row r="80" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="19"/>
+      <c r="B80" s="20"/>
+      <c r="C80" s="20"/>
+      <c r="D80" s="20"/>
+      <c r="E80" s="20"/>
+      <c r="F80" s="20"/>
+      <c r="G80" s="49" t="s">
         <v>111</v>
       </c>
-      <c r="H82" s="21"/>
-    </row>
-    <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="27" t="s">
+      <c r="H80" s="21"/>
+    </row>
+    <row r="81" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="B83" s="17"/>
-      <c r="C83" s="17"/>
-      <c r="D83" s="17"/>
-      <c r="E83" s="17"/>
-      <c r="F83" s="25"/>
-      <c r="G83" s="17"/>
-      <c r="H83" s="18"/>
+      <c r="B81" s="17"/>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="25"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="18"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="B82" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C82" s="17"/>
+      <c r="D82" s="17"/>
+      <c r="E82" s="17"/>
+      <c r="F82" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G82" s="17"/>
+      <c r="H82" s="18"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="22"/>
+      <c r="B83" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C83" s="1"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="1"/>
+      <c r="F83" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G83" s="1"/>
+      <c r="H83" s="23"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="B84" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="C84" s="17"/>
-      <c r="D84" s="17"/>
-      <c r="E84" s="17"/>
-      <c r="F84" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="G84" s="17"/>
-      <c r="H84" s="18"/>
+      <c r="A84" s="22"/>
+      <c r="B84" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="C84" s="1"/>
+      <c r="D84" s="1"/>
+      <c r="E84" s="1"/>
+      <c r="F84" s="24"/>
+      <c r="G84" s="1"/>
+      <c r="H84" s="23"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="22"/>
-      <c r="B85" s="1" t="s">
-        <v>114</v>
+      <c r="B85" s="41" t="s">
+        <v>116</v>
       </c>
       <c r="C85" s="1"/>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
-      <c r="F85" s="1" t="s">
-        <v>115</v>
-      </c>
+      <c r="F85" s="1"/>
       <c r="G85" s="1"/>
       <c r="H85" s="23"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="22"/>
       <c r="B86" s="2" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C86" s="1"/>
       <c r="D86" s="1"/>
       <c r="E86" s="1"/>
-      <c r="F86" s="24"/>
+      <c r="F86" s="1"/>
       <c r="G86" s="1"/>
       <c r="H86" s="23"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="22"/>
-      <c r="B87" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C87" s="1"/>
-      <c r="D87" s="1"/>
-      <c r="E87" s="1"/>
-      <c r="F87" s="1"/>
-      <c r="G87" s="1"/>
-      <c r="H87" s="23"/>
+    <row r="87" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="19"/>
+      <c r="B87" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="C87" s="20"/>
+      <c r="D87" s="20"/>
+      <c r="E87" s="20"/>
+      <c r="F87" s="20"/>
+      <c r="G87" s="20"/>
+      <c r="H87" s="21"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="22"/>
-      <c r="B88" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C88" s="1"/>
-      <c r="D88" s="1"/>
-      <c r="E88" s="1"/>
-      <c r="F88" s="1"/>
-      <c r="G88" s="1"/>
-      <c r="H88" s="23"/>
+      <c r="A88" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="B88" s="17"/>
+      <c r="C88" s="17"/>
+      <c r="D88" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="E88" s="17"/>
+      <c r="F88" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="G88" s="17"/>
+      <c r="H88" s="18"/>
     </row>
     <row r="89" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="19"/>
-      <c r="B89" s="20" t="s">
-        <v>117</v>
-      </c>
+      <c r="B89" s="20"/>
       <c r="C89" s="20"/>
-      <c r="D89" s="20"/>
+      <c r="D89" s="49" t="s">
+        <v>82</v>
+      </c>
       <c r="E89" s="20"/>
-      <c r="F89" s="20"/>
+      <c r="F89" s="49" t="s">
+        <v>64</v>
+      </c>
       <c r="G89" s="20"/>
       <c r="H89" s="21"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="B90" s="17"/>
-      <c r="C90" s="17"/>
-      <c r="D90" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="E90" s="17"/>
-      <c r="F90" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G90" s="17"/>
-      <c r="H90" s="18"/>
-    </row>
-    <row r="91" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="19"/>
-      <c r="B91" s="20"/>
-      <c r="C91" s="20"/>
-      <c r="D91" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="E91" s="20"/>
-      <c r="F91" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="G91" s="20"/>
-      <c r="H91" s="21"/>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B92" s="15"/>
-      <c r="C92" s="15"/>
-      <c r="D92" s="15"/>
-      <c r="E92" s="15"/>
-      <c r="F92" s="15"/>
-      <c r="G92" s="15"/>
-      <c r="H92" s="15"/>
+      <c r="B90" s="15"/>
+      <c r="C90" s="15"/>
+      <c r="D90" s="15"/>
+      <c r="E90" s="15"/>
+      <c r="F90" s="15"/>
+      <c r="G90" s="15"/>
+      <c r="H90" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B45:H45"/>
-    <mergeCell ref="B44:H44"/>
-    <mergeCell ref="B58:H58"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B56:H56"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="A4:A5"/>
@@ -7800,22 +7743,22 @@
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="A24:A25"/>
     <mergeCell ref="A26:A33"/>
-    <mergeCell ref="A34:A36"/>
-    <mergeCell ref="A37:A41"/>
-    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A36:A39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A44:A45"/>
     <mergeCell ref="A46:A47"/>
     <mergeCell ref="A48:A49"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="A52:A57"/>
-    <mergeCell ref="A59:A66"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="A69:A72"/>
-    <mergeCell ref="A73:A76"/>
-    <mergeCell ref="B92:H92"/>
-    <mergeCell ref="A77:A78"/>
-    <mergeCell ref="A79:A82"/>
-    <mergeCell ref="A84:A89"/>
-    <mergeCell ref="A90:A91"/>
+    <mergeCell ref="A50:A55"/>
+    <mergeCell ref="A57:A64"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="A67:A70"/>
+    <mergeCell ref="A71:A74"/>
+    <mergeCell ref="B90:H90"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="A77:A80"/>
+    <mergeCell ref="A82:A87"/>
+    <mergeCell ref="A88:A89"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/Plannings 2026 S19.xlsx
+++ b/Plannings 2026 S19.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="8_{84830FEF-CD99-488C-9111-90B341AA8F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{253740F5-E8EA-4A9B-AEAA-EA4B2B693C21}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="8_{84830FEF-CD99-488C-9111-90B341AA8F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A8FAAA4-DBC4-4BEA-9618-B21912BDD4DF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="130">
   <si>
     <t>Planning des salariés du 04/05/2026 au 10/05/2026</t>
   </si>
@@ -90,9 +90,6 @@
     <t>16:00/24:00</t>
   </si>
   <si>
-    <t>14:00/17:00</t>
-  </si>
-  <si>
     <t>L-REG</t>
   </si>
   <si>
@@ -285,13 +282,7 @@
     <t>ORDONEZ GOMEZ Oceane</t>
   </si>
   <si>
-    <t>INDIS</t>
-  </si>
-  <si>
     <t>PEREZ Loic</t>
-  </si>
-  <si>
-    <t>09:40/12:30</t>
   </si>
   <si>
     <t>09:50/13:45</t>
@@ -523,7 +514,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -550,6 +541,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFCCFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -813,7 +822,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -961,6 +970,36 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -970,8 +1009,8 @@
   <colors>
     <mruColors>
       <color rgb="FFCCFFFF"/>
+      <color rgb="FFFF99FF"/>
       <color rgb="FFCCECFF"/>
-      <color rgb="FFFF99FF"/>
       <color rgb="FFCC99FF"/>
     </mruColors>
   </colors>
@@ -992,13 +1031,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1036,13 +1075,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1080,13 +1119,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1124,13 +1163,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1168,13 +1207,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1212,13 +1251,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1256,13 +1295,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1300,13 +1339,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1344,13 +1383,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1388,13 +1427,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1432,13 +1471,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1476,13 +1515,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1520,13 +1559,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1564,13 +1603,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1608,13 +1647,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1652,13 +1691,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1696,13 +1735,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1740,13 +1779,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1784,13 +1823,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1828,13 +1867,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1872,13 +1911,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1916,13 +1955,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1960,13 +1999,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2004,13 +2043,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2048,13 +2087,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2092,13 +2131,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2136,13 +2175,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2180,13 +2219,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2224,13 +2263,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2268,13 +2307,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2312,13 +2351,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2356,13 +2395,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2400,13 +2439,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2444,13 +2483,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2488,13 +2527,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2532,13 +2571,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2576,13 +2615,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2620,13 +2659,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2664,13 +2703,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2708,13 +2747,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2752,13 +2791,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2796,13 +2835,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2840,13 +2879,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2884,13 +2923,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2928,13 +2967,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2972,13 +3011,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3016,13 +3055,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3060,13 +3099,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3104,13 +3143,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3148,13 +3187,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3192,13 +3231,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3236,13 +3275,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3280,13 +3319,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3324,13 +3363,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3368,13 +3407,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3412,13 +3451,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3456,13 +3495,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3500,13 +3539,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3544,13 +3583,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3559,50 +3598,6 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000040000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="66" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3643,10 +3638,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="67" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043000000}"/>
+        <xdr:cNvPr id="66" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3664,50 +3659,6 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="68" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3731,10 +3682,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="69" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
+        <xdr:cNvPr id="67" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3762,199 +3713,67 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="68" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="70" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="72" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
+        <xdr:cNvPr id="69" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000045000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3984,21 +3803,197 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="70" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000046000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="72" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="73" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="74" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
+        <xdr:cNvPr id="75" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4026,551 +4021,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000057000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
+        <xdr:cNvPr id="76" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4600,21 +4067,285 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="77" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="78" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="79" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="80" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000050000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000051000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000053000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000054000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4642,23 +4373,111 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000055000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="86" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000056000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="87" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000057000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4686,23 +4505,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="88" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000058000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4730,67 +4549,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="89" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000059000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4818,419 +4593,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>59</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>59</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
+        <xdr:cNvPr id="90" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5258,67 +4637,551 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="91" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="92" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="93" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="94" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="95" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00005F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="96" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000060000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="97" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000061000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="99" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000063000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="100" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000064000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="101" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000065000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="103" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000067000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="104" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000068000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>67</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="109" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006D000000}"/>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="105" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000069000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5346,32 +5209,32 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="110" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="106" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5392,21 +5255,21 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>71</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="111" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006F000000}"/>
+        <xdr:cNvPr id="107" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5434,23 +5297,155 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="108" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="109" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="110" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="112" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000070000000}"/>
+        <xdr:cNvPr id="111" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5478,111 +5473,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="113" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000071000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="114" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000072000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="115" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000073000000}"/>
+        <xdr:cNvPr id="112" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000070000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5610,199 +5517,111 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="113" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000071000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="114" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000072000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>81</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="116" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000074000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="117" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000075000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="118" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000076000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="119" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000077000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>83</xdr:row>
+      <xdr:row>81</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="120" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000078000000}"/>
+        <xdr:cNvPr id="115" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000073000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5830,32 +5649,120 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="121" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000079000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="116" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000074000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="117" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000075000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="118" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000076000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5876,17 +5783,149 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="119" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000077000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>84</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>84</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
+        <xdr:cNvPr id="120" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000078000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="121" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000079000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
         <xdr:cNvPr id="122" name="Picture 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
@@ -5920,13 +5959,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5964,13 +6003,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>88</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>88</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6373,10 +6412,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H90"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="8" width="34.5703125" customWidth="1"/>
+    <col min="1" max="8" width="46.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6401,166 +6443,161 @@
       <c r="G2" s="12"/>
       <c r="H2" s="12"/>
     </row>
-    <row r="3" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="28" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B4" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C4" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="28" t="s">
+      <c r="D4" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="28" t="s">
+      <c r="E4" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="28" t="s">
+      <c r="F4" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="28" t="s">
+      <c r="G4" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="28" t="s">
+      <c r="H4" s="28" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="47" t="s">
+      <c r="B5" s="29"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="18"/>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="19"/>
-      <c r="B5" s="30"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="49" t="s">
+      <c r="H5" s="18"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="19"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="21"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
+      <c r="H6" s="21"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B7" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C7" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="18"/>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="19"/>
-      <c r="B7" s="20" t="s">
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="18"/>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="19"/>
+      <c r="B8" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C8" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="21"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="21"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B9" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C9" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D9" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E9" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="18"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="22"/>
-      <c r="B9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="23"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="18"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="22"/>
-      <c r="B10" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="1"/>
-      <c r="F10" s="24"/>
+      <c r="B10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="23"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="22"/>
-      <c r="B11" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="41" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="41" t="s">
-        <v>26</v>
+      <c r="B11" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="40" t="s">
+        <v>22</v>
       </c>
       <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
+      <c r="F11" s="24"/>
       <c r="G11" s="1"/>
       <c r="H11" s="23"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="22"/>
-      <c r="B12" s="41"/>
-      <c r="C12" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>15</v>
+      <c r="B12" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="41" t="s">
+        <v>25</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
@@ -6570,11 +6607,11 @@
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="22"/>
       <c r="B13" s="41"/>
-      <c r="C13" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>29</v>
+      <c r="C13" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
@@ -6584,470 +6621,472 @@
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="22"/>
       <c r="B14" s="41"/>
-      <c r="C14" s="41"/>
-      <c r="D14" s="40" t="s">
-        <v>23</v>
+      <c r="C14" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="23"/>
     </row>
-    <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="19"/>
-      <c r="B15" s="42"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="42" t="s">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="22"/>
+      <c r="B15" s="41"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="23"/>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="19"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="21"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="21"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="16" t="s">
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="25"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="18"/>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="19"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17" t="s">
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="21"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="F16" s="25"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="18"/>
-    </row>
-    <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="19"/>
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="21"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="16" t="s">
+      <c r="D19" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="17"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="18"/>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="19"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="21"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17" t="s">
+      <c r="B21" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D18" s="17" t="s">
+      <c r="C21" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="E18" s="17"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="18"/>
-    </row>
-    <row r="19" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="19"/>
-      <c r="B19" s="20"/>
-      <c r="C19" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="21"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="B20" s="17" t="s">
+      <c r="D21" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="E21" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="F20" s="25"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="18"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="22"/>
-      <c r="B21" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="23"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="18"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="22"/>
-      <c r="B22" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="1"/>
-      <c r="D22" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E22" s="1"/>
+      <c r="B22" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="23"/>
     </row>
-    <row r="23" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="19"/>
-      <c r="B23" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20" t="s">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="22"/>
+      <c r="B23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="1"/>
+      <c r="D23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="23"/>
+    </row>
+    <row r="24" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="19"/>
+      <c r="B24" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="21"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="21"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
+      <c r="B25" s="17"/>
+      <c r="C25" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" s="17"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" s="18"/>
+    </row>
+    <row r="26" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="19"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17" t="s">
+      <c r="D26" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="H26" s="21"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="58" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" s="58" t="s">
+        <v>44</v>
+      </c>
+      <c r="D27" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" s="58" t="s">
+        <v>44</v>
+      </c>
+      <c r="F27" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="E24" s="17"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="H24" s="18"/>
-    </row>
-    <row r="25" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="19"/>
-      <c r="B25" s="20"/>
-      <c r="C25" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="D25" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="H25" s="21"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="B26" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="C26" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="D26" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="E26" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="F26" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="G26" s="17"/>
-      <c r="H26" s="18"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="22"/>
-      <c r="B27" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G27" s="1"/>
-      <c r="H27" s="23"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="18"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="22"/>
-      <c r="B28" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D28" s="2" t="s">
+      <c r="B28" s="59" t="s">
         <v>45</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F28" s="24"/>
+      <c r="C28" s="59" t="s">
+        <v>46</v>
+      </c>
+      <c r="D28" s="48" t="s">
+        <v>47</v>
+      </c>
+      <c r="E28" s="59" t="s">
+        <v>18</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="G28" s="1"/>
       <c r="H28" s="23"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="22"/>
-      <c r="B29" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F29" s="1"/>
+      <c r="B29" s="56" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D29" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" s="60" t="s">
+        <v>44</v>
+      </c>
+      <c r="F29" s="24"/>
       <c r="G29" s="1"/>
       <c r="H29" s="23"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="22"/>
-      <c r="B30" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D30" s="2" t="s">
+      <c r="B30" s="57" t="s">
         <v>51</v>
       </c>
-      <c r="E30" s="1"/>
+      <c r="C30" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D30" s="48" t="s">
+        <v>53</v>
+      </c>
+      <c r="E30" s="59" t="s">
+        <v>54</v>
+      </c>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="23"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="22"/>
-      <c r="B31" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E31" s="1"/>
+      <c r="B31" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" s="60" t="s">
+        <v>44</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E31" s="59"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="23"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="22"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E32" s="1"/>
+      <c r="B32" s="48" t="s">
+        <v>55</v>
+      </c>
+      <c r="C32" s="59" t="s">
+        <v>56</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E32" s="59"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
       <c r="H32" s="23"/>
     </row>
-    <row r="33" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="31"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E33" s="1"/>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="22"/>
+      <c r="B33" s="48"/>
+      <c r="C33" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33" s="60" t="s">
+        <v>44</v>
+      </c>
+      <c r="E33" s="59"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
       <c r="H33" s="23"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="16" t="s">
+    <row r="34" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="31"/>
+      <c r="B34" s="48"/>
+      <c r="C34" s="48" t="s">
+        <v>58</v>
+      </c>
+      <c r="D34" s="48" t="s">
+        <v>59</v>
+      </c>
+      <c r="E34" s="59"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="23"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="B34" s="44" t="s">
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="H35" s="18"/>
+    </row>
+    <row r="36" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="22"/>
+      <c r="B36" s="45" t="s">
         <v>62</v>
       </c>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="47" t="s">
-        <v>12</v>
-      </c>
-      <c r="H34" s="18"/>
-    </row>
-    <row r="35" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="22"/>
-      <c r="B35" s="45" t="s">
-        <v>63</v>
-      </c>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="48" t="s">
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="H35" s="23"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="16" t="s">
+      <c r="H36" s="23"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="B37" s="17"/>
+      <c r="C37" s="44" t="s">
         <v>65</v>
       </c>
-      <c r="B36" s="17"/>
-      <c r="C36" s="44" t="s">
-        <v>66</v>
-      </c>
-      <c r="D36" s="44" t="s">
-        <v>66</v>
-      </c>
-      <c r="E36" s="44" t="s">
-        <v>66</v>
-      </c>
-      <c r="F36" s="44" t="s">
-        <v>66</v>
-      </c>
-      <c r="G36" s="17"/>
-      <c r="H36" s="18" t="s">
+      <c r="D37" s="44" t="s">
+        <v>65</v>
+      </c>
+      <c r="E37" s="44" t="s">
+        <v>65</v>
+      </c>
+      <c r="F37" s="44" t="s">
+        <v>65</v>
+      </c>
+      <c r="G37" s="17"/>
+      <c r="H37" s="18" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="22"/>
-      <c r="B37" s="1"/>
-      <c r="C37" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="D37" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="E37" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="F37" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="G37" s="1"/>
-      <c r="H37" s="23" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="22"/>
       <c r="B38" s="1"/>
-      <c r="C38" s="46" t="s">
+      <c r="C38" s="45" t="s">
         <v>66</v>
       </c>
-      <c r="D38" s="46" t="s">
+      <c r="D38" s="45" t="s">
         <v>66</v>
       </c>
-      <c r="E38" s="46" t="s">
+      <c r="E38" s="45" t="s">
         <v>66</v>
       </c>
-      <c r="F38" s="46" t="s">
+      <c r="F38" s="45" t="s">
         <v>66</v>
       </c>
       <c r="G38" s="1"/>
-      <c r="H38" s="23"/>
-    </row>
-    <row r="39" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H38" s="23" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="22"/>
       <c r="B39" s="1"/>
-      <c r="C39" s="45" t="s">
-        <v>69</v>
-      </c>
-      <c r="D39" s="45" t="s">
-        <v>69</v>
-      </c>
-      <c r="E39" s="45" t="s">
-        <v>69</v>
-      </c>
-      <c r="F39" s="45" t="s">
-        <v>70</v>
+      <c r="C39" s="46" t="s">
+        <v>65</v>
+      </c>
+      <c r="D39" s="46" t="s">
+        <v>65</v>
+      </c>
+      <c r="E39" s="46" t="s">
+        <v>65</v>
+      </c>
+      <c r="F39" s="46" t="s">
+        <v>65</v>
       </c>
       <c r="G39" s="1"/>
       <c r="H39" s="23"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="B40" s="17"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="17"/>
-      <c r="E40" s="17" t="s">
+    <row r="40" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="22"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="45" t="s">
+        <v>68</v>
+      </c>
+      <c r="D40" s="45" t="s">
+        <v>68</v>
+      </c>
+      <c r="E40" s="45" t="s">
+        <v>68</v>
+      </c>
+      <c r="F40" s="45" t="s">
+        <v>69</v>
+      </c>
+      <c r="G40" s="1"/>
+      <c r="H40" s="23"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="B41" s="17"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="F40" s="25"/>
-      <c r="G40" s="17"/>
-      <c r="H40" s="18"/>
-    </row>
-    <row r="41" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="19"/>
-      <c r="B41" s="20"/>
-      <c r="C41" s="20"/>
-      <c r="D41" s="20"/>
-      <c r="E41" s="20" t="s">
+      <c r="F41" s="25"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="18"/>
+    </row>
+    <row r="42" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="19"/>
+      <c r="B42" s="20"/>
+      <c r="C42" s="20"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="F41" s="20"/>
-      <c r="G41" s="20"/>
-      <c r="H41" s="21"/>
-    </row>
-    <row r="42" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="33" t="s">
-        <v>73</v>
-      </c>
-      <c r="B42" s="34"/>
-      <c r="C42" s="35"/>
-      <c r="D42" s="35"/>
-      <c r="E42" s="35"/>
-      <c r="F42" s="35"/>
-      <c r="G42" s="35"/>
-      <c r="H42" s="36"/>
+      <c r="F42" s="20"/>
+      <c r="G42" s="20"/>
+      <c r="H42" s="21"/>
     </row>
     <row r="43" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="33" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B43" s="34"/>
       <c r="C43" s="35"/>
@@ -7057,120 +7096,118 @@
       <c r="G43" s="35"/>
       <c r="H43" s="36"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="32" t="s">
+    <row r="44" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="B44" s="34"/>
+      <c r="C44" s="35"/>
+      <c r="D44" s="35"/>
+      <c r="E44" s="35"/>
+      <c r="F44" s="35"/>
+      <c r="G44" s="35"/>
+      <c r="H44" s="36"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="E45" s="1"/>
+      <c r="F45" s="24"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="23"/>
+    </row>
+    <row r="46" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="19"/>
+      <c r="B46" s="20"/>
+      <c r="C46" s="20"/>
+      <c r="D46" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="E44" s="1"/>
-      <c r="F44" s="24"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="23"/>
-    </row>
-    <row r="45" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="19"/>
-      <c r="B45" s="20"/>
-      <c r="C45" s="20"/>
-      <c r="D45" s="42" t="s">
+      <c r="E46" s="20"/>
+      <c r="F46" s="20"/>
+      <c r="G46" s="20"/>
+      <c r="H46" s="21"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="E45" s="20"/>
-      <c r="F45" s="20"/>
-      <c r="G45" s="20"/>
-      <c r="H45" s="21"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="16" t="s">
+      <c r="B47" s="17"/>
+      <c r="C47" s="17"/>
+      <c r="D47" s="17"/>
+      <c r="E47" s="17"/>
+      <c r="F47" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="G47" s="17"/>
+      <c r="H47" s="18"/>
+    </row>
+    <row r="48" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="22"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="48" t="s">
+        <v>63</v>
+      </c>
+      <c r="G48" s="1"/>
+      <c r="H48" s="23"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="B46" s="17"/>
-      <c r="C46" s="17"/>
-      <c r="D46" s="17"/>
-      <c r="E46" s="17"/>
-      <c r="F46" s="47" t="s">
-        <v>12</v>
-      </c>
-      <c r="G46" s="17"/>
-      <c r="H46" s="18"/>
-    </row>
-    <row r="47" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="22"/>
-      <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="48" t="s">
-        <v>64</v>
-      </c>
-      <c r="G47" s="1"/>
-      <c r="H47" s="23"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="16" t="s">
+      <c r="B49" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="D49" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="E49" s="17"/>
+      <c r="F49" s="25"/>
+      <c r="G49" s="17"/>
+      <c r="H49" s="18"/>
+    </row>
+    <row r="50" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="19"/>
+      <c r="B50" s="42" t="s">
+        <v>75</v>
+      </c>
+      <c r="C50" s="42" t="s">
+        <v>75</v>
+      </c>
+      <c r="D50" s="42" t="s">
         <v>78</v>
       </c>
-      <c r="B48" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="C48" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="D48" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="E48" s="17"/>
-      <c r="F48" s="25"/>
-      <c r="G48" s="17"/>
-      <c r="H48" s="18"/>
-    </row>
-    <row r="49" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="19"/>
-      <c r="B49" s="42" t="s">
-        <v>76</v>
-      </c>
-      <c r="C49" s="42" t="s">
-        <v>76</v>
-      </c>
-      <c r="D49" s="42" t="s">
+      <c r="E50" s="20"/>
+      <c r="F50" s="20"/>
+      <c r="G50" s="20"/>
+      <c r="H50" s="21"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="E49" s="20"/>
-      <c r="F49" s="20"/>
-      <c r="G49" s="20"/>
-      <c r="H49" s="21"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="16" t="s">
+      <c r="B51" s="17"/>
+      <c r="C51" s="17"/>
+      <c r="D51" s="17"/>
+      <c r="E51" s="17"/>
+      <c r="F51" s="25"/>
+      <c r="G51" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="B50" s="17"/>
-      <c r="C50" s="17"/>
-      <c r="D50" s="17"/>
-      <c r="E50" s="17"/>
-      <c r="F50" s="25"/>
-      <c r="G50" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="H50" s="18" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="22"/>
-      <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="H51" s="23" t="s">
-        <v>83</v>
+      <c r="H51" s="53" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
@@ -7180,11 +7217,11 @@
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
-      <c r="G52" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H52" s="26" t="s">
-        <v>15</v>
+      <c r="G52" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="H52" s="54" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
@@ -7194,11 +7231,11 @@
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
-      <c r="G53" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="H53" s="23" t="s">
-        <v>85</v>
+      <c r="G53" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H53" s="26" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
@@ -7208,237 +7245,227 @@
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="26" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="31"/>
+      <c r="G54" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H54" s="23" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="22"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
-      <c r="H55" s="23" t="s">
-        <v>69</v>
+      <c r="H55" s="55" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="33" t="s">
+      <c r="A56" s="31"/>
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="54" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="B57" s="39"/>
+      <c r="C57" s="37"/>
+      <c r="D57" s="37"/>
+      <c r="E57" s="37"/>
+      <c r="F57" s="37"/>
+      <c r="G57" s="37"/>
+      <c r="H57" s="38"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="B56" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="C56" s="37"/>
-      <c r="D56" s="37"/>
-      <c r="E56" s="37"/>
-      <c r="F56" s="37"/>
-      <c r="G56" s="37"/>
-      <c r="H56" s="38"/>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="B57" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="C57" s="47" t="s">
+      <c r="B58" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="C58" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="D57" s="17" t="s">
+      <c r="D58" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="E57" s="17"/>
-      <c r="F57" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="G57" s="47" t="s">
+      <c r="E58" s="17"/>
+      <c r="F58" s="17"/>
+      <c r="G58" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="H57" s="18"/>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="22"/>
-      <c r="B58" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C58" s="48" t="s">
-        <v>64</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E58" s="1"/>
-      <c r="F58" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G58" s="48" t="s">
-        <v>91</v>
-      </c>
-      <c r="H58" s="23"/>
+      <c r="H58" s="18"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="22"/>
-      <c r="B59" s="1"/>
-      <c r="C59" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="D59" s="50" t="s">
-        <v>92</v>
+      <c r="B59" s="45" t="s">
+        <v>62</v>
+      </c>
+      <c r="C59" s="48" t="s">
+        <v>63</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="E59" s="1"/>
-      <c r="F59" s="24"/>
-      <c r="G59" s="50" t="s">
-        <v>92</v>
+      <c r="F59" s="1"/>
+      <c r="G59" s="48" t="s">
+        <v>88</v>
       </c>
       <c r="H59" s="23"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="22"/>
-      <c r="B60" s="1"/>
-      <c r="C60" s="41" t="s">
-        <v>76</v>
-      </c>
-      <c r="D60" s="48" t="s">
-        <v>93</v>
+      <c r="B60" s="45"/>
+      <c r="C60" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="D60" s="50" t="s">
+        <v>89</v>
       </c>
       <c r="E60" s="1"/>
-      <c r="F60" s="1"/>
-      <c r="G60" s="48" t="s">
-        <v>67</v>
+      <c r="F60" s="24"/>
+      <c r="G60" s="50" t="s">
+        <v>89</v>
       </c>
       <c r="H60" s="23"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="22"/>
-      <c r="B61" s="1"/>
-      <c r="C61" s="41"/>
-      <c r="D61" s="50" t="s">
-        <v>12</v>
+      <c r="B61" s="45"/>
+      <c r="C61" s="41" t="s">
+        <v>75</v>
+      </c>
+      <c r="D61" s="48" t="s">
+        <v>90</v>
       </c>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
-      <c r="G61" s="50" t="s">
-        <v>12</v>
+      <c r="G61" s="48" t="s">
+        <v>66</v>
       </c>
       <c r="H61" s="23"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="22"/>
-      <c r="B62" s="1"/>
+      <c r="B62" s="45"/>
       <c r="C62" s="41"/>
-      <c r="D62" s="48" t="s">
-        <v>94</v>
+      <c r="D62" s="50" t="s">
+        <v>12</v>
       </c>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
-      <c r="G62" s="48" t="s">
-        <v>95</v>
+      <c r="G62" s="50" t="s">
+        <v>12</v>
       </c>
       <c r="H62" s="23"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="22"/>
-      <c r="B63" s="1"/>
+      <c r="B63" s="45"/>
       <c r="C63" s="41"/>
-      <c r="D63" s="50" t="s">
-        <v>92</v>
+      <c r="D63" s="48" t="s">
+        <v>91</v>
       </c>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
-      <c r="G63" s="2" t="s">
-        <v>81</v>
+      <c r="G63" s="48" t="s">
+        <v>92</v>
       </c>
       <c r="H63" s="23"/>
     </row>
-    <row r="64" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="31"/>
-      <c r="B64" s="1"/>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="22"/>
+      <c r="B64" s="45"/>
       <c r="C64" s="41"/>
-      <c r="D64" s="48" t="s">
-        <v>96</v>
+      <c r="D64" s="50" t="s">
+        <v>89</v>
       </c>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
-      <c r="G64" s="1" t="s">
+      <c r="G64" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H64" s="23"/>
+    </row>
+    <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="31"/>
+      <c r="B65" s="45"/>
+      <c r="C65" s="41"/>
+      <c r="D65" s="48" t="s">
+        <v>93</v>
+      </c>
+      <c r="E65" s="1"/>
+      <c r="F65" s="1"/>
+      <c r="G65" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H65" s="23"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="B66" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="C66" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="D66" s="17"/>
+      <c r="E66" s="17"/>
+      <c r="F66" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="G66" s="17"/>
+      <c r="H66" s="18"/>
+    </row>
+    <row r="67" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="19"/>
+      <c r="B67" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="C67" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="D67" s="20"/>
+      <c r="E67" s="20"/>
+      <c r="F67" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="G67" s="20"/>
+      <c r="H67" s="21"/>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="B68" s="17"/>
+      <c r="C68" s="17"/>
+      <c r="D68" s="17"/>
+      <c r="E68" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F68" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="G68" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="H64" s="23"/>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="B65" s="47" t="s">
-        <v>12</v>
-      </c>
-      <c r="C65" s="47" t="s">
-        <v>12</v>
-      </c>
-      <c r="D65" s="17"/>
-      <c r="E65" s="17"/>
-      <c r="F65" s="47" t="s">
-        <v>12</v>
-      </c>
-      <c r="G65" s="17"/>
-      <c r="H65" s="18"/>
-    </row>
-    <row r="66" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="19"/>
-      <c r="B66" s="49" t="s">
-        <v>64</v>
-      </c>
-      <c r="C66" s="49" t="s">
-        <v>64</v>
-      </c>
-      <c r="D66" s="20"/>
-      <c r="E66" s="20"/>
-      <c r="F66" s="49" t="s">
-        <v>64</v>
-      </c>
-      <c r="G66" s="20"/>
-      <c r="H66" s="21"/>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="B67" s="17"/>
-      <c r="C67" s="17"/>
-      <c r="D67" s="17"/>
-      <c r="E67" s="17" t="s">
+      <c r="H68" s="18" t="s">
         <v>15</v>
-      </c>
-      <c r="F67" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="G67" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="H67" s="18" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="22"/>
-      <c r="B68" s="1"/>
-      <c r="C68" s="1"/>
-      <c r="D68" s="1"/>
-      <c r="E68" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="H68" s="23" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -7446,134 +7473,140 @@
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
-      <c r="E69" s="1"/>
-      <c r="F69" s="2" t="s">
+      <c r="E69" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="H69" s="23" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="22"/>
+      <c r="B70" s="1"/>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G69" s="2" t="s">
+      <c r="G70" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H69" s="23"/>
-    </row>
-    <row r="70" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="19"/>
-      <c r="B70" s="20"/>
-      <c r="C70" s="20"/>
-      <c r="D70" s="20"/>
-      <c r="E70" s="20"/>
-      <c r="F70" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="G70" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="H70" s="21"/>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="32" t="s">
-        <v>107</v>
-      </c>
-      <c r="B71" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="C71" s="1"/>
-      <c r="D71" s="1"/>
-      <c r="E71" s="1"/>
-      <c r="F71" s="24"/>
-      <c r="G71" s="1"/>
-      <c r="H71" s="23" t="s">
-        <v>81</v>
-      </c>
+      <c r="H70" s="23"/>
+    </row>
+    <row r="71" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="19"/>
+      <c r="B71" s="20"/>
+      <c r="C71" s="20"/>
+      <c r="D71" s="20"/>
+      <c r="E71" s="20"/>
+      <c r="F71" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="G71" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="H71" s="21"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="22"/>
+      <c r="A72" s="32" t="s">
+        <v>104</v>
+      </c>
       <c r="B72" s="41" t="s">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
-      <c r="F72" s="1"/>
+      <c r="F72" s="24"/>
       <c r="G72" s="1"/>
-      <c r="H72" s="23" t="s">
-        <v>82</v>
+      <c r="H72" s="54" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="22"/>
-      <c r="B73" s="41"/>
+      <c r="B73" s="41" t="s">
+        <v>75</v>
+      </c>
       <c r="C73" s="1"/>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
-      <c r="H73" s="26" t="s">
+      <c r="H73" s="54" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="22"/>
+      <c r="B74" s="41"/>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="26" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="19"/>
-      <c r="B74" s="42"/>
-      <c r="C74" s="20"/>
-      <c r="D74" s="20"/>
-      <c r="E74" s="20"/>
-      <c r="F74" s="20"/>
-      <c r="G74" s="20"/>
-      <c r="H74" s="21" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="B75" s="17"/>
-      <c r="C75" s="17"/>
-      <c r="D75" s="47" t="s">
+    <row r="75" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="19"/>
+      <c r="B75" s="42"/>
+      <c r="C75" s="20"/>
+      <c r="D75" s="20"/>
+      <c r="E75" s="20"/>
+      <c r="F75" s="20"/>
+      <c r="G75" s="20"/>
+      <c r="H75" s="21" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="B76" s="17"/>
+      <c r="C76" s="17"/>
+      <c r="D76" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="E75" s="17"/>
-      <c r="F75" s="25"/>
-      <c r="G75" s="17"/>
-      <c r="H75" s="18"/>
-    </row>
-    <row r="76" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="19"/>
-      <c r="B76" s="20"/>
-      <c r="C76" s="20"/>
-      <c r="D76" s="49" t="s">
-        <v>82</v>
-      </c>
-      <c r="E76" s="20"/>
-      <c r="F76" s="20"/>
-      <c r="G76" s="20"/>
-      <c r="H76" s="21"/>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="B77" s="17"/>
-      <c r="C77" s="17"/>
-      <c r="D77" s="17"/>
-      <c r="E77" s="17"/>
-      <c r="F77" s="25"/>
-      <c r="G77" s="47" t="s">
+      <c r="E76" s="17"/>
+      <c r="F76" s="25"/>
+      <c r="G76" s="17"/>
+      <c r="H76" s="18"/>
+    </row>
+    <row r="77" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="19"/>
+      <c r="B77" s="20"/>
+      <c r="C77" s="20"/>
+      <c r="D77" s="49" t="s">
+        <v>81</v>
+      </c>
+      <c r="E77" s="20"/>
+      <c r="F77" s="20"/>
+      <c r="G77" s="20"/>
+      <c r="H77" s="21"/>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="B78" s="17"/>
+      <c r="C78" s="17"/>
+      <c r="D78" s="17"/>
+      <c r="E78" s="17"/>
+      <c r="F78" s="25"/>
+      <c r="G78" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="H77" s="18"/>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="22"/>
-      <c r="B78" s="1"/>
-      <c r="C78" s="1"/>
-      <c r="D78" s="1"/>
-      <c r="E78" s="1"/>
-      <c r="F78" s="1"/>
-      <c r="G78" s="48" t="s">
-        <v>13</v>
-      </c>
-      <c r="H78" s="23"/>
+      <c r="H78" s="18"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="22"/>
@@ -7582,93 +7615,93 @@
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
-      <c r="G79" s="50" t="s">
+      <c r="G79" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="H79" s="23"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" s="22"/>
+      <c r="B80" s="1"/>
+      <c r="C80" s="1"/>
+      <c r="D80" s="1"/>
+      <c r="E80" s="1"/>
+      <c r="F80" s="1"/>
+      <c r="G80" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="H79" s="23"/>
-    </row>
-    <row r="80" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="19"/>
-      <c r="B80" s="20"/>
-      <c r="C80" s="20"/>
-      <c r="D80" s="20"/>
-      <c r="E80" s="20"/>
-      <c r="F80" s="20"/>
-      <c r="G80" s="49" t="s">
-        <v>111</v>
-      </c>
-      <c r="H80" s="21"/>
+      <c r="H80" s="23"/>
     </row>
     <row r="81" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="B81" s="17"/>
-      <c r="C81" s="17"/>
-      <c r="D81" s="17"/>
-      <c r="E81" s="17"/>
-      <c r="F81" s="25"/>
-      <c r="G81" s="17"/>
-      <c r="H81" s="18"/>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="B82" s="17" t="s">
-        <v>15</v>
-      </c>
+      <c r="A81" s="19"/>
+      <c r="B81" s="20"/>
+      <c r="C81" s="20"/>
+      <c r="D81" s="20"/>
+      <c r="E81" s="20"/>
+      <c r="F81" s="20"/>
+      <c r="G81" s="49" t="s">
+        <v>108</v>
+      </c>
+      <c r="H81" s="21"/>
+    </row>
+    <row r="82" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="B82" s="17"/>
       <c r="C82" s="17"/>
       <c r="D82" s="17"/>
       <c r="E82" s="17"/>
-      <c r="F82" s="17" t="s">
-        <v>15</v>
-      </c>
+      <c r="F82" s="25"/>
       <c r="G82" s="17"/>
       <c r="H82" s="18"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="22"/>
-      <c r="B83" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C83" s="1"/>
-      <c r="D83" s="1"/>
-      <c r="E83" s="1"/>
-      <c r="F83" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="G83" s="1"/>
-      <c r="H83" s="23"/>
+      <c r="A83" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="B83" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C83" s="17"/>
+      <c r="D83" s="17"/>
+      <c r="E83" s="17"/>
+      <c r="F83" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="G83" s="17"/>
+      <c r="H83" s="18"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="22"/>
-      <c r="B84" s="40" t="s">
-        <v>27</v>
+      <c r="B84" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="C84" s="1"/>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
-      <c r="F84" s="24"/>
+      <c r="F84" s="1" t="s">
+        <v>112</v>
+      </c>
       <c r="G84" s="1"/>
       <c r="H84" s="23"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="22"/>
-      <c r="B85" s="41" t="s">
-        <v>116</v>
+      <c r="B85" s="40" t="s">
+        <v>26</v>
       </c>
       <c r="C85" s="1"/>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
-      <c r="F85" s="1"/>
+      <c r="F85" s="24"/>
       <c r="G85" s="1"/>
       <c r="H85" s="23"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="22"/>
-      <c r="B86" s="2" t="s">
-        <v>15</v>
+      <c r="B86" s="41" t="s">
+        <v>113</v>
       </c>
       <c r="C86" s="1"/>
       <c r="D86" s="1"/>
@@ -7677,91 +7710,104 @@
       <c r="G86" s="1"/>
       <c r="H86" s="23"/>
     </row>
-    <row r="87" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="19"/>
-      <c r="B87" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="C87" s="20"/>
-      <c r="D87" s="20"/>
-      <c r="E87" s="20"/>
-      <c r="F87" s="20"/>
-      <c r="G87" s="20"/>
-      <c r="H87" s="21"/>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="B88" s="17"/>
-      <c r="C88" s="17"/>
-      <c r="D88" s="47" t="s">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="22"/>
+      <c r="B87" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C87" s="1"/>
+      <c r="D87" s="1"/>
+      <c r="E87" s="1"/>
+      <c r="F87" s="1"/>
+      <c r="G87" s="1"/>
+      <c r="H87" s="23"/>
+    </row>
+    <row r="88" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="19"/>
+      <c r="B88" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="C88" s="20"/>
+      <c r="D88" s="20"/>
+      <c r="E88" s="20"/>
+      <c r="F88" s="20"/>
+      <c r="G88" s="20"/>
+      <c r="H88" s="21"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="B89" s="17"/>
+      <c r="C89" s="17"/>
+      <c r="D89" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="E88" s="17"/>
-      <c r="F88" s="47" t="s">
+      <c r="E89" s="17"/>
+      <c r="F89" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="G88" s="17"/>
-      <c r="H88" s="18"/>
-    </row>
-    <row r="89" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="19"/>
-      <c r="B89" s="20"/>
-      <c r="C89" s="20"/>
-      <c r="D89" s="49" t="s">
-        <v>82</v>
-      </c>
-      <c r="E89" s="20"/>
-      <c r="F89" s="49" t="s">
-        <v>64</v>
-      </c>
-      <c r="G89" s="20"/>
-      <c r="H89" s="21"/>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B90" s="15"/>
-      <c r="C90" s="15"/>
-      <c r="D90" s="15"/>
-      <c r="E90" s="15"/>
-      <c r="F90" s="15"/>
-      <c r="G90" s="15"/>
-      <c r="H90" s="15"/>
+      <c r="G89" s="17"/>
+      <c r="H89" s="18"/>
+    </row>
+    <row r="90" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="19"/>
+      <c r="B90" s="20"/>
+      <c r="C90" s="20"/>
+      <c r="D90" s="49" t="s">
+        <v>81</v>
+      </c>
+      <c r="E90" s="20"/>
+      <c r="F90" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="G90" s="20"/>
+      <c r="H90" s="21"/>
+    </row>
+    <row r="91" spans="1:8" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B91" s="15"/>
+      <c r="C91" s="15"/>
+      <c r="D91" s="15"/>
+      <c r="E91" s="15"/>
+      <c r="F91" s="15"/>
+      <c r="G91" s="15"/>
+      <c r="H91" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="B44:H44"/>
     <mergeCell ref="B43:H43"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B56:H56"/>
+    <mergeCell ref="B57:H57"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B1:H1"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A36:A39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="A50:A55"/>
-    <mergeCell ref="A57:A64"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="A67:A70"/>
-    <mergeCell ref="A71:A74"/>
-    <mergeCell ref="B90:H90"/>
-    <mergeCell ref="A75:A76"/>
-    <mergeCell ref="A77:A80"/>
-    <mergeCell ref="A82:A87"/>
-    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A9:A16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A21:A24"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="A27:A34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A37:A40"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="A51:A56"/>
+    <mergeCell ref="A58:A65"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="A68:A71"/>
+    <mergeCell ref="A72:A75"/>
+    <mergeCell ref="B91:H91"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="A78:A81"/>
+    <mergeCell ref="A83:A88"/>
+    <mergeCell ref="A89:A90"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" scale="35" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -7777,7 +7823,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="13" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
@@ -7785,7 +7831,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" s="14" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
@@ -7796,16 +7842,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>121</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -7861,7 +7907,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B10" s="7">
         <v>0</v>
@@ -7878,7 +7924,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" s="7">
         <v>0</v>
@@ -7895,7 +7941,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12" s="7">
         <v>0</v>
@@ -7912,7 +7958,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B13" s="7">
         <v>0</v>
@@ -7929,7 +7975,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B14" s="7">
         <v>0</v>
@@ -7946,7 +7992,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B15" s="7">
         <v>0</v>
@@ -7963,7 +8009,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B16" s="7">
         <v>0</v>
@@ -7980,7 +8026,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B17" s="7">
         <v>0</v>
@@ -7997,7 +8043,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B18" s="7">
         <v>0</v>
@@ -8014,7 +8060,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B19" s="7">
         <v>0</v>
@@ -8031,7 +8077,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B20" s="7">
         <v>0</v>
@@ -8048,7 +8094,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B21" s="7">
         <v>0</v>
@@ -8065,7 +8111,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B22" s="7">
         <v>0</v>
@@ -8082,7 +8128,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B23" s="7">
         <v>0</v>
@@ -8099,7 +8145,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B24" s="7">
         <v>0</v>
@@ -8116,7 +8162,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B25" s="7">
         <v>0</v>
@@ -8133,7 +8179,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B26" s="7">
         <v>0</v>
@@ -8150,7 +8196,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B27" s="7">
         <v>0</v>
@@ -8167,7 +8213,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B28" s="7">
         <v>0</v>
@@ -8184,7 +8230,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B29" s="7">
         <v>0</v>
@@ -8201,7 +8247,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B30" s="7">
         <v>0</v>
@@ -8218,7 +8264,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B31" s="7">
         <v>0</v>
@@ -8235,7 +8281,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B32" s="7">
         <v>0</v>
@@ -8252,7 +8298,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B33" s="7">
         <v>0</v>
@@ -8269,7 +8315,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B34" s="7">
         <v>0</v>
@@ -8319,40 +8365,40 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/Plannings 2026 S19.xlsx
+++ b/Plannings 2026 S19.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="66" documentId="8_{84830FEF-CD99-488C-9111-90B341AA8F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A8FAAA4-DBC4-4BEA-9618-B21912BDD4DF}"/>
+  <xr:revisionPtr revIDLastSave="75" documentId="8_{84830FEF-CD99-488C-9111-90B341AA8F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33DBCCB4-6DD3-4F5C-A9C6-1F2F35E55F60}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="133">
   <si>
     <t>Planning des salariés du 04/05/2026 au 10/05/2026</t>
   </si>
@@ -412,6 +412,15 @@
   </si>
   <si>
     <t>22/04/2026 18:48</t>
+  </si>
+  <si>
+    <t>P50 // EDF // C. PADEL // LEAGUES</t>
+  </si>
+  <si>
+    <t>EDF // C. PADEL // LEAGUES // LDC</t>
+  </si>
+  <si>
+    <t>EDF    //    C. PADEL    //    LEAGUES    //    LDC : BAYERN-PSG</t>
   </si>
 </sst>
 </file>
@@ -822,7 +831,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -999,6 +1008,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6418,7 +6433,7 @@
   <dimension ref="A1:H91"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="8" width="46.42578125" customWidth="1"/>
+    <col min="1" max="8" width="47.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6443,14 +6458,20 @@
       <c r="G2" s="12"/>
       <c r="H2" s="12"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
+    <row r="3" spans="1:8" s="61" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B3" s="62" t="s">
+        <v>130</v>
+      </c>
+      <c r="C3" s="62" t="s">
+        <v>131</v>
+      </c>
+      <c r="D3" s="62" t="s">
+        <v>132</v>
+      </c>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
+      <c r="G3" s="62"/>
+      <c r="H3" s="62"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="28" t="s">
@@ -7806,7 +7827,7 @@
     <mergeCell ref="A89:A90"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="35" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="34" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>

--- a/Plannings 2026 S19.xlsx
+++ b/Plannings 2026 S19.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="75" documentId="8_{84830FEF-CD99-488C-9111-90B341AA8F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33DBCCB4-6DD3-4F5C-A9C6-1F2F35E55F60}"/>
+  <xr:revisionPtr revIDLastSave="82" documentId="8_{84830FEF-CD99-488C-9111-90B341AA8F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE736EBC-F88E-4637-B75F-5CD9E0EFE10D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="136">
   <si>
     <t>Planning des salariés du 04/05/2026 au 10/05/2026</t>
   </si>
@@ -421,6 +421,15 @@
   </si>
   <si>
     <t>EDF    //    C. PADEL    //    LEAGUES    //    LDC : BAYERN-PSG</t>
+  </si>
+  <si>
+    <t>P100 // EDF // C. PADEL</t>
+  </si>
+  <si>
+    <t>C. PADEL</t>
+  </si>
+  <si>
+    <t>EDF // ANNIV</t>
   </si>
 </sst>
 </file>
@@ -831,7 +840,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1014,6 +1023,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6468,10 +6480,18 @@
       <c r="D3" s="62" t="s">
         <v>132</v>
       </c>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
+      <c r="E3" s="62" t="s">
+        <v>134</v>
+      </c>
+      <c r="F3" s="62" t="s">
+        <v>133</v>
+      </c>
+      <c r="G3" s="62" t="s">
+        <v>135</v>
+      </c>
+      <c r="H3" s="62" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="28" t="s">
@@ -7416,7 +7436,7 @@
       </c>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
-      <c r="G64" s="2" t="s">
+      <c r="G64" s="63" t="s">
         <v>80</v>
       </c>
       <c r="H64" s="23"/>
@@ -7430,7 +7450,7 @@
       </c>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
-      <c r="G65" s="1" t="s">
+      <c r="G65" s="52" t="s">
         <v>94</v>
       </c>
       <c r="H65" s="23"/>

--- a/Plannings 2026 S19.xlsx
+++ b/Plannings 2026 S19.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="82" documentId="8_{84830FEF-CD99-488C-9111-90B341AA8F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE736EBC-F88E-4637-B75F-5CD9E0EFE10D}"/>
+  <xr:revisionPtr revIDLastSave="86" documentId="8_{84830FEF-CD99-488C-9111-90B341AA8F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAA3BF94-D7E8-43E9-901B-BBF8227E3D42}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="137">
   <si>
     <t>Planning des salariés du 04/05/2026 au 10/05/2026</t>
   </si>
@@ -357,18 +357,12 @@
     <t>TOPPAN Mattis</t>
   </si>
   <si>
-    <t>17:00/21:00</t>
-  </si>
-  <si>
     <t>17:30/00:20+</t>
   </si>
   <si>
     <t>21:00/22:00</t>
   </si>
   <si>
-    <t>22:00/00:15+</t>
-  </si>
-  <si>
     <t>VASSANT Tiffany</t>
   </si>
   <si>
@@ -430,6 +424,15 @@
   </si>
   <si>
     <t>EDF // ANNIV</t>
+  </si>
+  <si>
+    <t>22:00/22:30</t>
+  </si>
+  <si>
+    <t>13:30/21:00</t>
+  </si>
+  <si>
+    <t>22:30/00:15+</t>
   </si>
 </sst>
 </file>
@@ -439,7 +442,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[h]:mm"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -528,6 +531,12 @@
     <font>
       <sz val="8"/>
       <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color indexed="8"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -840,7 +849,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1027,6 +1036,12 @@
     <xf numFmtId="0" fontId="15" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6061,6 +6076,50 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="3048000" y="12001500"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="40" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB577FA1-236B-4B44-9758-6CE39BE9BFDC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15920357" y="13566321"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6472,22 +6531,22 @@
     </row>
     <row r="3" spans="1:8" s="61" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B3" s="62" t="s">
+        <v>128</v>
+      </c>
+      <c r="C3" s="62" t="s">
+        <v>129</v>
+      </c>
+      <c r="D3" s="62" t="s">
         <v>130</v>
       </c>
-      <c r="C3" s="62" t="s">
+      <c r="E3" s="62" t="s">
+        <v>132</v>
+      </c>
+      <c r="F3" s="62" t="s">
         <v>131</v>
       </c>
-      <c r="D3" s="62" t="s">
-        <v>132</v>
-      </c>
-      <c r="E3" s="62" t="s">
-        <v>134</v>
-      </c>
-      <c r="F3" s="62" t="s">
+      <c r="G3" s="62" t="s">
         <v>133</v>
-      </c>
-      <c r="G3" s="62" t="s">
-        <v>135</v>
       </c>
       <c r="H3" s="62" t="s">
         <v>80</v>
@@ -7587,7 +7646,9 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="22"/>
-      <c r="B74" s="41"/>
+      <c r="B74" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
@@ -7599,7 +7660,9 @@
     </row>
     <row r="75" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="19"/>
-      <c r="B75" s="42"/>
+      <c r="B75" s="64" t="s">
+        <v>136</v>
+      </c>
       <c r="C75" s="20"/>
       <c r="D75" s="20"/>
       <c r="E75" s="20"/>
@@ -7715,14 +7778,14 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="22"/>
-      <c r="B84" s="1" t="s">
-        <v>111</v>
+      <c r="B84" s="65" t="s">
+        <v>135</v>
       </c>
       <c r="C84" s="1"/>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
       <c r="F84" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G84" s="1"/>
       <c r="H84" s="23"/>
@@ -7742,7 +7805,7 @@
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="22"/>
       <c r="B86" s="41" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C86" s="1"/>
       <c r="D86" s="1"/>
@@ -7765,8 +7828,8 @@
     </row>
     <row r="88" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="19"/>
-      <c r="B88" s="20" t="s">
-        <v>114</v>
+      <c r="B88" s="64" t="s">
+        <v>134</v>
       </c>
       <c r="C88" s="20"/>
       <c r="D88" s="20"/>
@@ -7777,7 +7840,7 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="16" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B89" s="17"/>
       <c r="C89" s="17"/>
@@ -7864,7 +7927,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="13" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
@@ -7872,7 +7935,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" s="14" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
@@ -7883,16 +7946,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>119</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -8356,7 +8419,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B34" s="7">
         <v>0</v>
@@ -8406,21 +8469,21 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>96</v>
@@ -8428,18 +8491,18 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -8643,10 +8706,16 @@
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8A8CB62-EC1E-4BD8-BBB5-8A7D85090CA9}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="17e8e7ea-beb0-4155-adc4-5bfa61f32508"/>
+    <ds:schemaRef ds:uri="3c298670-db79-47a5-968d-a4570c34317f"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3c298670-db79-47a5-968d-a4570c34317f"/>
-    <ds:schemaRef ds:uri="17e8e7ea-beb0-4155-adc4-5bfa61f32508"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Plannings 2026 S19.xlsx
+++ b/Plannings 2026 S19.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="86" documentId="8_{84830FEF-CD99-488C-9111-90B341AA8F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAA3BF94-D7E8-43E9-901B-BBF8227E3D42}"/>
+  <xr:revisionPtr revIDLastSave="100" documentId="8_{84830FEF-CD99-488C-9111-90B341AA8F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{426CE5C1-628F-4671-A806-6F1357DEC51D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="139">
   <si>
     <t>Planning des salariés du 04/05/2026 au 10/05/2026</t>
   </si>
@@ -339,9 +339,6 @@
     <t>RABII Mehdi</t>
   </si>
   <si>
-    <t>17:45/22:20</t>
-  </si>
-  <si>
     <t>SANGARNE Enzo</t>
   </si>
   <si>
@@ -433,6 +430,15 @@
   </si>
   <si>
     <t>22:30/00:15+</t>
+  </si>
+  <si>
+    <t>10:45/12:45</t>
+  </si>
+  <si>
+    <t>13:50/17:50</t>
+  </si>
+  <si>
+    <t>17:50/22:10</t>
   </si>
 </sst>
 </file>
@@ -849,7 +855,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1042,6 +1048,9 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5429,13 +5438,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>75</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5461,50 +5470,6 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="111" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5528,10 +5493,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="112" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000070000000}"/>
+        <xdr:cNvPr id="111" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00006F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5559,252 +5524,120 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="113" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000071000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>79</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="114" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000072000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>81</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="112" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000070000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="113" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000071000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>81</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="115" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000073000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="116" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000074000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="117" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000075000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="118" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000076000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="114" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000072000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5825,118 +5658,162 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="119" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000077000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>83</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="115" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000073000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>84</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="120" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000078000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="114300" cy="114300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="116" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000074000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="117" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000075000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>88</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
       <xdr:row>88</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="121" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000079000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <xdr:cNvPr id="118" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000076000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5957,17 +5834,149 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="119" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000077000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>86</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>86</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
+        <xdr:cNvPr id="120" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000078000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="114300" cy="114300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="121" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000079000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
         <xdr:cNvPr id="122" name="Picture 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
@@ -6045,13 +6054,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>90</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>90</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6120,6 +6129,138 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="15920357" y="13566321"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="50" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF83E942-3588-4F58-AD98-AF6CAA8C1018}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4267200" y="20202525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="123" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{394C3646-1BF0-45FF-9135-153738395705}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4267200" y="20583525"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="126" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{848D63D7-541D-48B6-8757-7A4ECB5EA2D9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4267200" y="20964525"/>
           <a:ext cx="123825" cy="123825"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6501,10 +6642,11 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H91"/>
+  <dimension ref="A1:H93"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="8" width="47.7109375" customWidth="1"/>
+    <col min="1" max="1" width="50.28515625" customWidth="1"/>
+    <col min="2" max="8" width="47.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6531,22 +6673,22 @@
     </row>
     <row r="3" spans="1:8" s="61" customFormat="1" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B3" s="62" t="s">
+        <v>127</v>
+      </c>
+      <c r="C3" s="62" t="s">
         <v>128</v>
       </c>
-      <c r="C3" s="62" t="s">
+      <c r="D3" s="62" t="s">
         <v>129</v>
       </c>
-      <c r="D3" s="62" t="s">
+      <c r="E3" s="62" t="s">
+        <v>131</v>
+      </c>
+      <c r="F3" s="62" t="s">
         <v>130</v>
       </c>
-      <c r="E3" s="62" t="s">
+      <c r="G3" s="62" t="s">
         <v>132</v>
-      </c>
-      <c r="F3" s="62" t="s">
-        <v>131</v>
-      </c>
-      <c r="G3" s="62" t="s">
-        <v>133</v>
       </c>
       <c r="H3" s="62" t="s">
         <v>80</v>
@@ -7626,7 +7768,7 @@
       <c r="E72" s="1"/>
       <c r="F72" s="24"/>
       <c r="G72" s="1"/>
-      <c r="H72" s="54" t="s">
+      <c r="H72" s="63" t="s">
         <v>80</v>
       </c>
     </row>
@@ -7640,8 +7782,8 @@
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
-      <c r="H73" s="54" t="s">
-        <v>81</v>
+      <c r="H73" s="52" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -7654,228 +7796,252 @@
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
-      <c r="H74" s="26" t="s">
+      <c r="H74" s="63" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="31"/>
+      <c r="B75" s="65" t="s">
+        <v>135</v>
+      </c>
+      <c r="C75" s="1"/>
+      <c r="D75" s="1"/>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="52" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="31"/>
+      <c r="B76" s="1"/>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="66" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="75" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="19"/>
-      <c r="B75" s="64" t="s">
-        <v>136</v>
-      </c>
-      <c r="C75" s="20"/>
-      <c r="D75" s="20"/>
-      <c r="E75" s="20"/>
-      <c r="F75" s="20"/>
-      <c r="G75" s="20"/>
-      <c r="H75" s="21" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="B76" s="17"/>
-      <c r="C76" s="17"/>
-      <c r="D76" s="47" t="s">
-        <v>12</v>
-      </c>
-      <c r="E76" s="17"/>
-      <c r="F76" s="25"/>
-      <c r="G76" s="17"/>
-      <c r="H76" s="18"/>
     </row>
     <row r="77" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="19"/>
-      <c r="B77" s="20"/>
+      <c r="B77" s="64"/>
       <c r="C77" s="20"/>
-      <c r="D77" s="49" t="s">
-        <v>81</v>
-      </c>
+      <c r="D77" s="20"/>
       <c r="E77" s="20"/>
       <c r="F77" s="20"/>
       <c r="G77" s="20"/>
-      <c r="H77" s="21"/>
+      <c r="H77" s="65" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="16" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B78" s="17"/>
       <c r="C78" s="17"/>
-      <c r="D78" s="17"/>
+      <c r="D78" s="47" t="s">
+        <v>12</v>
+      </c>
       <c r="E78" s="17"/>
       <c r="F78" s="25"/>
-      <c r="G78" s="47" t="s">
+      <c r="G78" s="17"/>
+      <c r="H78" s="18"/>
+    </row>
+    <row r="79" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="19"/>
+      <c r="B79" s="20"/>
+      <c r="C79" s="20"/>
+      <c r="D79" s="49" t="s">
+        <v>81</v>
+      </c>
+      <c r="E79" s="20"/>
+      <c r="F79" s="20"/>
+      <c r="G79" s="20"/>
+      <c r="H79" s="21"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="B80" s="17"/>
+      <c r="C80" s="17"/>
+      <c r="D80" s="17"/>
+      <c r="E80" s="17"/>
+      <c r="F80" s="25"/>
+      <c r="G80" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="H78" s="18"/>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="22"/>
-      <c r="B79" s="1"/>
-      <c r="C79" s="1"/>
-      <c r="D79" s="1"/>
-      <c r="E79" s="1"/>
-      <c r="F79" s="1"/>
-      <c r="G79" s="48" t="s">
+      <c r="H80" s="18"/>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="22"/>
+      <c r="B81" s="1"/>
+      <c r="C81" s="1"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="H79" s="23"/>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="22"/>
-      <c r="B80" s="1"/>
-      <c r="C80" s="1"/>
-      <c r="D80" s="1"/>
-      <c r="E80" s="1"/>
-      <c r="F80" s="1"/>
-      <c r="G80" s="50" t="s">
+      <c r="H81" s="23"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="22"/>
+      <c r="B82" s="1"/>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="H80" s="23"/>
-    </row>
-    <row r="81" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="19"/>
-      <c r="B81" s="20"/>
-      <c r="C81" s="20"/>
-      <c r="D81" s="20"/>
-      <c r="E81" s="20"/>
-      <c r="F81" s="20"/>
-      <c r="G81" s="49" t="s">
+      <c r="H82" s="23"/>
+    </row>
+    <row r="83" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="19"/>
+      <c r="B83" s="20"/>
+      <c r="C83" s="20"/>
+      <c r="D83" s="20"/>
+      <c r="E83" s="20"/>
+      <c r="F83" s="20"/>
+      <c r="G83" s="49" t="s">
+        <v>107</v>
+      </c>
+      <c r="H83" s="21"/>
+    </row>
+    <row r="84" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="H81" s="21"/>
-    </row>
-    <row r="82" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="27" t="s">
+      <c r="B84" s="17"/>
+      <c r="C84" s="17"/>
+      <c r="D84" s="17"/>
+      <c r="E84" s="17"/>
+      <c r="F84" s="25"/>
+      <c r="G84" s="17"/>
+      <c r="H84" s="18"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="B82" s="17"/>
-      <c r="C82" s="17"/>
-      <c r="D82" s="17"/>
-      <c r="E82" s="17"/>
-      <c r="F82" s="25"/>
-      <c r="G82" s="17"/>
-      <c r="H82" s="18"/>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="B83" s="17" t="s">
+      <c r="B85" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="C83" s="17"/>
-      <c r="D83" s="17"/>
-      <c r="E83" s="17"/>
-      <c r="F83" s="17" t="s">
+      <c r="C85" s="17"/>
+      <c r="D85" s="17"/>
+      <c r="E85" s="17"/>
+      <c r="F85" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="G83" s="17"/>
-      <c r="H83" s="18"/>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="22"/>
-      <c r="B84" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="C84" s="1"/>
-      <c r="D84" s="1"/>
-      <c r="E84" s="1"/>
-      <c r="F84" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G84" s="1"/>
-      <c r="H84" s="23"/>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="22"/>
-      <c r="B85" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="C85" s="1"/>
-      <c r="D85" s="1"/>
-      <c r="E85" s="1"/>
-      <c r="F85" s="24"/>
-      <c r="G85" s="1"/>
-      <c r="H85" s="23"/>
+      <c r="G85" s="17"/>
+      <c r="H85" s="18"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="22"/>
-      <c r="B86" s="41" t="s">
-        <v>112</v>
+      <c r="B86" s="65" t="s">
+        <v>134</v>
       </c>
       <c r="C86" s="1"/>
       <c r="D86" s="1"/>
       <c r="E86" s="1"/>
-      <c r="F86" s="1"/>
+      <c r="F86" s="1" t="s">
+        <v>110</v>
+      </c>
       <c r="G86" s="1"/>
       <c r="H86" s="23"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="22"/>
-      <c r="B87" s="2" t="s">
-        <v>15</v>
+      <c r="B87" s="40" t="s">
+        <v>26</v>
       </c>
       <c r="C87" s="1"/>
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
-      <c r="F87" s="1"/>
+      <c r="F87" s="24"/>
       <c r="G87" s="1"/>
       <c r="H87" s="23"/>
     </row>
-    <row r="88" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="19"/>
-      <c r="B88" s="64" t="s">
-        <v>134</v>
-      </c>
-      <c r="C88" s="20"/>
-      <c r="D88" s="20"/>
-      <c r="E88" s="20"/>
-      <c r="F88" s="20"/>
-      <c r="G88" s="20"/>
-      <c r="H88" s="21"/>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="22"/>
+      <c r="B88" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="C88" s="1"/>
+      <c r="D88" s="1"/>
+      <c r="E88" s="1"/>
+      <c r="F88" s="1"/>
+      <c r="G88" s="1"/>
+      <c r="H88" s="23"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="B89" s="17"/>
-      <c r="C89" s="17"/>
-      <c r="D89" s="47" t="s">
-        <v>12</v>
-      </c>
-      <c r="E89" s="17"/>
-      <c r="F89" s="47" t="s">
-        <v>12</v>
-      </c>
-      <c r="G89" s="17"/>
-      <c r="H89" s="18"/>
+      <c r="A89" s="22"/>
+      <c r="B89" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C89" s="1"/>
+      <c r="D89" s="1"/>
+      <c r="E89" s="1"/>
+      <c r="F89" s="1"/>
+      <c r="G89" s="1"/>
+      <c r="H89" s="23"/>
     </row>
     <row r="90" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="19"/>
-      <c r="B90" s="20"/>
+      <c r="B90" s="64" t="s">
+        <v>133</v>
+      </c>
       <c r="C90" s="20"/>
-      <c r="D90" s="49" t="s">
-        <v>81</v>
-      </c>
+      <c r="D90" s="20"/>
       <c r="E90" s="20"/>
-      <c r="F90" s="49" t="s">
-        <v>63</v>
-      </c>
+      <c r="F90" s="20"/>
       <c r="G90" s="20"/>
       <c r="H90" s="21"/>
     </row>
-    <row r="91" spans="1:8" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B91" s="15"/>
-      <c r="C91" s="15"/>
-      <c r="D91" s="15"/>
-      <c r="E91" s="15"/>
-      <c r="F91" s="15"/>
-      <c r="G91" s="15"/>
-      <c r="H91" s="15"/>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="B91" s="17"/>
+      <c r="C91" s="17"/>
+      <c r="D91" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="E91" s="17"/>
+      <c r="F91" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="G91" s="17"/>
+      <c r="H91" s="18"/>
+    </row>
+    <row r="92" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="19"/>
+      <c r="B92" s="20"/>
+      <c r="C92" s="20"/>
+      <c r="D92" s="49" t="s">
+        <v>81</v>
+      </c>
+      <c r="E92" s="20"/>
+      <c r="F92" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="G92" s="20"/>
+      <c r="H92" s="21"/>
+    </row>
+    <row r="93" spans="1:8" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B93" s="15"/>
+      <c r="C93" s="15"/>
+      <c r="D93" s="15"/>
+      <c r="E93" s="15"/>
+      <c r="F93" s="15"/>
+      <c r="G93" s="15"/>
+      <c r="H93" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="29">
@@ -7902,12 +8068,12 @@
     <mergeCell ref="A58:A65"/>
     <mergeCell ref="A66:A67"/>
     <mergeCell ref="A68:A71"/>
-    <mergeCell ref="A72:A75"/>
-    <mergeCell ref="B91:H91"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="A78:A81"/>
-    <mergeCell ref="A83:A88"/>
-    <mergeCell ref="A89:A90"/>
+    <mergeCell ref="A72:A77"/>
+    <mergeCell ref="B93:H93"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="A80:A83"/>
+    <mergeCell ref="A85:A90"/>
+    <mergeCell ref="A91:A92"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="34" fitToHeight="0" orientation="landscape" r:id="rId1"/>
@@ -7927,7 +8093,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
@@ -7935,7 +8101,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" s="14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
@@ -7946,16 +8112,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>118</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -8351,7 +8517,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B30" s="7">
         <v>0</v>
@@ -8368,7 +8534,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B31" s="7">
         <v>0</v>
@@ -8385,7 +8551,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B32" s="7">
         <v>0</v>
@@ -8402,7 +8568,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B33" s="7">
         <v>0</v>
@@ -8419,7 +8585,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B34" s="7">
         <v>0</v>
@@ -8469,21 +8635,21 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>120</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>96</v>
@@ -8491,18 +8657,18 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>124</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>126</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>127</v>
       </c>
     </row>
   </sheetData>
